--- a/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:AQ32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0156</v>
+        <v>0.09705</v>
       </c>
       <c r="E2">
-        <v>0.103</v>
+        <v>0.1285</v>
       </c>
       <c r="F2">
-        <v>0.329</v>
+        <v>0.209</v>
       </c>
       <c r="G2">
-        <v>0.1081543601455871</v>
+        <v>0.02950827904728575</v>
       </c>
       <c r="H2">
-        <v>0.08112438737615073</v>
+        <v>-0.004879859261688828</v>
       </c>
       <c r="I2">
-        <v>0.08337265238299636</v>
+        <v>-0.04705235186745236</v>
       </c>
       <c r="J2">
-        <v>0.07026184333933048</v>
+        <v>-0.03984908628244688</v>
       </c>
       <c r="K2">
-        <v>1862.95</v>
+        <v>2318.291</v>
       </c>
       <c r="L2">
-        <v>0.1486438655910615</v>
+        <v>0.1819092106068476</v>
       </c>
       <c r="M2">
-        <v>3222.313</v>
+        <v>3749.3293</v>
       </c>
       <c r="N2">
-        <v>0.03222685542448707</v>
+        <v>0.05298911055647105</v>
       </c>
       <c r="O2">
-        <v>1.729683029603586</v>
+        <v>1.617281566464262</v>
       </c>
       <c r="P2">
-        <v>3028.595</v>
+        <v>3066.9543</v>
       </c>
       <c r="Q2">
-        <v>0.03028945146058884</v>
+        <v>0.04334513388150363</v>
       </c>
       <c r="R2">
-        <v>1.625698488955689</v>
+        <v>1.322937586351325</v>
       </c>
       <c r="S2">
-        <v>193.718</v>
+        <v>682.375</v>
       </c>
       <c r="T2">
-        <v>0.0601176856500284</v>
+        <v>0.1819992178334403</v>
       </c>
       <c r="U2">
-        <v>26354.825</v>
+        <v>25517.969</v>
       </c>
       <c r="V2">
-        <v>0.2635787196999973</v>
+        <v>0.3606443639179949</v>
       </c>
       <c r="W2">
-        <v>0.06567157503702983</v>
+        <v>0.05064261420389173</v>
       </c>
       <c r="X2">
-        <v>0.02671619154126129</v>
+        <v>0.05360988815958427</v>
       </c>
       <c r="Y2">
-        <v>0.03895538349576854</v>
+        <v>-0.002967273955692545</v>
       </c>
       <c r="Z2">
-        <v>0.1222292241436745</v>
+        <v>0.09783591774518501</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02620291131922228</v>
+        <v>0.05084166475712444</v>
       </c>
       <c r="AC2">
-        <v>-0.02555524450752344</v>
+        <v>-0.0503393639490503</v>
       </c>
       <c r="AD2">
-        <v>117514.541</v>
+        <v>121235.439</v>
       </c>
       <c r="AE2">
-        <v>227.0527431378185</v>
+        <v>0.9176185811185392</v>
       </c>
       <c r="AF2">
-        <v>117741.5937431378</v>
+        <v>121236.3566185811</v>
       </c>
       <c r="AG2">
-        <v>91386.76874313781</v>
+        <v>95718.38761858112</v>
       </c>
       <c r="AH2">
-        <v>0.5407687296004411</v>
+        <v>0.6314625221352929</v>
       </c>
       <c r="AI2">
-        <v>0.7397553435457539</v>
+        <v>0.7265985803184357</v>
       </c>
       <c r="AJ2">
-        <v>0.4775266835413168</v>
+        <v>0.5749715857488822</v>
       </c>
       <c r="AK2">
-        <v>0.6881116222012376</v>
+        <v>0.6772366696246057</v>
       </c>
       <c r="AL2">
-        <v>856.393</v>
+        <v>784.89</v>
       </c>
       <c r="AM2">
-        <v>235.588</v>
+        <v>-90.25599999999997</v>
       </c>
       <c r="AN2">
-        <v>100.8476513557396</v>
+        <v>-288.9915878449246</v>
       </c>
       <c r="AO2">
-        <v>1.164453702914433</v>
+        <v>-0.7646421791588631</v>
       </c>
       <c r="AP2">
-        <v>78.42553708085849</v>
+        <v>-228.1660300982597</v>
       </c>
       <c r="AQ2">
-        <v>4.232940557244003</v>
+        <v>6.64953022513739</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zero2IPO Holdings Inc. (SEHK:1945)</t>
+          <t>Hithink RoyalFlush Information Network Co., Ltd. (SZSE:300033)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,113 +724,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.188</v>
+      </c>
+      <c r="E3">
+        <v>0.134</v>
+      </c>
+      <c r="F3">
+        <v>0.305</v>
+      </c>
       <c r="G3">
-        <v>0.2472303206997085</v>
+        <v>0.8952776131199368</v>
       </c>
       <c r="H3">
-        <v>0.1921282798833819</v>
+        <v>0.6022525192649674</v>
       </c>
       <c r="I3">
-        <v>0.2880466472303208</v>
+        <v>0.4706579727326615</v>
       </c>
       <c r="J3">
-        <v>0.2268553905648122</v>
+        <v>0.4322891162598901</v>
       </c>
       <c r="K3">
-        <v>7.61</v>
+        <v>253.4</v>
       </c>
       <c r="L3">
-        <v>0.221865889212828</v>
+        <v>0.5006915629322268</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>136</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01769427928338169</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.5367008681925809</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>136</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01769427928338169</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.5367008681925809</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>60.4</v>
+        <v>956.1</v>
       </c>
       <c r="V3">
-        <v>0.3904330963154493</v>
+        <v>0.1243933854620679</v>
       </c>
       <c r="W3">
-        <v>1.393772893772894</v>
+        <v>0.293422880963409</v>
       </c>
       <c r="X3">
-        <v>0.02440260948526917</v>
+        <v>0.05005624910221628</v>
       </c>
       <c r="Y3">
-        <v>1.369370284287625</v>
-      </c>
-      <c r="Z3">
-        <v>21.70886075949367</v>
-      </c>
-      <c r="AA3">
-        <v>4.924772086312061</v>
+        <v>0.2433666318611927</v>
       </c>
       <c r="AB3">
-        <v>0.02445036575366338</v>
-      </c>
-      <c r="AC3">
-        <v>4.900321720558398</v>
+        <v>0.05005617042465565</v>
       </c>
       <c r="AD3">
-        <v>2.24</v>
+        <v>0.259</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.24</v>
+        <v>0.259</v>
       </c>
       <c r="AG3">
-        <v>-58.16</v>
+        <v>-955.841</v>
       </c>
       <c r="AH3">
-        <v>0.01427297056199822</v>
+        <v>3.369605817266667e-05</v>
       </c>
       <c r="AI3">
-        <v>0.02837598175829744</v>
+        <v>0.0002857902652552968</v>
       </c>
       <c r="AJ3">
-        <v>-0.6024445825564533</v>
+        <v>-0.142021428893004</v>
       </c>
       <c r="AK3">
-        <v>-3.13700107874865</v>
+        <v>19.17780542123954</v>
       </c>
       <c r="AL3">
-        <v>0.149</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.092</v>
+        <v>-25.593</v>
       </c>
       <c r="AN3">
-        <v>0.2196078431372549</v>
+        <v>0.001053273688491257</v>
       </c>
       <c r="AO3">
-        <v>66.30872483221478</v>
+        <v>34028.57142857143</v>
       </c>
       <c r="AP3">
-        <v>-5.701960784313726</v>
+        <v>-3.887112647417649</v>
       </c>
       <c r="AQ3">
-        <v>107.3913043478261</v>
+        <v>-9.307232446372055</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Metropolis Capital Holdings Limited (SEHK:8621)</t>
+          <t>Beijing Compass Technology Development Co., Ltd. (SZSE:300803)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,101 +852,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.138</v>
+      </c>
+      <c r="E4">
+        <v>0.123</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2449091909741332</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1419922949917446</v>
       </c>
       <c r="I4">
-        <v>0.006281676759997649</v>
+        <v>0.2575674188222344</v>
       </c>
       <c r="J4">
-        <v>0.006281676759997649</v>
+        <v>0.2282305892652618</v>
       </c>
       <c r="K4">
-        <v>1.78</v>
+        <v>45.9</v>
       </c>
       <c r="L4">
-        <v>0.2772585669781932</v>
+        <v>0.2526141992294992</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.844</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0003128591021981688</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.01838779956427015</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.844</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0003128591021981688</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.01838779956427015</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.03009971457167217</v>
+      </c>
+      <c r="W4">
+        <v>0.2333502796136248</v>
       </c>
       <c r="X4">
-        <v>0.03382558680285606</v>
+        <v>0.05006610363650001</v>
+      </c>
+      <c r="Y4">
+        <v>0.1832841759771248</v>
       </c>
       <c r="Z4">
-        <v>132.759349721109</v>
+        <v>3.135786276404805</v>
       </c>
       <c r="AA4">
-        <v>0.833951321815491</v>
+        <v>0.7156823496737897</v>
       </c>
       <c r="AB4">
-        <v>0.02897737228617554</v>
+        <v>0.05006329088771976</v>
       </c>
       <c r="AC4">
-        <v>0.8049739495293154</v>
+        <v>0.66561905878607</v>
       </c>
       <c r="AD4">
-        <v>11.5</v>
+        <v>3.24</v>
       </c>
       <c r="AE4">
-        <v>0.04835817600407548</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>11.54835817600408</v>
+        <v>3.24</v>
       </c>
       <c r="AG4">
-        <v>11.54835817600408</v>
+        <v>-77.96000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.5797846425874871</v>
+        <v>0.001199582367620162</v>
       </c>
       <c r="AI4">
-        <v>0.2627710944230338</v>
+        <v>0.01358832410669351</v>
       </c>
       <c r="AJ4">
-        <v>0.5797846425874871</v>
+        <v>-0.02975867834212556</v>
       </c>
       <c r="AK4">
-        <v>0.2627710944230338</v>
+        <v>-0.4958025947596033</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-5.662</v>
       </c>
       <c r="AN4">
-        <v>230</v>
+        <v>0.06585365853658537</v>
+      </c>
+      <c r="AO4">
+        <v>53.91705069124423</v>
       </c>
       <c r="AP4">
-        <v>230.9671635200815</v>
+        <v>-1.584552845528455</v>
+      </c>
+      <c r="AQ4">
+        <v>-8.265630519251147</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beijing Compass Technology Development Co., Ltd. (SZSE:300803)</t>
+          <t>China Art Financial Holdings Limited (SEHK:1572)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,121 +987,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0694</v>
+        <v>-0.286</v>
       </c>
       <c r="E5">
-        <v>0.0563</v>
+        <v>-0.273</v>
       </c>
       <c r="G5">
-        <v>0.1994091580502216</v>
+        <v>0.7332268370607029</v>
       </c>
       <c r="H5">
-        <v>0.08345642540620385</v>
+        <v>0.7332268370607029</v>
       </c>
       <c r="I5">
-        <v>0.1646952250790743</v>
+        <v>0.7523961661341854</v>
       </c>
       <c r="J5">
-        <v>0.1603195585825085</v>
+        <v>0.5372249260995491</v>
       </c>
       <c r="K5">
-        <v>26.4</v>
+        <v>3.83</v>
       </c>
       <c r="L5">
-        <v>0.1949778434268833</v>
+        <v>0.6118210862619808</v>
       </c>
       <c r="M5">
-        <v>3.14</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.001244698140880802</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.118939393939394</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>3.14</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.001244698140880802</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.118939393939394</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>139.1</v>
+        <v>128.2</v>
       </c>
       <c r="V5">
-        <v>0.05513933483965593</v>
+        <v>3.427807486631016</v>
       </c>
       <c r="W5">
-        <v>0.1608775137111517</v>
+        <v>0.02316999395039322</v>
       </c>
       <c r="X5">
-        <v>0.02430620127379673</v>
+        <v>0.05029974354454146</v>
       </c>
       <c r="Y5">
-        <v>0.136571312437355</v>
+        <v>-0.02712974959414824</v>
       </c>
       <c r="Z5">
-        <v>2.841771707293932</v>
+        <v>0.2526230831315577</v>
       </c>
       <c r="AA5">
-        <v>0.4555915857056246</v>
+        <v>0.1357154171663913</v>
       </c>
       <c r="AB5">
-        <v>0.02430679291201876</v>
+        <v>0.05143774545902023</v>
       </c>
       <c r="AC5">
-        <v>0.4312847927936059</v>
+        <v>0.08427767170737109</v>
       </c>
       <c r="AD5">
-        <v>0.344</v>
+        <v>1.08</v>
       </c>
       <c r="AE5">
-        <v>0.9463326214667128</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.290332621466713</v>
+        <v>1.08</v>
       </c>
       <c r="AG5">
-        <v>-137.8096673785333</v>
+        <v>-127.12</v>
       </c>
       <c r="AH5">
-        <v>0.0005112272439358147</v>
+        <v>0.02806652806652807</v>
       </c>
       <c r="AI5">
-        <v>0.006517149622318534</v>
+        <v>0.006574141709276845</v>
       </c>
       <c r="AJ5">
-        <v>-0.05778448823978131</v>
+        <v>1.416852429781543</v>
       </c>
       <c r="AK5">
-        <v>-2.34010679247376</v>
+        <v>-3.523281596452328</v>
       </c>
       <c r="AL5">
-        <v>0.014</v>
+        <v>0.033</v>
       </c>
       <c r="AM5">
-        <v>-6.156</v>
+        <v>-0.401</v>
       </c>
       <c r="AN5">
-        <v>0.01376605706510865</v>
+        <v>0.2273684210526316</v>
       </c>
       <c r="AO5">
-        <v>1557.142857142857</v>
+        <v>142.7272727272727</v>
       </c>
       <c r="AP5">
-        <v>-5.514813212955031</v>
+        <v>-26.76210526315789</v>
       </c>
       <c r="AQ5">
-        <v>-3.541260558804419</v>
+        <v>-11.74563591022444</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shanghai DZH Limited (SHSE:601519)</t>
+          <t>Panda Financial Holding Corp., Ltd. (SHSE:600599)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,115 +1118,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0156</v>
+        <v>-0.009990000000000001</v>
+      </c>
+      <c r="E6">
+        <v>0.224</v>
       </c>
       <c r="G6">
-        <v>0.3047696038803557</v>
+        <v>0.2863157894736842</v>
       </c>
       <c r="H6">
-        <v>0.08407437348423606</v>
+        <v>0.2863157894736842</v>
       </c>
       <c r="I6">
-        <v>0.05223541370818324</v>
+        <v>0.2610526315789474</v>
       </c>
       <c r="J6">
-        <v>0.04350024788639462</v>
+        <v>0.202226387887527</v>
       </c>
       <c r="K6">
-        <v>9.859999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="L6">
-        <v>0.07970897332255455</v>
+        <v>0.2378947368421053</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.002999702999703</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.08938053097345132</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1.01</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.002999702999703</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.08938053097345132</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>195.5</v>
+        <v>21.2</v>
       </c>
       <c r="V6">
-        <v>0.08308189197229188</v>
+        <v>0.06296406296406297</v>
       </c>
       <c r="W6">
-        <v>0.04539594843462247</v>
+        <v>0.105904404873477</v>
       </c>
       <c r="X6">
-        <v>0.02435012176260015</v>
+        <v>0.05037438774727347</v>
       </c>
       <c r="Y6">
-        <v>0.02104582667202232</v>
+        <v>0.05553001712620358</v>
       </c>
       <c r="Z6">
-        <v>9.178330465007624</v>
+        <v>0.6152849740932642</v>
       </c>
       <c r="AA6">
-        <v>0.3992596504110792</v>
+        <v>0.1244268578323515</v>
       </c>
       <c r="AB6">
-        <v>0.02435772383638657</v>
+        <v>0.05027795434745962</v>
       </c>
       <c r="AC6">
-        <v>0.3749019265746927</v>
+        <v>0.07414890348489184</v>
       </c>
       <c r="AD6">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="AE6">
-        <v>0.5773966214886612</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>16.17739662148866</v>
+        <v>12.7</v>
       </c>
       <c r="AG6">
-        <v>-179.3226033785113</v>
+        <v>-8.5</v>
       </c>
       <c r="AH6">
-        <v>0.006827987573155045</v>
+        <v>0.0363480251860332</v>
       </c>
       <c r="AI6">
-        <v>0.06295260530371447</v>
+        <v>0.1052195526097763</v>
       </c>
       <c r="AJ6">
-        <v>-0.08249354494955036</v>
+        <v>-0.0258988421694089</v>
       </c>
       <c r="AK6">
-        <v>-2.916886745913884</v>
+        <v>-0.08542713567839195</v>
       </c>
       <c r="AL6">
-        <v>0.5580000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="AM6">
-        <v>-5.002</v>
+        <v>-0.3739999999999999</v>
       </c>
       <c r="AN6">
-        <v>1.672563525249276</v>
+        <v>1.016</v>
       </c>
       <c r="AO6">
-        <v>10.7168458781362</v>
+        <v>15.38461538461538</v>
       </c>
       <c r="AP6">
-        <v>-19.22618241433594</v>
+        <v>-0.68</v>
       </c>
       <c r="AQ6">
-        <v>-1.195521791283487</v>
+        <v>-33.15508021390375</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1243,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bairong Inc. (SEHK:6608)</t>
+          <t>SY Holdings Group Limited (SEHK:6069)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1224,116 +1251,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.382</v>
+      </c>
+      <c r="E7">
+        <v>0.6629999999999999</v>
+      </c>
       <c r="G7">
-        <v>0.1640604175921813</v>
+        <v>0.5577350859453993</v>
       </c>
       <c r="H7">
-        <v>0.01657041314971124</v>
+        <v>0.5237613751263902</v>
       </c>
       <c r="I7">
-        <v>0.0964015992892048</v>
+        <v>0.614762386248736</v>
       </c>
       <c r="J7">
-        <v>0.0964015992892048</v>
+        <v>0.5763620111076918</v>
       </c>
       <c r="K7">
-        <v>-567.6</v>
+        <v>62.5</v>
       </c>
       <c r="L7">
-        <v>-2.521545979564638</v>
+        <v>0.6319514661274014</v>
       </c>
       <c r="M7">
-        <v>6.15</v>
+        <v>10.0893</v>
       </c>
       <c r="N7">
-        <v>0.009651600753295669</v>
+        <v>0.01245131432802666</v>
       </c>
       <c r="O7">
-        <v>-0.01083509513742072</v>
+        <v>0.1614288</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>9.0693</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.0111925212884117</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.1451088</v>
       </c>
       <c r="S7">
-        <v>6.15</v>
+        <v>1.02</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.1010972019862626</v>
       </c>
       <c r="U7">
-        <v>430.7</v>
+        <v>143.1</v>
       </c>
       <c r="V7">
-        <v>0.6759259259259258</v>
+        <v>0.1766012587930396</v>
       </c>
       <c r="W7">
-        <v>3.346698113207547</v>
+        <v>0.1323872061004024</v>
       </c>
       <c r="X7">
-        <v>0.02451172411940674</v>
+        <v>0.05756862299469619</v>
       </c>
       <c r="Y7">
-        <v>3.322186389088141</v>
+        <v>0.07481858310570624</v>
       </c>
       <c r="Z7">
-        <v>1.524035206499661</v>
+        <v>0.1314460393407762</v>
       </c>
       <c r="AA7">
-        <v>0.1469194312796208</v>
+        <v>0.07576050358659055</v>
       </c>
       <c r="AB7">
-        <v>0.02460688087821932</v>
+        <v>0.05293176601415059</v>
       </c>
       <c r="AC7">
-        <v>0.1223125504014015</v>
+        <v>0.02282873757243996</v>
       </c>
       <c r="AD7">
-        <v>19.3</v>
+        <v>721.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>19.3</v>
+        <v>721.1</v>
       </c>
       <c r="AG7">
-        <v>-411.4</v>
+        <v>578</v>
       </c>
       <c r="AH7">
-        <v>0.0293983244478294</v>
+        <v>0.4708763223194463</v>
       </c>
       <c r="AI7">
-        <v>0.02896158463385354</v>
+        <v>0.5427517687791661</v>
       </c>
       <c r="AJ7">
-        <v>-1.821966341895482</v>
+        <v>0.4163365266873154</v>
       </c>
       <c r="AK7">
-        <v>-1.745439117522274</v>
+        <v>0.4875579924082665</v>
       </c>
       <c r="AL7">
-        <v>1.53</v>
+        <v>29.5</v>
       </c>
       <c r="AM7">
-        <v>-4</v>
+        <v>27.77</v>
       </c>
       <c r="AN7">
-        <v>0.7813765182186235</v>
+        <v>11.70616883116883</v>
       </c>
       <c r="AO7">
-        <v>14.18300653594771</v>
+        <v>2.061016949152542</v>
       </c>
       <c r="AP7">
-        <v>-16.65587044534413</v>
+        <v>9.383116883116882</v>
       </c>
       <c r="AQ7">
-        <v>-5.425</v>
+        <v>2.189413035649982</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Panda Financial Holding Corp., Ltd. (SHSE:600599)</t>
+          <t>China Huirong Financial Holdings Limited (SEHK:1290)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,46 +1386,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0492</v>
+        <v>0.19</v>
       </c>
       <c r="E8">
-        <v>0.473</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G8">
-        <v>0.2019047619047619</v>
+        <v>0.2854209445585216</v>
       </c>
       <c r="H8">
-        <v>0.2019047619047619</v>
+        <v>0.2854209445585216</v>
       </c>
       <c r="I8">
-        <v>0.3476190476190476</v>
+        <v>0.2720739219712526</v>
       </c>
       <c r="J8">
-        <v>0.2928287606433302</v>
+        <v>0.1896127509068377</v>
       </c>
       <c r="K8">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="L8">
-        <v>0.3047619047619048</v>
+        <v>0.1386036960985626</v>
       </c>
       <c r="M8">
-        <v>1.15</v>
+        <v>5.57</v>
       </c>
       <c r="N8">
-        <v>0.005346350534635053</v>
+        <v>0.04194277108433735</v>
       </c>
       <c r="O8">
-        <v>0.08984374999999999</v>
+        <v>0.4125925925925926</v>
       </c>
       <c r="P8">
-        <v>1.15</v>
+        <v>5.57</v>
       </c>
       <c r="Q8">
-        <v>0.005346350534635053</v>
+        <v>0.04194277108433735</v>
       </c>
       <c r="R8">
-        <v>0.08984374999999999</v>
+        <v>0.4125925925925926</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1401,73 +1434,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>43.7</v>
+        <v>55.9</v>
       </c>
       <c r="V8">
-        <v>0.203161320316132</v>
+        <v>0.420933734939759</v>
       </c>
       <c r="W8">
-        <v>0.1434977578475336</v>
+        <v>0.04856115107913669</v>
       </c>
       <c r="X8">
-        <v>0.02475831228749538</v>
+        <v>0.05622216513542601</v>
       </c>
       <c r="Y8">
-        <v>0.1187394455600383</v>
+        <v>-0.007661014056289314</v>
       </c>
       <c r="Z8">
-        <v>0.4194966040751099</v>
+        <v>0.3051378446115289</v>
       </c>
       <c r="AA8">
-        <v>0.1228406706654002</v>
+        <v>0.05785802612257516</v>
       </c>
       <c r="AB8">
-        <v>0.02494348949935941</v>
+        <v>0.05019624702646572</v>
       </c>
       <c r="AC8">
-        <v>0.09789718116604076</v>
+        <v>0.00766177909610944</v>
       </c>
       <c r="AD8">
-        <v>14.2</v>
+        <v>97</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>14.2</v>
+        <v>97</v>
       </c>
       <c r="AG8">
-        <v>-29.5</v>
+        <v>41.1</v>
       </c>
       <c r="AH8">
-        <v>0.06192760575665068</v>
+        <v>0.4221061792863359</v>
       </c>
       <c r="AI8">
-        <v>0.1166803615447822</v>
+        <v>0.2384464110127827</v>
       </c>
       <c r="AJ8">
-        <v>-0.1589439655172414</v>
+        <v>0.2363427257044278</v>
       </c>
       <c r="AK8">
-        <v>-0.3782051282051282</v>
+        <v>0.1171273867198632</v>
       </c>
       <c r="AL8">
-        <v>1.18</v>
+        <v>4.1</v>
       </c>
       <c r="AM8">
-        <v>-0.1100000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AN8">
-        <v>0.9726027397260274</v>
+        <v>3.646616541353383</v>
       </c>
       <c r="AO8">
-        <v>12.3728813559322</v>
+        <v>6.463414634146342</v>
       </c>
       <c r="AP8">
-        <v>-2.02054794520548</v>
+        <v>1.545112781954887</v>
       </c>
       <c r="AQ8">
-        <v>-132.7272727272726</v>
+        <v>6.463414634146342</v>
       </c>
     </row>
     <row r="9">
@@ -1478,7 +1511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Art Financial Holdings Limited (SEHK:1572)</t>
+          <t>SPIC Industry-Finance Holdings Co., Ltd. (SZSE:000958)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1487,118 +1520,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.187</v>
+        <v>0.168</v>
       </c>
       <c r="E9">
-        <v>-0.0849</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G9">
-        <v>0.8589263420724095</v>
+        <v>0.5444230986552153</v>
       </c>
       <c r="H9">
-        <v>0.8589263420724095</v>
+        <v>0.5427731947112668</v>
       </c>
       <c r="I9">
-        <v>0.7578027465667916</v>
+        <v>0.2940445248050627</v>
       </c>
       <c r="J9">
-        <v>0.5831384549800555</v>
+        <v>0.2513060909104265</v>
       </c>
       <c r="K9">
-        <v>6.31</v>
+        <v>193.6</v>
       </c>
       <c r="L9">
-        <v>0.7877652933832708</v>
+        <v>0.2187817832523449</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>611.1</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.1755479589784838</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>3.15650826446281</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>181.1</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.05202378558501623</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.9354338842975206</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>430</v>
+      </c>
+      <c r="T9">
+        <v>0.7036491572574046</v>
       </c>
       <c r="U9">
-        <v>141.4</v>
+        <v>351.7</v>
       </c>
       <c r="V9">
-        <v>2.344941956882256</v>
+        <v>0.1010312832150757</v>
       </c>
       <c r="W9">
-        <v>0.04333791208791209</v>
+        <v>0.07090276506134408</v>
       </c>
       <c r="X9">
-        <v>0.02440339672890872</v>
+        <v>0.0546740595110899</v>
       </c>
       <c r="Y9">
-        <v>0.01893451535900337</v>
+        <v>0.01622870555025417</v>
       </c>
       <c r="Z9">
-        <v>0.2068644921360502</v>
+        <v>0.2087274442740889</v>
       </c>
       <c r="AA9">
-        <v>0.1206306403344501</v>
+        <v>0.05245447808624518</v>
       </c>
       <c r="AB9">
-        <v>0.02445151245224056</v>
+        <v>0.05221554532758464</v>
       </c>
       <c r="AC9">
-        <v>0.09617912788220957</v>
+        <v>0.0002389327586605414</v>
       </c>
       <c r="AD9">
-        <v>0.88</v>
+        <v>1904.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.88</v>
+        <v>1904.3</v>
       </c>
       <c r="AG9">
-        <v>-140.52</v>
+        <v>1552.6</v>
       </c>
       <c r="AH9">
-        <v>0.01438378555083361</v>
+        <v>0.3536041891038735</v>
       </c>
       <c r="AI9">
-        <v>0.005295462751233602</v>
+        <v>0.3372651116660468</v>
       </c>
       <c r="AJ9">
-        <v>1.75168287210172</v>
+        <v>0.3084411069392296</v>
       </c>
       <c r="AK9">
-        <v>-5.670702179176756</v>
+        <v>0.2932421712688399</v>
       </c>
       <c r="AL9">
-        <v>0.025</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AM9">
-        <v>-0.4</v>
+        <v>-65.59999999999999</v>
       </c>
       <c r="AN9">
-        <v>0.1444991789819376</v>
+        <v>5.039163799947076</v>
       </c>
       <c r="AO9">
-        <v>242.8</v>
+        <v>2.736067297581493</v>
       </c>
       <c r="AP9">
-        <v>-23.07389162561577</v>
+        <v>4.108494310664197</v>
       </c>
       <c r="AQ9">
-        <v>-15.175</v>
+        <v>-3.966463414634147</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1645,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sheng Ye Capital Limited (SEHK:6069)</t>
+          <t>Bairong Inc. (SEHK:6608)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1618,115 +1654,115 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.746031746031746</v>
+        <v>0.2691292875989446</v>
       </c>
       <c r="H10">
-        <v>0.6994708994708995</v>
+        <v>0.10139464756879</v>
       </c>
       <c r="I10">
-        <v>0.6634920634920636</v>
+        <v>0.0336600075386355</v>
       </c>
       <c r="J10">
-        <v>0.5910895306244145</v>
+        <v>0.0336600075386355</v>
       </c>
       <c r="K10">
-        <v>48.1</v>
+        <v>20.6</v>
       </c>
       <c r="L10">
-        <v>0.508994708994709</v>
+        <v>0.07764794572182435</v>
       </c>
       <c r="M10">
-        <v>7.5</v>
+        <v>25.2</v>
       </c>
       <c r="N10">
-        <v>0.007517289766462864</v>
+        <v>0.03819339193695059</v>
       </c>
       <c r="O10">
-        <v>0.1559251559251559</v>
+        <v>1.223300970873786</v>
       </c>
       <c r="P10">
-        <v>7.5</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.007517289766462864</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1559251559251559</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>46.7</v>
+        <v>174.5</v>
       </c>
       <c r="V10">
-        <v>0.04680765761250877</v>
+        <v>0.2644740830554714</v>
       </c>
       <c r="W10">
-        <v>0.1398255813953488</v>
+        <v>0.03199254542630844</v>
       </c>
       <c r="X10">
-        <v>0.02656482899745998</v>
+        <v>0.05026963689118975</v>
       </c>
       <c r="Y10">
-        <v>0.1132607523978889</v>
+        <v>-0.01827709146488132</v>
       </c>
       <c r="Z10">
-        <v>0.1617873651771957</v>
+        <v>1.167539497425516</v>
       </c>
       <c r="AA10">
-        <v>0.09563081774354933</v>
+        <v>0.03929938828499759</v>
       </c>
       <c r="AB10">
-        <v>0.02543803913970059</v>
+        <v>0.05020672969165312</v>
       </c>
       <c r="AC10">
-        <v>0.07019277860384873</v>
+        <v>-0.01090734140665552</v>
       </c>
       <c r="AD10">
-        <v>327</v>
+        <v>16.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>327</v>
+        <v>16.7</v>
       </c>
       <c r="AG10">
-        <v>280.3</v>
+        <v>-157.8</v>
       </c>
       <c r="AH10">
-        <v>0.2468483430210614</v>
+        <v>0.02468588322246859</v>
       </c>
       <c r="AI10">
-        <v>0.4018186286556894</v>
+        <v>0.02585539557206997</v>
       </c>
       <c r="AJ10">
-        <v>0.2193270735524257</v>
+        <v>-0.3143426294820718</v>
       </c>
       <c r="AK10">
-        <v>0.3654021639942641</v>
+        <v>-0.3347475604582096</v>
       </c>
       <c r="AL10">
-        <v>17.5</v>
+        <v>1.54</v>
       </c>
       <c r="AM10">
-        <v>16.917</v>
+        <v>-7.329999999999999</v>
       </c>
       <c r="AN10">
-        <v>5.157728706624606</v>
+        <v>1.325396825396825</v>
       </c>
       <c r="AO10">
-        <v>3.582857142857143</v>
+        <v>5.798701298701299</v>
       </c>
       <c r="AP10">
-        <v>4.421135646687698</v>
+        <v>-12.52380952380953</v>
       </c>
       <c r="AQ10">
-        <v>3.706330909735768</v>
+        <v>-1.218281036834925</v>
       </c>
     </row>
     <row r="11">
@@ -1746,121 +1782,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.278</v>
+        <v>0.103</v>
       </c>
       <c r="E11">
-        <v>0.203</v>
+        <v>-0.0223</v>
       </c>
       <c r="G11">
-        <v>0.4866235167206041</v>
+        <v>0.6640295358649789</v>
       </c>
       <c r="H11">
-        <v>0.4858414239482201</v>
+        <v>0.6618143459915612</v>
       </c>
       <c r="I11">
-        <v>0.4199900405348692</v>
+        <v>0.3662447257383966</v>
       </c>
       <c r="J11">
-        <v>0.302661159809187</v>
+        <v>0.262814502265979</v>
       </c>
       <c r="K11">
-        <v>230.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="L11">
-        <v>0.3102750809061489</v>
+        <v>0.1964135021097046</v>
       </c>
       <c r="M11">
-        <v>153.7</v>
+        <v>137.44</v>
       </c>
       <c r="N11">
-        <v>0.08958964793658195</v>
+        <v>0.1065178640626211</v>
       </c>
       <c r="O11">
-        <v>0.6679704476314645</v>
+        <v>1.476262083780881</v>
       </c>
       <c r="P11">
-        <v>153.7</v>
+        <v>128.2</v>
       </c>
       <c r="Q11">
-        <v>0.08958964793658195</v>
+        <v>0.099356738742928</v>
       </c>
       <c r="R11">
-        <v>0.6679704476314645</v>
+        <v>1.377013963480129</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>9.240000000000009</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.06722933643771835</v>
       </c>
       <c r="U11">
-        <v>249.4</v>
+        <v>242</v>
       </c>
       <c r="V11">
-        <v>0.1453718815574726</v>
+        <v>0.1875532821824382</v>
       </c>
       <c r="W11">
-        <v>0.1370948522402288</v>
+        <v>0.04843408594319009</v>
       </c>
       <c r="X11">
-        <v>0.03275809535498396</v>
+        <v>0.06084151316364127</v>
       </c>
       <c r="Y11">
-        <v>0.1043367568852448</v>
+        <v>-0.01240742722045118</v>
       </c>
       <c r="Z11">
-        <v>0.226888424178242</v>
+        <v>0.1260554484409281</v>
       </c>
       <c r="AA11">
-        <v>0.0686703136090655</v>
+        <v>0.03312919993991732</v>
       </c>
       <c r="AB11">
-        <v>0.02683501921809187</v>
+        <v>0.05024238801339388</v>
       </c>
       <c r="AC11">
-        <v>0.04183529439097364</v>
+        <v>-0.01711318807347656</v>
       </c>
       <c r="AD11">
-        <v>2095</v>
+        <v>1648.5</v>
       </c>
       <c r="AE11">
-        <v>6.726929696704918</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2101.726929696705</v>
+        <v>1648.5</v>
       </c>
       <c r="AG11">
-        <v>1852.326929696705</v>
+        <v>1406.5</v>
       </c>
       <c r="AH11">
-        <v>0.5505755646304289</v>
+        <v>0.5609432421396489</v>
       </c>
       <c r="AI11">
-        <v>0.5221906348790711</v>
+        <v>0.4768171694675035</v>
       </c>
       <c r="AJ11">
-        <v>0.5191605563105418</v>
+        <v>0.5215440522100266</v>
       </c>
       <c r="AK11">
-        <v>0.4906271434169988</v>
+        <v>0.4374397412372096</v>
       </c>
       <c r="AL11">
-        <v>51.3</v>
+        <v>38</v>
       </c>
       <c r="AM11">
-        <v>47.47</v>
+        <v>32.83</v>
       </c>
       <c r="AN11">
-        <v>5.863255996193781</v>
+        <v>7.864980916030534</v>
       </c>
       <c r="AO11">
-        <v>6.025341130604289</v>
+        <v>4.568421052631579</v>
       </c>
       <c r="AP11">
-        <v>5.184089249382062</v>
+        <v>6.710400763358779</v>
       </c>
       <c r="AQ11">
-        <v>6.511480935327576</v>
+        <v>5.287846481876333</v>
       </c>
     </row>
     <row r="12">
@@ -1871,7 +1907,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>China Huirong Financial Holdings Limited (SEHK:1290)</t>
+          <t>Minsheng Holdings Co.,Ltd (SZSE:000416)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1880,46 +1916,43 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0259</v>
-      </c>
-      <c r="E12">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="G12">
-        <v>0.2773722627737226</v>
+        <v>0.5584</v>
       </c>
       <c r="H12">
-        <v>0.2773722627737226</v>
+        <v>0.5584</v>
       </c>
       <c r="I12">
-        <v>0.389294403892944</v>
+        <v>0.2224</v>
       </c>
       <c r="J12">
-        <v>0.2441528486843031</v>
+        <v>0.1112</v>
       </c>
       <c r="K12">
-        <v>2.49</v>
+        <v>-0.326</v>
       </c>
       <c r="L12">
-        <v>0.06058394160583942</v>
+        <v>-0.05216</v>
       </c>
       <c r="M12">
-        <v>0.135</v>
+        <v>1.74</v>
       </c>
       <c r="N12">
-        <v>0.0009560906515580738</v>
+        <v>0.005876393110435663</v>
       </c>
       <c r="O12">
-        <v>0.05421686746987952</v>
+        <v>-5.337423312883435</v>
       </c>
       <c r="P12">
-        <v>0.135</v>
+        <v>1.74</v>
       </c>
       <c r="Q12">
-        <v>0.0009560906515580738</v>
+        <v>0.005876393110435663</v>
       </c>
       <c r="R12">
-        <v>0.05421686746987952</v>
+        <v>-5.337423312883435</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1928,73 +1961,70 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>64.7</v>
+        <v>6.13</v>
       </c>
       <c r="V12">
-        <v>0.458215297450425</v>
+        <v>0.02070246538331644</v>
       </c>
       <c r="W12">
-        <v>0.009884874950377135</v>
+        <v>-0.0023589001447178</v>
       </c>
       <c r="X12">
-        <v>0.02947917340144141</v>
+        <v>0.05011298572882499</v>
       </c>
       <c r="Y12">
-        <v>-0.01959429845106428</v>
+        <v>-0.05247188587354279</v>
       </c>
       <c r="Z12">
-        <v>0.1609870740305523</v>
+        <v>0.04638563158675968</v>
       </c>
       <c r="AA12">
-        <v>0.03930545272591013</v>
+        <v>0.005158082232447676</v>
       </c>
       <c r="AB12">
-        <v>0.02627386652768545</v>
+        <v>0.05009693973450365</v>
       </c>
       <c r="AC12">
-        <v>0.01303158619822468</v>
+        <v>-0.04493885750205597</v>
       </c>
       <c r="AD12">
-        <v>105.9</v>
+        <v>2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>105.9</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>41.2</v>
+        <v>-4.13</v>
       </c>
       <c r="AH12">
-        <v>0.4285714285714286</v>
+        <v>0.006709158000670915</v>
       </c>
       <c r="AI12">
-        <v>0.2597498160412067</v>
+        <v>0.015527950310559</v>
       </c>
       <c r="AJ12">
-        <v>0.2258771929824562</v>
+        <v>-0.01414528889954447</v>
       </c>
       <c r="AK12">
-        <v>0.1201166180758018</v>
+        <v>-0.03366756338142985</v>
       </c>
       <c r="AL12">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.12</v>
+        <v>-1.87</v>
       </c>
       <c r="AN12">
-        <v>6.61875</v>
-      </c>
-      <c r="AO12">
-        <v>3.883495145631068</v>
+        <v>1.092896174863388</v>
       </c>
       <c r="AP12">
-        <v>2.575</v>
+        <v>-2.256830601092896</v>
       </c>
       <c r="AQ12">
-        <v>3.883495145631068</v>
+        <v>-0.7433155080213902</v>
       </c>
     </row>
     <row r="13">
@@ -2005,7 +2035,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oceanwide Holdings Co., Ltd. (SZSE:000046)</t>
+          <t>Metropolis Capital Holdings Limited (SEHK:8621)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2013,119 +2043,107 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>-0.07580000000000001</v>
-      </c>
       <c r="G13">
-        <v>0.1394077789840153</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.1394077789840153</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0.1337746318077198</v>
+        <v>0.09212346417184436</v>
       </c>
       <c r="J13">
-        <v>0.1337746318077198</v>
+        <v>0.09212346417184436</v>
       </c>
       <c r="K13">
-        <v>-900.2</v>
+        <v>-0.333</v>
       </c>
       <c r="L13">
-        <v>-0.3369894807771497</v>
+        <v>-0.1534562211981567</v>
       </c>
       <c r="M13">
-        <v>654.3</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.425477955520874</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>-0.7268384803377026</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>654.3</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.425477955520874</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>-0.7268384803377026</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>677.4</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.4404994147483418</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>-0.2988811049503636</v>
+        <v>-0.01030959752321981</v>
       </c>
       <c r="X13">
-        <v>0.07012455397907072</v>
+        <v>0.05068763368966726</v>
       </c>
       <c r="Y13">
-        <v>-0.3690056589294343</v>
+        <v>-0.06099723121288708</v>
       </c>
       <c r="Z13">
-        <v>0.1908284184502753</v>
+        <v>0.05274612821969066</v>
       </c>
       <c r="AA13">
-        <v>0.02552800141663506</v>
+        <v>0.004859156053250182</v>
       </c>
       <c r="AB13">
-        <v>0.02830001948099958</v>
+        <v>0.05067953713219175</v>
       </c>
       <c r="AC13">
-        <v>-0.002772018064364515</v>
+        <v>-0.04582038107894157</v>
       </c>
       <c r="AD13">
-        <v>10031.6</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>177.7391302601908</v>
+        <v>0.2304604137354888</v>
       </c>
       <c r="AF13">
-        <v>10209.33913026019</v>
+        <v>0.2304604137354888</v>
       </c>
       <c r="AG13">
-        <v>9531.939130260191</v>
+        <v>0.2304604137354888</v>
       </c>
       <c r="AH13">
-        <v>0.8690915308869813</v>
+        <v>0.06961581923145235</v>
       </c>
       <c r="AI13">
-        <v>0.7247276424160384</v>
+        <v>1</v>
       </c>
       <c r="AJ13">
-        <v>0.8610807371425514</v>
+        <v>0.06961581923145235</v>
       </c>
       <c r="AK13">
-        <v>0.71082211500674</v>
+        <v>1</v>
       </c>
       <c r="AL13">
-        <v>774.4</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>774.4</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>24.92942345924454</v>
-      </c>
-      <c r="AO13">
-        <v>0.4238119834710744</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>23.68772149667046</v>
-      </c>
-      <c r="AQ13">
-        <v>0.4238119834710744</v>
+        <v>0.9368309501442633</v>
       </c>
     </row>
     <row r="14">
@@ -2136,7 +2154,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minsheng Holdings Co.,Ltd (SZSE:000416)</t>
+          <t>Baiying Holdings Group Limited (SEHK:8525)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2144,122 +2162,95 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.313</v>
-      </c>
-      <c r="E14">
-        <v>-0.201</v>
-      </c>
       <c r="G14">
-        <v>0.6238317757009345</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.6238317757009345</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0.1214953271028037</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.09535970441208434</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>2.49</v>
+        <v>-2.9</v>
       </c>
       <c r="L14">
-        <v>0.2908878504672897</v>
+        <v>-0.8605341246290801</v>
       </c>
       <c r="M14">
-        <v>2.48</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.007517429524098212</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.9959839357429718</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.48</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.007517429524098212</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.9959839357429718</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.01679296756592907</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>0.01893536121673004</v>
+        <v>-0.0651685393258427</v>
       </c>
       <c r="X14">
-        <v>0.02434618769933536</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="Y14">
-        <v>-0.005410826482605317</v>
+        <v>-0.1152245039572442</v>
       </c>
       <c r="Z14">
-        <v>0.07035423687022274</v>
+        <v>0.07269197584124246</v>
       </c>
       <c r="AA14">
-        <v>0.006708959232082205</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02433148858362482</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="AC14">
-        <v>-0.01762252935154262</v>
+        <v>-0.05005596463140148</v>
       </c>
       <c r="AD14">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>-3.46</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>0.006265437676968493</v>
-      </c>
-      <c r="AI14">
-        <v>0.01440642748303089</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.01059919127557897</v>
-      </c>
-      <c r="AK14">
-        <v>-0.02492077211178335</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>-3.013</v>
-      </c>
-      <c r="AN14">
-        <v>1.368421052631579</v>
-      </c>
-      <c r="AO14">
-        <v>13.50649350649351</v>
-      </c>
-      <c r="AP14">
-        <v>-2.276315789473684</v>
-      </c>
-      <c r="AQ14">
-        <v>-0.345170925987388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2278,98 +2269,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="K15">
-        <v>5.81</v>
-      </c>
-      <c r="L15">
-        <v>0.641988950276243</v>
+        <v>-1.96</v>
       </c>
       <c r="M15">
-        <v>2.31</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.01547220361687877</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.3975903614457832</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.31</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.01547220361687877</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.3975903614457832</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>0.102</v>
+        <v>0.079</v>
       </c>
       <c r="V15">
-        <v>0.0006831882116543871</v>
+        <v>0.0004796599878567092</v>
       </c>
       <c r="W15">
-        <v>0.04689265536723163</v>
+        <v>-0.01409058231488138</v>
       </c>
       <c r="X15">
-        <v>0.02431792657683401</v>
+        <v>0.05006647224865757</v>
       </c>
       <c r="Y15">
-        <v>0.02257472879039762</v>
+        <v>-0.06415705456353894</v>
       </c>
       <c r="Z15">
-        <v>0.07293857846337355</v>
+        <v>0</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02432549257384481</v>
+        <v>0.05006709985785952</v>
       </c>
       <c r="AC15">
-        <v>-0.02432549257384481</v>
+        <v>-0.05006709985785952</v>
       </c>
       <c r="AD15">
-        <v>0.33</v>
+        <v>0.205</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.33</v>
+        <v>0.205</v>
       </c>
       <c r="AG15">
-        <v>0.228</v>
+        <v>0.126</v>
       </c>
       <c r="AH15">
-        <v>0.002205440085544342</v>
+        <v>0.001243139989691034</v>
       </c>
       <c r="AI15">
-        <v>0.002366779028903393</v>
+        <v>0.001549450134159707</v>
       </c>
       <c r="AJ15">
-        <v>0.001524798031137981</v>
+        <v>0.0007644425030031671</v>
       </c>
       <c r="AK15">
-        <v>0.001636426274689941</v>
+        <v>0.0009529139503577209</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2386,7 +2359,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quanzhou Huixin Micro-Credit Co., Ltd. (SEHK:1577)</t>
+          <t>Jiangsu Financial Leasing Co., Ltd. (SHSE:600901)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2407,28 +2380,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>10.4</v>
+        <v>326.3</v>
       </c>
       <c r="L16">
-        <v>0.5810055865921788</v>
+        <v>0.6462665874430581</v>
       </c>
       <c r="M16">
-        <v>5.27</v>
+        <v>188.6</v>
       </c>
       <c r="N16">
-        <v>0.05212660731948566</v>
+        <v>0.07947075678408899</v>
       </c>
       <c r="O16">
-        <v>0.5067307692307692</v>
+        <v>0.577995709469813</v>
       </c>
       <c r="P16">
-        <v>5.27</v>
+        <v>188.6</v>
       </c>
       <c r="Q16">
-        <v>0.05212660731948566</v>
+        <v>0.07947075678408899</v>
       </c>
       <c r="R16">
-        <v>0.5067307692307692</v>
+        <v>0.577995709469813</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2437,55 +2410,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>14.9</v>
+        <v>312.7</v>
       </c>
       <c r="V16">
-        <v>0.1473788328387735</v>
+        <v>0.1317630203944042</v>
       </c>
       <c r="W16">
-        <v>0.06979865771812081</v>
+        <v>0.1533725029377203</v>
       </c>
       <c r="X16">
-        <v>0.02451703586466387</v>
+        <v>0.09171126278268701</v>
       </c>
       <c r="Y16">
-        <v>0.04528162185345694</v>
+        <v>0.06166124015503333</v>
       </c>
       <c r="Z16">
-        <v>0.121142393069843</v>
+        <v>0.03935123844559101</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02444121944905659</v>
+        <v>0.05033230073859365</v>
       </c>
       <c r="AC16">
-        <v>-0.02444121944905659</v>
+        <v>-0.05033230073859365</v>
       </c>
       <c r="AD16">
-        <v>3.14</v>
+        <v>11710.1</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>3.14</v>
+        <v>11710.1</v>
       </c>
       <c r="AG16">
-        <v>-11.76</v>
+        <v>11397.4</v>
       </c>
       <c r="AH16">
-        <v>0.03012279355333845</v>
+        <v>0.8314883585523281</v>
       </c>
       <c r="AI16">
-        <v>0.01609926168990976</v>
+        <v>0.8441232654532348</v>
       </c>
       <c r="AJ16">
-        <v>-0.1316319677635998</v>
+        <v>0.8276618302760955</v>
       </c>
       <c r="AK16">
-        <v>-0.06528255801043632</v>
+        <v>0.8405286213660969</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2502,7 +2475,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Differ Group Holding Company Limited (SEHK:6878)</t>
+          <t>AVIC Industry-Finance Holdings Co., Ltd. (SHSE:600705)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2511,13 +2484,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.774</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E17">
-        <v>0.27</v>
+        <v>0.0538</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.007565550834283345</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2529,28 +2502,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>59.2</v>
+        <v>477.7</v>
       </c>
       <c r="L17">
-        <v>0.1055823078294988</v>
+        <v>0.2475386050367914</v>
       </c>
       <c r="M17">
-        <v>4.74</v>
+        <v>1729.8</v>
       </c>
       <c r="N17">
-        <v>0.002092900035323207</v>
+        <v>0.4119061793070604</v>
       </c>
       <c r="O17">
-        <v>0.08006756756756757</v>
+        <v>3.621101109482939</v>
       </c>
       <c r="P17">
-        <v>4.74</v>
+        <v>1729.8</v>
       </c>
       <c r="Q17">
-        <v>0.002092900035323207</v>
+        <v>0.4119061793070604</v>
       </c>
       <c r="R17">
-        <v>0.08006756756756757</v>
+        <v>3.621101109482939</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2559,61 +2532,64 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>19</v>
+        <v>7497.4</v>
       </c>
       <c r="V17">
-        <v>0.008389261744966443</v>
+        <v>1.785307774735087</v>
       </c>
       <c r="W17">
-        <v>0.2462562396006656</v>
+        <v>0.07380911914216405</v>
       </c>
       <c r="X17">
-        <v>0.02486310827579748</v>
+        <v>0.09427425578709009</v>
       </c>
       <c r="Y17">
-        <v>0.2213931313248681</v>
+        <v>-0.02046513664492604</v>
       </c>
       <c r="Z17">
-        <v>1.204588910133843</v>
+        <v>0.07379862131417991</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.02490819769037764</v>
+        <v>0.05033502642416218</v>
       </c>
       <c r="AC17">
-        <v>-0.02490819769037764</v>
+        <v>-0.05033502642416218</v>
       </c>
       <c r="AD17">
-        <v>183.9</v>
+        <v>21996.6</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>183.9</v>
+        <v>21996.6</v>
       </c>
       <c r="AG17">
-        <v>164.9</v>
+        <v>14499.2</v>
       </c>
       <c r="AH17">
-        <v>0.07510107403928615</v>
+        <v>0.8396898775008493</v>
       </c>
       <c r="AI17">
-        <v>0.3328506787330317</v>
+        <v>0.6878881696219157</v>
       </c>
       <c r="AJ17">
-        <v>0.06786846112688809</v>
+        <v>0.7754121944306289</v>
       </c>
       <c r="AK17">
-        <v>0.3090909090909091</v>
+        <v>0.5922972597591464</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>-456.7</v>
+      </c>
+      <c r="AQ17">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2624,7 +2600,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guangdong Join-Share Financing Guarantee Investment Co., Ltd. (SEHK:1543)</t>
+          <t>Genertec Universal Medical Group Company Limited (SEHK:2666)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2633,13 +2609,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0178</v>
+        <v>0.271</v>
       </c>
       <c r="E18">
-        <v>-0.0133</v>
+        <v>0.134</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.002398907814328436</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2651,28 +2627,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>15.3</v>
+        <v>296.7</v>
       </c>
       <c r="L18">
-        <v>0.3072289156626506</v>
+        <v>0.1928877909244572</v>
       </c>
       <c r="M18">
-        <v>15.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N18">
-        <v>0.04203013481363996</v>
+        <v>0.07513696843203757</v>
       </c>
       <c r="O18">
-        <v>1.03921568627451</v>
+        <v>0.2912032355915066</v>
       </c>
       <c r="P18">
-        <v>15.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>0.04203013481363996</v>
+        <v>0.07513696843203757</v>
       </c>
       <c r="R18">
-        <v>1.03921568627451</v>
+        <v>0.2912032355915066</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2681,55 +2657,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>100.8</v>
+        <v>549.3</v>
       </c>
       <c r="V18">
-        <v>0.2664551942902458</v>
+        <v>0.4776937124967388</v>
       </c>
       <c r="W18">
-        <v>0.05264969029593943</v>
+        <v>0.1316793893129771</v>
       </c>
       <c r="X18">
-        <v>0.02542290094913313</v>
+        <v>0.1045165678329815</v>
       </c>
       <c r="Y18">
-        <v>0.0272267893468063</v>
+        <v>0.02716282147999562</v>
       </c>
       <c r="Z18">
-        <v>0.228397411496003</v>
+        <v>0.1739297587010109</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.02494494210702478</v>
+        <v>0.05034370147393842</v>
       </c>
       <c r="AC18">
-        <v>-0.02494494210702478</v>
+        <v>-0.05034370147393842</v>
       </c>
       <c r="AD18">
-        <v>61.4</v>
+        <v>7418.2</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>61.4</v>
+        <v>7418.2</v>
       </c>
       <c r="AG18">
-        <v>-39.4</v>
+        <v>6868.9</v>
       </c>
       <c r="AH18">
-        <v>0.1396406640891517</v>
+        <v>0.8657928829028606</v>
       </c>
       <c r="AI18">
-        <v>0.1434914699696191</v>
+        <v>0.7311596916950857</v>
       </c>
       <c r="AJ18">
-        <v>-0.1162584833284154</v>
+        <v>0.8565994911956901</v>
       </c>
       <c r="AK18">
-        <v>-0.1204524610210945</v>
+        <v>0.7157713749804616</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2746,7 +2722,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Roan Holdings Group Co., Ltd. (OTCPK:RAHG.F)</t>
+          <t>Anhui Xinli Finance Co., Ltd. (SHSE:600318)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2755,112 +2731,112 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.281</v>
+        <v>-0.121</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.02926208651399491</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.03048970686185539</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.03048970686185539</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>-1.97</v>
+        <v>-43.8</v>
       </c>
       <c r="L19">
-        <v>-0.4218415417558887</v>
+        <v>-1.114503816793893</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>1.59</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.003164179104477612</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-0.0363013698630137</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>1.59</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.003164179104477612</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>-0.0363013698630137</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
       <c r="U19">
-        <v>2.26</v>
+        <v>46.2</v>
       </c>
       <c r="V19">
-        <v>0.5580246913580247</v>
+        <v>0.09194029850746269</v>
       </c>
       <c r="W19">
-        <v>0.2334123222748815</v>
+        <v>-0.2030598052851182</v>
       </c>
       <c r="X19">
-        <v>0.03482279862266569</v>
+        <v>0.05254571680807864</v>
       </c>
       <c r="Y19">
-        <v>0.1985895236522159</v>
+        <v>-0.2556055220931969</v>
       </c>
       <c r="Z19">
-        <v>0.1754052185316009</v>
+        <v>0.1350979718116191</v>
       </c>
       <c r="AA19">
-        <v>0.005348053695068196</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03055109515237096</v>
+        <v>0.05144693997671509</v>
       </c>
       <c r="AC19">
-        <v>-0.02520304145730277</v>
+        <v>-0.05144693997671509</v>
       </c>
       <c r="AD19">
-        <v>5.88</v>
+        <v>148.2</v>
       </c>
       <c r="AE19">
-        <v>0.2930653447756768</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>6.173065344775677</v>
+        <v>148.2</v>
       </c>
       <c r="AG19">
-        <v>3.913065344775677</v>
+        <v>102</v>
       </c>
       <c r="AH19">
-        <v>0.6038370231028912</v>
+        <v>0.2277547256800369</v>
       </c>
       <c r="AI19">
-        <v>0.1043222166843633</v>
+        <v>0.3041247691360558</v>
       </c>
       <c r="AJ19">
-        <v>0.4914018880107419</v>
+        <v>0.1687344913151365</v>
       </c>
       <c r="AK19">
-        <v>0.06875513242997157</v>
+        <v>0.2312400816141464</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AM19">
-        <v>-0.01</v>
-      </c>
-      <c r="AN19">
-        <v>29.25373134328358</v>
-      </c>
-      <c r="AP19">
-        <v>19.46798678992874</v>
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
       </c>
       <c r="AQ19">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2880,16 +2856,16 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.373</v>
+        <v>0.403</v>
       </c>
       <c r="E20">
-        <v>0.517</v>
+        <v>0.718</v>
       </c>
       <c r="F20">
-        <v>0.329</v>
+        <v>0.113</v>
       </c>
       <c r="G20">
-        <v>0.05563876407610806</v>
+        <v>0.07534857780256553</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2901,28 +2877,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>1181.6</v>
+        <v>1252.8</v>
       </c>
       <c r="L20">
-        <v>0.655461252565596</v>
+        <v>0.6987172336865588</v>
       </c>
       <c r="M20">
-        <v>138.4</v>
+        <v>262.6</v>
       </c>
       <c r="N20">
-        <v>0.002292206662967779</v>
+        <v>0.007065236400227078</v>
       </c>
       <c r="O20">
-        <v>0.1171293161814489</v>
+        <v>0.2096104725415071</v>
       </c>
       <c r="P20">
-        <v>138.4</v>
+        <v>262.6</v>
       </c>
       <c r="Q20">
-        <v>0.002292206662967779</v>
+        <v>0.007065236400227078</v>
       </c>
       <c r="R20">
-        <v>0.1171293161814489</v>
+        <v>0.2096104725415071</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2931,61 +2907,61 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>9008.6</v>
+        <v>7963</v>
       </c>
       <c r="V20">
-        <v>0.1492021166474821</v>
+        <v>0.2142440116336947</v>
       </c>
       <c r="W20">
-        <v>0.2522899540941603</v>
+        <v>0.1968016588645575</v>
       </c>
       <c r="X20">
-        <v>0.02541752422646455</v>
+        <v>0.05208319754046637</v>
       </c>
       <c r="Y20">
-        <v>0.2268724298676958</v>
+        <v>0.1447184613240911</v>
       </c>
       <c r="Z20">
-        <v>0.7068303011292347</v>
+        <v>0.269510582010582</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.02590744755774412</v>
+        <v>0.05209542241720233</v>
       </c>
       <c r="AC20">
-        <v>-0.02590744755774412</v>
+        <v>-0.05209542241720233</v>
       </c>
       <c r="AD20">
-        <v>9752.700000000001</v>
+        <v>8925.4</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>9752.700000000001</v>
+        <v>8925.4</v>
       </c>
       <c r="AG20">
-        <v>744.1000000000004</v>
+        <v>962.3999999999996</v>
       </c>
       <c r="AH20">
-        <v>0.1390636407191093</v>
+        <v>0.1936376870391141</v>
       </c>
       <c r="AI20">
-        <v>0.6050625058162981</v>
+        <v>0.5002746482820469</v>
       </c>
       <c r="AJ20">
-        <v>0.01217389312627408</v>
+        <v>0.02523976994673526</v>
       </c>
       <c r="AK20">
-        <v>0.1046568868760461</v>
+        <v>0.09742862927718157</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-90.59999999999999</v>
+        <v>-198.6</v>
       </c>
       <c r="AQ20">
         <v>-0</v>
@@ -2999,7 +2975,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anhui Xinli Finance Co., Ltd. (SHSE:600318)</t>
+          <t>Differ Group Auto Limited (SEHK:6878)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3008,10 +2984,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.174</v>
+        <v>0.391</v>
+      </c>
+      <c r="E21">
+        <v>0.246</v>
       </c>
       <c r="G21">
-        <v>0.01695652173913044</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3023,28 +3002,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-4.38</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L21">
-        <v>-0.07934782608695652</v>
+        <v>0.3418886198547215</v>
       </c>
       <c r="M21">
-        <v>3.93</v>
+        <v>4.57</v>
       </c>
       <c r="N21">
-        <v>0.004087363494539782</v>
+        <v>0.003340154948107002</v>
       </c>
       <c r="O21">
-        <v>-0.8972602739726028</v>
+        <v>0.06473087818696885</v>
       </c>
       <c r="P21">
-        <v>3.93</v>
+        <v>4.57</v>
       </c>
       <c r="Q21">
-        <v>0.004087363494539782</v>
+        <v>0.003340154948107002</v>
       </c>
       <c r="R21">
-        <v>-0.8972602739726028</v>
+        <v>0.06473087818696885</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3053,64 +3032,61 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>35.4</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="V21">
-        <v>0.03681747269890796</v>
+        <v>0.00649758807191931</v>
       </c>
       <c r="W21">
-        <v>-0.0232484076433121</v>
+        <v>0.1944903581267217</v>
       </c>
       <c r="X21">
-        <v>0.026080035511935</v>
+        <v>0.05133750087643624</v>
       </c>
       <c r="Y21">
-        <v>-0.04932844315524709</v>
+        <v>0.1431528572502855</v>
       </c>
       <c r="Z21">
-        <v>0.1491085899513776</v>
+        <v>0.4010487473295786</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.02595377934485334</v>
+        <v>0.05235350688324462</v>
       </c>
       <c r="AC21">
-        <v>-0.02595377934485334</v>
+        <v>-0.05235350688324462</v>
       </c>
       <c r="AD21">
-        <v>247.6</v>
+        <v>207.7</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>247.6</v>
+        <v>207.7</v>
       </c>
       <c r="AG21">
-        <v>212.2</v>
+        <v>198.81</v>
       </c>
       <c r="AH21">
-        <v>0.2047804151848482</v>
+        <v>0.1317977028999302</v>
       </c>
       <c r="AI21">
-        <v>0.3865126443958788</v>
+        <v>0.3338691528693136</v>
       </c>
       <c r="AJ21">
-        <v>0.1807957740478827</v>
+        <v>0.1268721960931966</v>
       </c>
       <c r="AK21">
-        <v>0.3506278916060806</v>
+        <v>0.3242119339214951</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1.76</v>
-      </c>
-      <c r="AQ21">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3121,7 +3097,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zuoli Kechuang Micro-finance Company Limited (SEHK:6866)</t>
+          <t>Yixin Group Limited (SEHK:2858)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3130,13 +3106,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0303</v>
-      </c>
-      <c r="E22">
-        <v>-0.07440000000000001</v>
+        <v>0.0911</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.04478120211135706</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3148,19 +3121,19 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>15.7</v>
+        <v>42.9</v>
       </c>
       <c r="L22">
-        <v>0.5413793103448276</v>
+        <v>0.07304614336795505</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>2.31</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.002846229669788073</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3172,58 +3145,61 @@
         <v>-0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.31</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>1.2</v>
+        <v>622.2</v>
       </c>
       <c r="V22">
-        <v>0.02173913043478261</v>
+        <v>0.7666338097585017</v>
       </c>
       <c r="W22">
-        <v>0.06154449235593885</v>
+        <v>0.01922732162065257</v>
       </c>
       <c r="X22">
-        <v>0.03871935526549811</v>
+        <v>0.06699295995789639</v>
       </c>
       <c r="Y22">
-        <v>0.02282513709044073</v>
+        <v>-0.04776563833724383</v>
       </c>
       <c r="Z22">
-        <v>0.08724428399518651</v>
+        <v>0.1933752592934049</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.02741303642955354</v>
+        <v>0.054131779330704</v>
       </c>
       <c r="AC22">
-        <v>-0.02741303642955354</v>
+        <v>-0.054131779330704</v>
       </c>
       <c r="AD22">
-        <v>115.3</v>
+        <v>1628.3</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>115.3</v>
+        <v>1628.3</v>
       </c>
       <c r="AG22">
-        <v>114.1</v>
+        <v>1006.1</v>
       </c>
       <c r="AH22">
-        <v>0.6762463343108505</v>
+        <v>0.6673634165334644</v>
       </c>
       <c r="AI22">
-        <v>0.2810823988298391</v>
+        <v>0.4220033691849164</v>
       </c>
       <c r="AJ22">
-        <v>0.6739515652687537</v>
+        <v>0.5535016779446553</v>
       </c>
       <c r="AK22">
-        <v>0.2789731051344743</v>
+        <v>0.3108797083088712</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3240,7 +3216,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shanghai Dongzheng Automotive Finance Co., Ltd. (SEHK:2718)</t>
+          <t>Zuoli Kechuang Micro-finance Company Limited (SEHK:6866)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3248,95 +3224,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D23">
+        <v>-0.0572</v>
+      </c>
+      <c r="E23">
+        <v>-0.06309999999999999</v>
+      </c>
       <c r="G23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>-53.8</v>
+        <v>15</v>
       </c>
       <c r="L23">
-        <v>1.16702819956616</v>
+        <v>0.5859375</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>8.26</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.1819383259911894</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>0.5506666666666666</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>8.26</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.1819383259911894</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>0.5506666666666666</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>0.0960352422907489</v>
       </c>
       <c r="W23">
-        <v>-0.09152773052058523</v>
+        <v>0.05272407732864675</v>
       </c>
       <c r="X23">
-        <v>0.02879316574875765</v>
+        <v>0.07210922573191164</v>
       </c>
       <c r="Y23">
-        <v>-0.1203208962693429</v>
+        <v>-0.01938514840326489</v>
       </c>
       <c r="Z23">
-        <v>-0.03934790030727211</v>
+        <v>0.06475275072720374</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.02748073317941057</v>
+        <v>0.05447261352970116</v>
       </c>
       <c r="AC23">
-        <v>-0.02748073317941057</v>
+        <v>-0.05447261352970116</v>
       </c>
       <c r="AD23">
-        <v>155.3</v>
+        <v>118.6</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>155.3</v>
+        <v>118.6</v>
       </c>
       <c r="AG23">
-        <v>155.3</v>
+        <v>114.24</v>
       </c>
       <c r="AH23">
-        <v>0.3941624365482234</v>
+        <v>0.723170731707317</v>
       </c>
       <c r="AI23">
-        <v>0.2085963734049698</v>
+        <v>0.3026282214850727</v>
       </c>
       <c r="AJ23">
-        <v>0.3941624365482234</v>
+        <v>0.7156101227762466</v>
       </c>
       <c r="AK23">
-        <v>0.2085963734049698</v>
+        <v>0.294782474067193</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3353,7 +3338,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AVIC Industry-Finance Holdings Co., Ltd. (SHSE:600705)</t>
+          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3362,46 +3347,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.112</v>
+        <v>0.186</v>
       </c>
       <c r="E24">
-        <v>0.104</v>
+        <v>0.183</v>
       </c>
       <c r="G24">
-        <v>0.003682950435535633</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.007481172261017036</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.00585230945425306</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>553.1</v>
+        <v>606</v>
       </c>
       <c r="L24">
-        <v>0.2817482553104784</v>
+        <v>0.2994367032315446</v>
       </c>
       <c r="M24">
-        <v>1437</v>
+        <v>137.2</v>
       </c>
       <c r="N24">
-        <v>0.2603874100784605</v>
+        <v>0.07982777680805259</v>
       </c>
       <c r="O24">
-        <v>2.59808352919906</v>
+        <v>0.2264026402640264</v>
       </c>
       <c r="P24">
-        <v>1437</v>
+        <v>137.2</v>
       </c>
       <c r="Q24">
-        <v>0.2603874100784605</v>
+        <v>0.07982777680805259</v>
       </c>
       <c r="R24">
-        <v>2.59808352919906</v>
+        <v>0.2264026402640264</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3410,70 +3395,61 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>7845</v>
+        <v>4554</v>
       </c>
       <c r="V24">
-        <v>1.421530432891804</v>
+        <v>2.649677081515099</v>
       </c>
       <c r="W24">
-        <v>0.1148248873756981</v>
+        <v>0.1409630146545708</v>
       </c>
       <c r="X24">
-        <v>0.05877525315424112</v>
+        <v>0.2655475664434029</v>
       </c>
       <c r="Y24">
-        <v>0.05604963422145695</v>
+        <v>-0.1245845517888321</v>
       </c>
       <c r="Z24">
-        <v>0.09672926597921178</v>
+        <v>0.04875698361034887</v>
       </c>
       <c r="AA24">
-        <v>0.0005660895977930998</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.02813485764872416</v>
+        <v>0.05448961369554494</v>
       </c>
       <c r="AC24">
-        <v>-0.02756876805093106</v>
+        <v>-0.05448961369554494</v>
       </c>
       <c r="AD24">
-        <v>27524</v>
+        <v>43871.9</v>
       </c>
       <c r="AE24">
-        <v>39.5685536719873</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>27563.56855367199</v>
+        <v>43871.9</v>
       </c>
       <c r="AG24">
-        <v>19718.56855367199</v>
+        <v>39317.9</v>
       </c>
       <c r="AH24">
-        <v>0.8331825403373841</v>
+        <v>0.9623014393317921</v>
       </c>
       <c r="AI24">
-        <v>0.7236513722866716</v>
+        <v>0.900943619020238</v>
       </c>
       <c r="AJ24">
-        <v>0.7813273655877851</v>
+        <v>0.9581178752625705</v>
       </c>
       <c r="AK24">
-        <v>0.6519705684899896</v>
+        <v>0.8907241484770567</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-465.1</v>
-      </c>
-      <c r="AN24">
-        <v>1217.87610619469</v>
-      </c>
-      <c r="AP24">
-        <v>872.5030333483179</v>
-      </c>
-      <c r="AQ24">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3484,7 +3460,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jiangsu Financial Leasing Co., Ltd. (SHSE:600901)</t>
+          <t>Roan Holdings Group Co., Ltd. (OTCPK:RAHG.F)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3492,6 +3468,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>-0.288</v>
+      </c>
+      <c r="E25">
+        <v>-0.4</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3499,103 +3481,103 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>2.122840224981808e-05</v>
+        <v>0.01208723058309487</v>
       </c>
       <c r="J25">
-        <v>1.59187876653065e-05</v>
+        <v>0.008720423036062777</v>
       </c>
       <c r="K25">
-        <v>316.6</v>
+        <v>1.22</v>
       </c>
       <c r="L25">
-        <v>0.6416700445885691</v>
+        <v>0.2791762013729977</v>
       </c>
       <c r="M25">
-        <v>191.7</v>
+        <v>-0</v>
       </c>
       <c r="N25">
-        <v>0.08010865022983701</v>
+        <v>-0</v>
       </c>
       <c r="O25">
-        <v>0.6054958938723941</v>
+        <v>-0</v>
       </c>
       <c r="P25">
-        <v>191.7</v>
+        <v>-0</v>
       </c>
       <c r="Q25">
-        <v>0.08010865022983701</v>
+        <v>-0</v>
       </c>
       <c r="R25">
-        <v>0.6054958938723941</v>
+        <v>-0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
-        <v>306.7</v>
+        <v>1.04</v>
       </c>
       <c r="V25">
-        <v>0.1281654826577518</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="W25">
-        <v>0.1714038222077852</v>
+        <v>-0.1345093715545755</v>
       </c>
       <c r="X25">
-        <v>0.05605769076812991</v>
+        <v>0.06480598146890318</v>
       </c>
       <c r="Y25">
-        <v>0.1153461314396553</v>
+        <v>-0.1993153530234787</v>
       </c>
       <c r="Z25">
-        <v>0.04874765443263898</v>
+        <v>0.1185892148999252</v>
       </c>
       <c r="AA25">
-        <v>7.760035600949173e-07</v>
+        <v>0.001034148121441907</v>
       </c>
       <c r="AB25">
-        <v>0.02808091911755859</v>
+        <v>0.0557527979358543</v>
       </c>
       <c r="AC25">
-        <v>-0.0280801431139985</v>
+        <v>-0.0547186498144124</v>
       </c>
       <c r="AD25">
-        <v>11009.8</v>
+        <v>5.67</v>
       </c>
       <c r="AE25">
-        <v>0.0126295316496988</v>
+        <v>0.06089401175937712</v>
       </c>
       <c r="AF25">
-        <v>11009.81262953165</v>
+        <v>5.730894011759377</v>
       </c>
       <c r="AG25">
-        <v>10703.11262953165</v>
+        <v>4.690894011759377</v>
       </c>
       <c r="AH25">
-        <v>0.8214553865561559</v>
+        <v>0.635996162454076</v>
       </c>
       <c r="AI25">
-        <v>0.8380566817586766</v>
+        <v>0.09791229244863388</v>
       </c>
       <c r="AJ25">
-        <v>0.8172740211012083</v>
+        <v>0.5885028711759245</v>
       </c>
       <c r="AK25">
-        <v>0.8341856260937044</v>
+        <v>0.08159368700719606</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-0.081</v>
       </c>
       <c r="AN25">
-        <v>846907.6923076923</v>
+        <v>87.23076923076923</v>
       </c>
       <c r="AP25">
-        <v>823316.3561178191</v>
+        <v>72.16760018091348</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -3606,7 +3588,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Haitong Unitrust International Financial Leasing Co., Ltd. (SEHK:1905)</t>
+          <t>Zhongguancun Science-Tech Leasing Co., Ltd. (SEHK:1601)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3614,12 +3596,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.0166</v>
-      </c>
-      <c r="E26">
-        <v>0.112</v>
-      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3633,94 +3609,91 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>206.1</v>
+        <v>31.5</v>
       </c>
       <c r="L26">
-        <v>0.4974656046343229</v>
+        <v>0.5311973018549747</v>
       </c>
       <c r="M26">
-        <v>263.4</v>
+        <v>8.66</v>
       </c>
       <c r="N26">
-        <v>0.2421400992829564</v>
+        <v>0.07787769784172661</v>
       </c>
       <c r="O26">
-        <v>1.27802037845706</v>
+        <v>0.2749206349206349</v>
       </c>
       <c r="P26">
-        <v>77.2</v>
+        <v>8.66</v>
       </c>
       <c r="Q26">
-        <v>0.07096892811178526</v>
+        <v>0.07787769784172661</v>
       </c>
       <c r="R26">
-        <v>0.3745754488112567</v>
+        <v>0.2749206349206349</v>
       </c>
       <c r="S26">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.7069096431283219</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>994.2</v>
+        <v>70.2</v>
       </c>
       <c r="V26">
-        <v>0.9139547710976283</v>
+        <v>0.6312949640287769</v>
       </c>
       <c r="W26">
-        <v>0.08993716180834352</v>
+        <v>0.1040634291377602</v>
       </c>
       <c r="X26">
-        <v>0.09919873308302492</v>
+        <v>0.1078819645846738</v>
       </c>
       <c r="Y26">
-        <v>-0.009261571274681399</v>
+        <v>-0.003818535446913629</v>
       </c>
       <c r="Z26">
-        <v>0.0539439077107367</v>
+        <v>0.06426790939633684</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.02851403174881096</v>
+        <v>0.05538528093992202</v>
       </c>
       <c r="AC26">
-        <v>-0.02851403174881096</v>
+        <v>-0.05538528093992202</v>
       </c>
       <c r="AD26">
-        <v>11804.1</v>
+        <v>761.7</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>11804.1</v>
+        <v>761.7</v>
       </c>
       <c r="AG26">
-        <v>10809.9</v>
+        <v>691.5</v>
       </c>
       <c r="AH26">
-        <v>0.9156214367160775</v>
+        <v>0.8726085462252262</v>
       </c>
       <c r="AI26">
-        <v>0.8121379329324508</v>
+        <v>0.7078338444382494</v>
       </c>
       <c r="AJ26">
-        <v>0.9085705640585996</v>
+        <v>0.8614675470287778</v>
       </c>
       <c r="AK26">
-        <v>0.798344214351127</v>
+        <v>0.6874440799284223</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1.14</v>
-      </c>
-      <c r="AQ26">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3731,7 +3704,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yixin Group Limited (SEHK:2858)</t>
+          <t>Haitong Unitrust International Financial Leasing Co., Ltd. (SEHK:1905)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3739,8 +3712,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D27">
+        <v>0.0329</v>
+      </c>
+      <c r="E27">
+        <v>0.0653</v>
+      </c>
       <c r="G27">
-        <v>0.04661791590493601</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3752,91 +3731,91 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-36.8</v>
+        <v>213.7</v>
       </c>
       <c r="L27">
-        <v>-0.08409506398537477</v>
+        <v>0.4041225416036309</v>
       </c>
       <c r="M27">
-        <v>0.777</v>
+        <v>313.3</v>
       </c>
       <c r="N27">
-        <v>0.0007618393960192176</v>
+        <v>0.348964134551125</v>
       </c>
       <c r="O27">
-        <v>-0.02111413043478261</v>
+        <v>1.466073935423491</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>104.4</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.1162842503898418</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>0.4885353299017314</v>
       </c>
       <c r="S27">
-        <v>0.777</v>
+        <v>208.9</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>0.6667730609639323</v>
       </c>
       <c r="U27">
-        <v>467.7</v>
+        <v>1034.1</v>
       </c>
       <c r="V27">
-        <v>0.458574370036278</v>
+        <v>1.151815549120071</v>
       </c>
       <c r="W27">
-        <v>-0.01762536519948273</v>
+        <v>0.07860952731285635</v>
       </c>
       <c r="X27">
-        <v>0.03292154666782982</v>
+        <v>0.1641815164727743</v>
       </c>
       <c r="Y27">
-        <v>-0.05054691186731256</v>
+        <v>-0.08557198915991794</v>
       </c>
       <c r="Z27">
-        <v>0.1158806238911104</v>
+        <v>0.06791241250882937</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.0287800253083395</v>
+        <v>0.05574265403189646</v>
       </c>
       <c r="AC27">
-        <v>-0.0287800253083395</v>
+        <v>-0.05574265403189646</v>
       </c>
       <c r="AD27">
-        <v>1273.6</v>
+        <v>12137.2</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>1273.6</v>
+        <v>12137.2</v>
       </c>
       <c r="AG27">
-        <v>805.8999999999999</v>
+        <v>11103.1</v>
       </c>
       <c r="AH27">
-        <v>0.5553084804883366</v>
+        <v>0.9311238971998467</v>
       </c>
       <c r="AI27">
-        <v>0.3633873544852773</v>
+        <v>0.8274667812024897</v>
       </c>
       <c r="AJ27">
-        <v>0.4413955526344616</v>
+        <v>0.9251889441625212</v>
       </c>
       <c r="AK27">
-        <v>0.2653518158769879</v>
+        <v>0.8143804368554622</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-5.64</v>
+        <v>-3.07</v>
       </c>
       <c r="AQ27">
         <v>-0</v>
@@ -3850,7 +3829,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hanhua Financial Holding Co., Ltd. (SEHK:3903)</t>
+          <t>51 Credit Card Inc. (SEHK:2051)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3858,110 +3837,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D28">
-        <v>-0.06849999999999999</v>
-      </c>
-      <c r="E28">
-        <v>-0.124</v>
-      </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.06361111111111112</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>-0.03458333333333333</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>-0.1066666666666667</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>-0.1066666666666667</v>
       </c>
       <c r="K28">
-        <v>18.4</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L28">
-        <v>0.1374159820761762</v>
+        <v>-0.1301388888888889</v>
       </c>
       <c r="M28">
-        <v>23</v>
+        <v>0.025</v>
       </c>
       <c r="N28">
-        <v>0.07357645553422903</v>
+        <v>0.0007936507936507937</v>
       </c>
       <c r="O28">
-        <v>1.25</v>
+        <v>-0.002668089647812167</v>
       </c>
       <c r="P28">
-        <v>23</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.07357645553422903</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>100.1</v>
+        <v>52.5</v>
       </c>
       <c r="V28">
-        <v>0.3202175303902751</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="W28">
-        <v>0.01764480245492904</v>
+        <v>-0.07349019607843137</v>
       </c>
       <c r="X28">
-        <v>0.03712635452633851</v>
+        <v>0.05914113608388982</v>
       </c>
       <c r="Y28">
-        <v>-0.01948155207140947</v>
+        <v>-0.1326313321623212</v>
       </c>
       <c r="Z28">
-        <v>0.08062767956067249</v>
+        <v>0.6328557616243298</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>-0.06750461457326183</v>
       </c>
       <c r="AB28">
-        <v>0.02954431856700392</v>
+        <v>0.06737261288949242</v>
       </c>
       <c r="AC28">
-        <v>-0.02954431856700392</v>
+        <v>-0.1348772274627543</v>
       </c>
       <c r="AD28">
-        <v>580.8</v>
+        <v>33.9</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>580.8</v>
+        <v>33.9</v>
       </c>
       <c r="AG28">
-        <v>480.6999999999999</v>
+        <v>-18.6</v>
       </c>
       <c r="AH28">
-        <v>0.6501007387508394</v>
+        <v>0.5183486238532109</v>
       </c>
       <c r="AI28">
-        <v>0.3185782458449893</v>
+        <v>0.2281292059219381</v>
       </c>
       <c r="AJ28">
-        <v>0.6059498298247825</v>
+        <v>-1.441860465116279</v>
       </c>
       <c r="AK28">
-        <v>0.2789901334881021</v>
+        <v>-0.1935483870967742</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.353</v>
+      </c>
+      <c r="AN28">
+        <v>-5.905923344947735</v>
+      </c>
+      <c r="AO28">
+        <v>-3.522935779816514</v>
+      </c>
+      <c r="AP28">
+        <v>3.240418118466899</v>
+      </c>
+      <c r="AQ28">
+        <v>-5.676274944567626</v>
       </c>
     </row>
     <row r="29">
@@ -3972,7 +3957,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
+          <t>Oceanwide Holdings Co., Ltd. (SZSE:000046)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3981,46 +3966,43 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.244</v>
-      </c>
-      <c r="E29">
-        <v>0.274</v>
+        <v>-0.212</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>-1.902506557854853</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>-1.902506557854853</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>-2.040221509763917</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>-2.040221509763917</v>
       </c>
       <c r="K29">
-        <v>594.9</v>
+        <v>-1645</v>
       </c>
       <c r="L29">
-        <v>0.323455850369726</v>
+        <v>-2.397260273972603</v>
       </c>
       <c r="M29">
-        <v>191.9</v>
+        <v>71.3</v>
       </c>
       <c r="N29">
-        <v>0.1003083999790915</v>
+        <v>0.07571413401295529</v>
       </c>
       <c r="O29">
-        <v>0.3225752227265087</v>
+        <v>-0.0433434650455927</v>
       </c>
       <c r="P29">
-        <v>191.9</v>
+        <v>71.3</v>
       </c>
       <c r="Q29">
-        <v>0.1003083999790915</v>
+        <v>0.07571413401295529</v>
       </c>
       <c r="R29">
-        <v>0.3225752227265087</v>
+        <v>-0.0433434650455927</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4029,61 +4011,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>4138.6</v>
+        <v>380.5</v>
       </c>
       <c r="V29">
-        <v>2.163295175369819</v>
+        <v>0.4040564935754486</v>
       </c>
       <c r="W29">
-        <v>0.1697628627685986</v>
+        <v>-0.7100310773480663</v>
       </c>
       <c r="X29">
-        <v>0.1734744752023825</v>
+        <v>0.1204371197135399</v>
       </c>
       <c r="Y29">
-        <v>-0.003711612433783901</v>
+        <v>-0.8304681970616061</v>
       </c>
       <c r="Z29">
-        <v>0.05420287411977798</v>
+        <v>0.0606435534188223</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>-0.1237262821135984</v>
       </c>
       <c r="AB29">
-        <v>0.03094493946109365</v>
+        <v>0.05550920645820581</v>
       </c>
       <c r="AC29">
-        <v>-0.03094493946109365</v>
+        <v>-0.1792354885718042</v>
       </c>
       <c r="AD29">
-        <v>41347.5</v>
+        <v>7851</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>41347.5</v>
+        <v>7851</v>
       </c>
       <c r="AG29">
-        <v>37208.9</v>
+        <v>7470.5</v>
       </c>
       <c r="AH29">
-        <v>0.955777312381243</v>
+        <v>0.8928997918728035</v>
       </c>
       <c r="AI29">
-        <v>0.9058197233084684</v>
+        <v>0.8259776330601466</v>
       </c>
       <c r="AJ29">
-        <v>0.9510991258115639</v>
+        <v>0.8880554432847531</v>
       </c>
       <c r="AK29">
-        <v>0.8964293544120517</v>
+        <v>0.8187208206387129</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>611.5</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>611.5</v>
+      </c>
+      <c r="AN29">
+        <v>-5.627553580388503</v>
+      </c>
+      <c r="AO29">
+        <v>-2.289452166802944</v>
+      </c>
+      <c r="AP29">
+        <v>-5.354813275034048</v>
+      </c>
+      <c r="AQ29">
+        <v>-2.289452166802944</v>
       </c>
     </row>
     <row r="30">
@@ -4094,7 +4088,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zhongguancun Science-Tech Leasing Co., Ltd. (SEHK:1601)</t>
+          <t>Zero2IPO Holdings Inc. (SEHK:1945)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4103,103 +4097,115 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.1805970149253731</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.08097014925373133</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>-0.1757462686567164</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>-0.1757462686567164</v>
       </c>
       <c r="K30">
-        <v>27.9</v>
+        <v>-3.81</v>
       </c>
       <c r="L30">
-        <v>0.5234521575984991</v>
+        <v>-0.1421641791044776</v>
       </c>
       <c r="M30">
-        <v>8.331</v>
+        <v>2.12</v>
       </c>
       <c r="N30">
-        <v>0.05733654507914659</v>
+        <v>0.01843478260869565</v>
       </c>
       <c r="O30">
-        <v>0.2986021505376344</v>
+        <v>-0.5564304461942258</v>
       </c>
       <c r="P30">
-        <v>7.74</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.05326909841706813</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>0.2774193548387097</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>0.5909999999999993</v>
+        <v>2.12</v>
       </c>
       <c r="T30">
-        <v>0.0709398631616852</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>67</v>
+        <v>58.3</v>
       </c>
       <c r="V30">
-        <v>0.4611149346180316</v>
+        <v>0.5069565217391304</v>
       </c>
       <c r="W30">
-        <v>0.1075973775549556</v>
+        <v>-0.04967405475880052</v>
       </c>
       <c r="X30">
-        <v>0.05693636829873475</v>
+        <v>0.05017268409073145</v>
       </c>
       <c r="Y30">
-        <v>0.05066100925622089</v>
+        <v>-0.09984673884953196</v>
       </c>
       <c r="Z30">
-        <v>0.0721928755248544</v>
+        <v>1.445523193096009</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>-0.2540453074433657</v>
       </c>
       <c r="AB30">
-        <v>0.0309579152700203</v>
+        <v>0.05013925367159903</v>
       </c>
       <c r="AC30">
-        <v>-0.0309579152700203</v>
+        <v>-0.3041845611149648</v>
       </c>
       <c r="AD30">
-        <v>687</v>
+        <v>1.59</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>687</v>
+        <v>1.59</v>
       </c>
       <c r="AG30">
-        <v>620</v>
+        <v>-56.70999999999999</v>
       </c>
       <c r="AH30">
-        <v>0.8254235251712123</v>
+        <v>0.0136375332361266</v>
       </c>
       <c r="AI30">
-        <v>0.6941497423461654</v>
+        <v>0.02097902097902098</v>
       </c>
       <c r="AJ30">
-        <v>0.810139814451849</v>
+        <v>-0.9728941499399552</v>
       </c>
       <c r="AK30">
-        <v>0.6719410425923918</v>
+        <v>-3.24242424242424</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>-0.02100000000000002</v>
+      </c>
+      <c r="AN30">
+        <v>-0.3638443935926773</v>
+      </c>
+      <c r="AO30">
+        <v>-32.93706293706294</v>
+      </c>
+      <c r="AP30">
+        <v>12.97711670480549</v>
+      </c>
+      <c r="AQ30">
+        <v>224.2857142857141</v>
       </c>
     </row>
     <row r="31">
@@ -4210,7 +4216,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>China Rongzhong Financial Holdings Company Limited (SEHK:3963)</t>
+          <t>Senmiao Technology Limited (NasdaqCM:AIHS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4218,32 +4224,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D31">
+        <v>0.99</v>
+      </c>
       <c r="G31">
-        <v>-0</v>
+        <v>-1.2875</v>
       </c>
       <c r="H31">
-        <v>-0</v>
+        <v>-1.2875</v>
       </c>
       <c r="I31">
-        <v>-0</v>
+        <v>-0.9047816038905918</v>
       </c>
       <c r="J31">
-        <v>-0</v>
+        <v>-0.9047816038905918</v>
       </c>
       <c r="K31">
-        <v>-18.1</v>
+        <v>4.54</v>
       </c>
       <c r="L31">
-        <v>14.48</v>
+        <v>0.5675</v>
       </c>
       <c r="M31">
-        <v>-0</v>
+        <v>3.56</v>
       </c>
       <c r="N31">
-        <v>-0</v>
+        <v>0.5129682997118156</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>0.7841409691629956</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -4252,67 +4261,82 @@
         <v>-0</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.56</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
       </c>
       <c r="U31">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="V31">
-        <v>0.2309090909090909</v>
+        <v>0.2838616714697406</v>
       </c>
       <c r="W31">
-        <v>-3.995584988962472</v>
+        <v>1.883817427385892</v>
       </c>
       <c r="X31">
-        <v>0.1366170872179994</v>
+        <v>0.05105496898537171</v>
       </c>
       <c r="Y31">
-        <v>-4.132202076180472</v>
+        <v>1.83276245840052</v>
       </c>
       <c r="Z31">
-        <v>-0.01479815319048183</v>
+        <v>0.8756314248067941</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>-0.7922552049536953</v>
       </c>
       <c r="AB31">
-        <v>0.03189869954277715</v>
+        <v>0.05100379238205713</v>
       </c>
       <c r="AC31">
-        <v>-0.03189869954277715</v>
+        <v>-0.8432589973357524</v>
       </c>
       <c r="AD31">
-        <v>89.5</v>
+        <v>0.195</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>0.6262641556236733</v>
       </c>
       <c r="AF31">
-        <v>89.5</v>
+        <v>0.8212641556236733</v>
       </c>
       <c r="AG31">
-        <v>88.23</v>
+        <v>-1.148735844376327</v>
       </c>
       <c r="AH31">
-        <v>0.9421052631578948</v>
+        <v>0.1058157716521734</v>
       </c>
       <c r="AI31">
-        <v>1.191744340878828</v>
+        <v>0.07006617585950778</v>
       </c>
       <c r="AJ31">
-        <v>0.9413208151072229</v>
+        <v>-0.1983566650574613</v>
       </c>
       <c r="AK31">
-        <v>1.195042665583096</v>
+        <v>-0.1178037868776057</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>0.033</v>
+      </c>
+      <c r="AN31">
+        <v>-0.0336613153806318</v>
+      </c>
+      <c r="AO31">
+        <v>-227.2727272727273</v>
+      </c>
+      <c r="AP31">
+        <v>0.1982972284440405</v>
+      </c>
+      <c r="AQ31">
+        <v>-227.2727272727273</v>
       </c>
     </row>
     <row r="32">
@@ -4323,7 +4347,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>51 Credit Card Inc. (SEHK:2051)</t>
+          <t>Shanghai DZH Limited (SHSE:601519)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4331,628 +4355,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D32">
+        <v>-0.0225</v>
+      </c>
       <c r="G32">
-        <v>-1.444863731656185</v>
+        <v>0.2304029304029304</v>
       </c>
       <c r="H32">
-        <v>-1.624737945492662</v>
+        <v>0.008424908424908424</v>
       </c>
       <c r="I32">
-        <v>-1.148846960167715</v>
+        <v>-0.1010989010989011</v>
       </c>
       <c r="J32">
-        <v>-1.148846960167715</v>
+        <v>-0.1010989010989011</v>
       </c>
       <c r="K32">
-        <v>-177.4</v>
+        <v>-10.9</v>
       </c>
       <c r="L32">
-        <v>-3.719077568134172</v>
+        <v>-0.07985347985347986</v>
       </c>
       <c r="M32">
-        <v>-0</v>
+        <v>0.041</v>
       </c>
       <c r="N32">
-        <v>-0</v>
+        <v>2.415743577657318e-05</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>-0.003761467889908257</v>
       </c>
       <c r="P32">
-        <v>-0</v>
+        <v>0.041</v>
       </c>
       <c r="Q32">
-        <v>-0</v>
+        <v>2.415743577657318e-05</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>-0.003761467889908257</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
       <c r="U32">
-        <v>42.8</v>
+        <v>201.2</v>
       </c>
       <c r="V32">
-        <v>0.4637053087757313</v>
+        <v>0.118548197030403</v>
       </c>
       <c r="W32">
-        <v>-0.6889320388349515</v>
+        <v>-0.04526578073089701</v>
       </c>
       <c r="X32">
-        <v>0.0268675540850626</v>
+        <v>0.05011615074914245</v>
       </c>
       <c r="Y32">
-        <v>-0.715799592920014</v>
+        <v>-0.09538193148003946</v>
       </c>
       <c r="Z32">
-        <v>0.1870588235294118</v>
+        <v>8.863636363636344</v>
       </c>
       <c r="AA32">
-        <v>-0.2149019607843137</v>
+        <v>-0.8961038961038942</v>
       </c>
       <c r="AB32">
-        <v>0.02710623953642069</v>
+        <v>0.05005831723382369</v>
       </c>
       <c r="AC32">
-        <v>-0.2420082003207344</v>
+        <v>-0.9461622133377179</v>
       </c>
       <c r="AD32">
-        <v>34.3</v>
+        <v>12.1</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>34.3</v>
+        <v>12.1</v>
       </c>
       <c r="AG32">
-        <v>-8.5</v>
+        <v>-189.1</v>
       </c>
       <c r="AH32">
-        <v>0.2709320695102685</v>
+        <v>0.00707892119581115</v>
       </c>
       <c r="AI32">
-        <v>0.2122524752475247</v>
+        <v>0.04971240755957271</v>
       </c>
       <c r="AJ32">
-        <v>-0.1014319809069213</v>
+        <v>-0.1253895630263245</v>
       </c>
       <c r="AK32">
-        <v>-0.07154882154882156</v>
+        <v>-4.481042654028434</v>
       </c>
       <c r="AL32">
-        <v>3.25</v>
+        <v>0.512</v>
       </c>
       <c r="AM32">
-        <v>1.78</v>
+        <v>-3.108</v>
       </c>
       <c r="AN32">
-        <v>-0.6686159844054581</v>
+        <v>-1.070796460176991</v>
       </c>
       <c r="AO32">
-        <v>-16.86153846153846</v>
+        <v>-26.953125</v>
       </c>
       <c r="AP32">
-        <v>0.165692007797271</v>
+        <v>16.73451327433628</v>
       </c>
       <c r="AQ32">
-        <v>-30.78651685393258</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Dragon Victory International Limited (NasdaqCM:LYL)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>-0.329</v>
-      </c>
-      <c r="G33">
-        <v>-17.07964601769912</v>
-      </c>
-      <c r="H33">
-        <v>-17.07964601769912</v>
-      </c>
-      <c r="I33">
-        <v>-17.3023055443123</v>
-      </c>
-      <c r="J33">
-        <v>-17.3023055443123</v>
-      </c>
-      <c r="K33">
-        <v>-5.15</v>
-      </c>
-      <c r="L33">
-        <v>-22.78761061946903</v>
-      </c>
-      <c r="M33">
-        <v>-0</v>
-      </c>
-      <c r="N33">
-        <v>-0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>-0</v>
-      </c>
-      <c r="Q33">
-        <v>-0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0.983</v>
-      </c>
-      <c r="V33">
-        <v>0.03473498233215547</v>
-      </c>
-      <c r="W33">
-        <v>-0.6502525252525253</v>
-      </c>
-      <c r="X33">
-        <v>0.02529446329796897</v>
-      </c>
-      <c r="Y33">
-        <v>-0.6755469885504942</v>
-      </c>
-      <c r="Z33">
-        <v>0.02842550880909918</v>
-      </c>
-      <c r="AA33">
-        <v>-0.4918268386675749</v>
-      </c>
-      <c r="AB33">
-        <v>0.02613195611075912</v>
-      </c>
-      <c r="AC33">
-        <v>-0.517958794778334</v>
-      </c>
-      <c r="AD33">
-        <v>4.02</v>
-      </c>
-      <c r="AE33">
-        <v>0.04660526507289848</v>
-      </c>
-      <c r="AF33">
-        <v>4.066605265072898</v>
-      </c>
-      <c r="AG33">
-        <v>3.083605265072898</v>
-      </c>
-      <c r="AH33">
-        <v>0.125642007611506</v>
-      </c>
-      <c r="AI33">
-        <v>0.3223216689144313</v>
-      </c>
-      <c r="AJ33">
-        <v>0.09825529090836069</v>
-      </c>
-      <c r="AK33">
-        <v>0.2650601593240129</v>
-      </c>
-      <c r="AL33">
-        <v>1.61</v>
-      </c>
-      <c r="AM33">
-        <v>1.196</v>
-      </c>
-      <c r="AN33">
-        <v>-1.052080607170898</v>
-      </c>
-      <c r="AO33">
-        <v>-2.447204968944099</v>
-      </c>
-      <c r="AP33">
-        <v>-0.8070152486450923</v>
-      </c>
-      <c r="AQ33">
-        <v>-3.294314381270902</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>China Binary New Fintech Group (SEHK:8255)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>0.0274</v>
-      </c>
-      <c r="G34">
-        <v>-0.7126623376623378</v>
-      </c>
-      <c r="H34">
-        <v>-1.256493506493507</v>
-      </c>
-      <c r="I34">
-        <v>-1.779686974375493</v>
-      </c>
-      <c r="J34">
-        <v>-1.779686974375493</v>
-      </c>
-      <c r="K34">
-        <v>-14</v>
-      </c>
-      <c r="L34">
-        <v>-2.272727272727272</v>
-      </c>
-      <c r="M34">
-        <v>-0</v>
-      </c>
-      <c r="N34">
-        <v>-0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>-0</v>
-      </c>
-      <c r="Q34">
-        <v>-0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>129.7</v>
-      </c>
-      <c r="V34">
-        <v>15.04640371229698</v>
-      </c>
-      <c r="W34">
-        <v>-0.5</v>
-      </c>
-      <c r="X34">
-        <v>0.02502438575948823</v>
-      </c>
-      <c r="Y34">
-        <v>-0.5250243857594883</v>
-      </c>
-      <c r="Z34">
-        <v>0.6689574251601222</v>
-      </c>
-      <c r="AA34">
-        <v>-1.190534815969238</v>
-      </c>
-      <c r="AB34">
-        <v>0.02528227270625561</v>
-      </c>
-      <c r="AC34">
-        <v>-1.215817088675494</v>
-      </c>
-      <c r="AD34">
-        <v>0.857</v>
-      </c>
-      <c r="AE34">
-        <v>0.04435881076517788</v>
-      </c>
-      <c r="AF34">
-        <v>0.9013588107651779</v>
-      </c>
-      <c r="AG34">
-        <v>-128.7986411892348</v>
-      </c>
-      <c r="AH34">
-        <v>0.09466703531286631</v>
-      </c>
-      <c r="AI34">
-        <v>0.04461872189928379</v>
-      </c>
-      <c r="AJ34">
-        <v>1.071726555689932</v>
-      </c>
-      <c r="AK34">
-        <v>1.176257894987444</v>
-      </c>
-      <c r="AL34">
-        <v>0.04</v>
-      </c>
-      <c r="AM34">
-        <v>0.004000000000000004</v>
-      </c>
-      <c r="AN34">
-        <v>-0.07895706651925556</v>
-      </c>
-      <c r="AO34">
-        <v>-275</v>
-      </c>
-      <c r="AP34">
-        <v>11.86646777125804</v>
-      </c>
-      <c r="AQ34">
-        <v>-2749.999999999998</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Senmiao Technology Limited (NasdaqCM:AIHS)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>-1.163265306122449</v>
-      </c>
-      <c r="H35">
-        <v>-1.163265306122449</v>
-      </c>
-      <c r="I35">
-        <v>-1.736719883258405</v>
-      </c>
-      <c r="J35">
-        <v>-1.736719883258405</v>
-      </c>
-      <c r="K35">
-        <v>-12</v>
-      </c>
-      <c r="L35">
-        <v>-1.440576230492197</v>
-      </c>
-      <c r="M35">
-        <v>-0</v>
-      </c>
-      <c r="N35">
-        <v>-0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>-0</v>
-      </c>
-      <c r="Q35">
-        <v>-0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>1.77</v>
-      </c>
-      <c r="V35">
-        <v>0.07729257641921398</v>
-      </c>
-      <c r="W35">
-        <v>-2.448979591836734</v>
-      </c>
-      <c r="X35">
-        <v>0.0269909509441762</v>
-      </c>
-      <c r="Y35">
-        <v>-2.475970542780911</v>
-      </c>
-      <c r="Z35">
-        <v>0.8119396544788031</v>
-      </c>
-      <c r="AA35">
-        <v>-1.410111741939297</v>
-      </c>
-      <c r="AB35">
-        <v>0.02720331096820462</v>
-      </c>
-      <c r="AC35">
-        <v>-1.437315052907501</v>
-      </c>
-      <c r="AD35">
-        <v>7.87</v>
-      </c>
-      <c r="AE35">
-        <v>1.049383137712566</v>
-      </c>
-      <c r="AF35">
-        <v>8.919383137712565</v>
-      </c>
-      <c r="AG35">
-        <v>7.149383137712565</v>
-      </c>
-      <c r="AH35">
-        <v>0.2803128866172533</v>
-      </c>
-      <c r="AI35">
-        <v>1.402554767429977</v>
-      </c>
-      <c r="AJ35">
-        <v>0.2379211281958048</v>
-      </c>
-      <c r="AK35">
-        <v>1.557809170248521</v>
-      </c>
-      <c r="AL35">
-        <v>0.55</v>
-      </c>
-      <c r="AM35">
-        <v>0.55</v>
-      </c>
-      <c r="AN35">
-        <v>-0.584825741249907</v>
-      </c>
-      <c r="AO35">
-        <v>-26.72727272727272</v>
-      </c>
-      <c r="AP35">
-        <v>-0.5312761490460404</v>
-      </c>
-      <c r="AQ35">
-        <v>-26.72727272727272</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Hithink RoyalFlush Information Network Co., Ltd. (SZSE:300033)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>0.125</v>
-      </c>
-      <c r="E36">
-        <v>0.103</v>
-      </c>
-      <c r="G36">
-        <v>0.70388814403371</v>
-      </c>
-      <c r="H36">
-        <v>0.4838153610419459</v>
-      </c>
-      <c r="I36">
-        <v>0.5451063014748133</v>
-      </c>
-      <c r="J36">
-        <v>0.5131113015755735</v>
-      </c>
-      <c r="K36">
-        <v>301.4</v>
-      </c>
-      <c r="L36">
-        <v>0.5772840452020686</v>
-      </c>
-      <c r="M36">
-        <v>107.1</v>
-      </c>
-      <c r="N36">
-        <v>0.008753361176268666</v>
-      </c>
-      <c r="O36">
-        <v>0.3553417385534174</v>
-      </c>
-      <c r="P36">
-        <v>107.1</v>
-      </c>
-      <c r="Q36">
-        <v>0.008753361176268666</v>
-      </c>
-      <c r="R36">
-        <v>0.3553417385534174</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>1022.2</v>
-      </c>
-      <c r="V36">
-        <v>0.08354515214175379</v>
-      </c>
-      <c r="W36">
-        <v>0.4766724656017713</v>
-      </c>
-      <c r="X36">
-        <v>0.02430267097692251</v>
-      </c>
-      <c r="Y36">
-        <v>0.4523697946248488</v>
-      </c>
-      <c r="Z36">
-        <v>-29.37436705299869</v>
-      </c>
-      <c r="AA36">
-        <v>-15.0723197115228</v>
-      </c>
-      <c r="AB36">
-        <v>0.02430267097692251</v>
-      </c>
-      <c r="AC36">
-        <v>-15.09662238249972</v>
-      </c>
-      <c r="AD36">
-        <v>0</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36">
-        <v>-1022.2</v>
-      </c>
-      <c r="AH36">
-        <v>0</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
-      <c r="AJ36">
-        <v>-0.09116123106009937</v>
-      </c>
-      <c r="AK36">
-        <v>6.44514501891551</v>
-      </c>
-      <c r="AL36">
-        <v>0.09</v>
-      </c>
-      <c r="AM36">
-        <v>-28.01</v>
-      </c>
-      <c r="AN36">
-        <v>0</v>
-      </c>
-      <c r="AO36">
-        <v>3162.222222222223</v>
-      </c>
-      <c r="AP36">
-        <v>-3.509097150703742</v>
-      </c>
-      <c r="AQ36">
-        <v>-10.16065690824706</v>
+        <v>4.440154440154441</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09705</v>
+        <v>0.0318</v>
       </c>
       <c r="E2">
-        <v>0.1285</v>
+        <v>-0.0214</v>
       </c>
       <c r="F2">
-        <v>0.209</v>
+        <v>0.144</v>
       </c>
       <c r="G2">
-        <v>0.02950827904728575</v>
+        <v>0.1074166410604523</v>
       </c>
       <c r="H2">
-        <v>-0.004879859261688828</v>
+        <v>0.06879063583800876</v>
       </c>
       <c r="I2">
-        <v>-0.04705235186745236</v>
+        <v>-0.005627680436357421</v>
       </c>
       <c r="J2">
-        <v>-0.03984908628244688</v>
+        <v>-0.004868990622372314</v>
       </c>
       <c r="K2">
-        <v>2318.291</v>
+        <v>543.197</v>
       </c>
       <c r="L2">
-        <v>0.1819092106068476</v>
+        <v>0.03324912867459378</v>
       </c>
       <c r="M2">
-        <v>3749.3293</v>
+        <v>3103.7892</v>
       </c>
       <c r="N2">
-        <v>0.05298911055647105</v>
+        <v>0.03967052820217801</v>
       </c>
       <c r="O2">
-        <v>1.617281566464262</v>
+        <v>5.713929200639916</v>
       </c>
       <c r="P2">
-        <v>3066.9543</v>
+        <v>2141.6572</v>
       </c>
       <c r="Q2">
-        <v>0.04334513388150363</v>
+        <v>0.02737320960843527</v>
       </c>
       <c r="R2">
-        <v>1.322937586351325</v>
+        <v>3.942689668757375</v>
       </c>
       <c r="S2">
-        <v>682.375</v>
+        <v>962.1319999999999</v>
       </c>
       <c r="T2">
-        <v>0.1819992178334403</v>
+        <v>0.3099862580873727</v>
       </c>
       <c r="U2">
-        <v>25517.969</v>
+        <v>25883.915</v>
       </c>
       <c r="V2">
-        <v>0.3606443639179949</v>
+        <v>0.3308306440367402</v>
       </c>
       <c r="W2">
-        <v>0.05064261420389173</v>
+        <v>0.02994326380690017</v>
       </c>
       <c r="X2">
-        <v>0.05360988815958427</v>
+        <v>0.05514857767979778</v>
       </c>
       <c r="Y2">
-        <v>-0.002967273955692545</v>
+        <v>-0.02520531387289762</v>
       </c>
       <c r="Z2">
-        <v>0.09783591774518501</v>
+        <v>0.1189515638833702</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05084166475712444</v>
+        <v>0.05240495747670604</v>
       </c>
       <c r="AC2">
-        <v>-0.0503393639490503</v>
+        <v>-0.05009738575259369</v>
       </c>
       <c r="AD2">
-        <v>121235.439</v>
+        <v>128688.418</v>
       </c>
       <c r="AE2">
-        <v>0.9176185811185392</v>
+        <v>0.6971413562489661</v>
       </c>
       <c r="AF2">
-        <v>121236.3566185811</v>
+        <v>128689.1151413562</v>
       </c>
       <c r="AG2">
-        <v>95718.38761858112</v>
+        <v>102805.2001413562</v>
       </c>
       <c r="AH2">
-        <v>0.6314625221352929</v>
+        <v>0.6219020036504267</v>
       </c>
       <c r="AI2">
-        <v>0.7265985803184357</v>
+        <v>0.7288983567124284</v>
       </c>
       <c r="AJ2">
-        <v>0.5749715857488822</v>
+        <v>0.5678453301866705</v>
       </c>
       <c r="AK2">
-        <v>0.6772366696246057</v>
+        <v>0.6823249221233552</v>
       </c>
       <c r="AL2">
-        <v>784.89</v>
+        <v>719.987</v>
       </c>
       <c r="AM2">
-        <v>-90.25599999999997</v>
+        <v>-237.673</v>
       </c>
       <c r="AN2">
-        <v>-288.9915878449246</v>
+        <v>564.395656349913</v>
       </c>
       <c r="AO2">
-        <v>-0.7646421791588631</v>
+        <v>-0.1283509285584322</v>
       </c>
       <c r="AP2">
-        <v>-228.1660300982597</v>
+        <v>450.8782477220671</v>
       </c>
       <c r="AQ2">
-        <v>6.64953022513739</v>
+        <v>0.3888157258081479</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hithink RoyalFlush Information Network Co., Ltd. (SZSE:300033)</t>
+          <t>Lakala Payment Co., Ltd. (SZSE:300773)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,50 +724,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.188</v>
-      </c>
-      <c r="E3">
-        <v>0.134</v>
-      </c>
-      <c r="F3">
-        <v>0.305</v>
-      </c>
       <c r="G3">
-        <v>0.8952776131199368</v>
+        <v>0.1403673414666846</v>
       </c>
       <c r="H3">
-        <v>0.6022525192649674</v>
+        <v>0.09652768467623006</v>
       </c>
       <c r="I3">
-        <v>0.4706579727326615</v>
+        <v>0.05724627966215311</v>
       </c>
       <c r="J3">
-        <v>0.4322891162598901</v>
+        <v>0.05724627966215311</v>
       </c>
       <c r="K3">
-        <v>253.4</v>
+        <v>-168.6</v>
       </c>
       <c r="L3">
-        <v>0.5006915629322268</v>
+        <v>-0.2260356616168387</v>
       </c>
       <c r="M3">
-        <v>136</v>
+        <v>3.84</v>
       </c>
       <c r="N3">
-        <v>0.01769427928338169</v>
+        <v>0.002176747349923474</v>
       </c>
       <c r="O3">
-        <v>0.5367008681925809</v>
+        <v>-0.02277580071174377</v>
       </c>
       <c r="P3">
-        <v>136</v>
+        <v>3.84</v>
       </c>
       <c r="Q3">
-        <v>0.01769427928338169</v>
+        <v>0.002176747349923474</v>
       </c>
       <c r="R3">
-        <v>0.5367008681925809</v>
+        <v>-0.02277580071174377</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,64 +767,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>956.1</v>
+        <v>926.5</v>
       </c>
       <c r="V3">
-        <v>0.1243933854620679</v>
+        <v>0.5251969842979424</v>
       </c>
       <c r="W3">
-        <v>0.293422880963409</v>
+        <v>-0.2305168170631665</v>
       </c>
       <c r="X3">
-        <v>0.05005624910221628</v>
+        <v>0.05261755652616062</v>
       </c>
       <c r="Y3">
-        <v>0.2433666318611927</v>
+        <v>-0.2831343735893271</v>
       </c>
       <c r="AB3">
-        <v>0.05005617042465565</v>
+        <v>0.05234202078306532</v>
       </c>
       <c r="AD3">
-        <v>0.259</v>
+        <v>57.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.259</v>
+        <v>57.6</v>
       </c>
       <c r="AG3">
-        <v>-955.841</v>
+        <v>-868.9</v>
       </c>
       <c r="AH3">
-        <v>3.369605817266667e-05</v>
+        <v>0.03161881758796729</v>
       </c>
       <c r="AI3">
-        <v>0.0002857902652552968</v>
+        <v>0.09696969696969697</v>
       </c>
       <c r="AJ3">
-        <v>-0.142021428893004</v>
+        <v>-0.97062109025916</v>
       </c>
       <c r="AK3">
-        <v>19.17780542123954</v>
+        <v>2.613233082706767</v>
       </c>
       <c r="AL3">
-        <v>0.007</v>
+        <v>3.85</v>
       </c>
       <c r="AM3">
-        <v>-25.593</v>
+        <v>-22.75</v>
       </c>
       <c r="AN3">
-        <v>0.001053273688491257</v>
+        <v>0.8834355828220859</v>
       </c>
       <c r="AO3">
-        <v>34028.57142857143</v>
+        <v>11.09090909090909</v>
       </c>
       <c r="AP3">
-        <v>-3.887112647417649</v>
+        <v>-13.32668711656442</v>
       </c>
       <c r="AQ3">
-        <v>-9.307232446372055</v>
+        <v>-1.876923076923077</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Beijing Compass Technology Development Co., Ltd. (SZSE:300803)</t>
+          <t>JF Wealth Holdings Ltd (SEHK:9636)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,122 +843,98 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.138</v>
-      </c>
-      <c r="E4">
-        <v>0.123</v>
-      </c>
       <c r="G4">
-        <v>0.2449091909741332</v>
+        <v>0.392109500805153</v>
       </c>
       <c r="H4">
-        <v>0.1419922949917446</v>
+        <v>0.2439613526570048</v>
       </c>
       <c r="I4">
-        <v>0.2575674188222344</v>
+        <v>0.07809983896940417</v>
       </c>
       <c r="J4">
-        <v>0.2282305892652618</v>
+        <v>0.07809983896940417</v>
       </c>
       <c r="K4">
-        <v>45.9</v>
+        <v>27.9</v>
       </c>
       <c r="L4">
-        <v>0.2526141992294992</v>
+        <v>0.1123188405797101</v>
       </c>
       <c r="M4">
-        <v>0.844</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0003128591021981688</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.01838779956427015</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.844</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0003128591021981688</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.01838779956427015</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>81.2</v>
+        <v>112.2</v>
       </c>
       <c r="V4">
-        <v>0.03009971457167217</v>
-      </c>
-      <c r="W4">
-        <v>0.2333502796136248</v>
+        <v>0.1580281690140845</v>
       </c>
       <c r="X4">
-        <v>0.05006610363650001</v>
-      </c>
-      <c r="Y4">
-        <v>0.1832841759771248</v>
-      </c>
-      <c r="Z4">
-        <v>3.135786276404805</v>
-      </c>
-      <c r="AA4">
-        <v>0.7156823496737897</v>
+        <v>0.05258788890136161</v>
       </c>
       <c r="AB4">
-        <v>0.05006329088771976</v>
-      </c>
-      <c r="AC4">
-        <v>0.66561905878607</v>
+        <v>0.05239501687469292</v>
       </c>
       <c r="AD4">
-        <v>3.24</v>
+        <v>21.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.24</v>
+        <v>21.1</v>
       </c>
       <c r="AG4">
-        <v>-77.96000000000001</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.001199582367620162</v>
+        <v>0.02886062098208179</v>
       </c>
       <c r="AI4">
-        <v>0.01358832410669351</v>
+        <v>0.1109942135718043</v>
       </c>
       <c r="AJ4">
-        <v>-0.02975867834212556</v>
+        <v>-0.1471966391985781</v>
       </c>
       <c r="AK4">
-        <v>-0.4958025947596033</v>
+        <v>-1.169448010269576</v>
       </c>
       <c r="AL4">
-        <v>0.868</v>
+        <v>0.3</v>
       </c>
       <c r="AM4">
-        <v>-5.662</v>
+        <v>-0.627</v>
       </c>
       <c r="AN4">
-        <v>0.06585365853658537</v>
+        <v>1.004761904761905</v>
       </c>
       <c r="AO4">
-        <v>53.91705069124423</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="AP4">
-        <v>-1.584552845528455</v>
+        <v>-4.338095238095238</v>
       </c>
       <c r="AQ4">
-        <v>-8.265630519251147</v>
+        <v>-30.94098883572568</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Art Financial Holdings Limited (SEHK:1572)</t>
+          <t>Hithink RoyalFlush Information Network Co., Ltd. (SZSE:300033)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,118 +954,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.286</v>
+        <v>0.224</v>
       </c>
       <c r="E5">
-        <v>-0.273</v>
+        <v>0.225</v>
+      </c>
+      <c r="F5">
+        <v>0.156</v>
       </c>
       <c r="G5">
-        <v>0.7332268370607029</v>
+        <v>0.7838323353293413</v>
       </c>
       <c r="H5">
-        <v>0.7332268370607029</v>
+        <v>0.4684630738522954</v>
       </c>
       <c r="I5">
-        <v>0.7523961661341854</v>
+        <v>0.3758483033932136</v>
       </c>
       <c r="J5">
-        <v>0.5372249260995491</v>
+        <v>0.3557986781138205</v>
       </c>
       <c r="K5">
-        <v>3.83</v>
+        <v>216.5</v>
       </c>
       <c r="L5">
-        <v>0.6118210862619808</v>
+        <v>0.4321357285429142</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>166.8</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.01402482090606397</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.7704387990762125</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>166.8</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01402482090606397</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.7704387990762125</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>128.2</v>
+        <v>958.6</v>
       </c>
       <c r="V5">
-        <v>3.427807486631016</v>
+        <v>0.08060067937981368</v>
       </c>
       <c r="W5">
-        <v>0.02316999395039322</v>
+        <v>0.238962472406181</v>
       </c>
       <c r="X5">
-        <v>0.05029974354454146</v>
+        <v>0.05228738606473404</v>
       </c>
       <c r="Y5">
-        <v>-0.02712974959414824</v>
-      </c>
-      <c r="Z5">
-        <v>0.2526230831315577</v>
-      </c>
-      <c r="AA5">
-        <v>0.1357154171663913</v>
+        <v>0.186675086341447</v>
       </c>
       <c r="AB5">
-        <v>0.05143774545902023</v>
-      </c>
-      <c r="AC5">
-        <v>0.08427767170737109</v>
+        <v>0.05228729371714223</v>
       </c>
       <c r="AD5">
-        <v>1.08</v>
+        <v>0.131</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.08</v>
+        <v>0.131</v>
       </c>
       <c r="AG5">
-        <v>-127.12</v>
+        <v>-958.4690000000001</v>
       </c>
       <c r="AH5">
-        <v>0.02806652806652807</v>
+        <v>1.101457615196281e-05</v>
       </c>
       <c r="AI5">
-        <v>0.006574141709276845</v>
+        <v>0.0001425724643596048</v>
       </c>
       <c r="AJ5">
-        <v>1.416852429781543</v>
+        <v>-0.08765364232554053</v>
       </c>
       <c r="AK5">
-        <v>-3.523281596452328</v>
+        <v>24.10090774221127</v>
       </c>
       <c r="AL5">
-        <v>0.033</v>
+        <v>0.012</v>
       </c>
       <c r="AM5">
-        <v>-0.401</v>
+        <v>-25.688</v>
       </c>
       <c r="AN5">
-        <v>0.2273684210526316</v>
+        <v>0.0006687085247575294</v>
       </c>
       <c r="AO5">
-        <v>142.7272727272727</v>
+        <v>15691.66666666667</v>
       </c>
       <c r="AP5">
-        <v>-26.76210526315789</v>
+        <v>-4.892644206227668</v>
       </c>
       <c r="AQ5">
-        <v>-11.74563591022444</v>
+        <v>-7.330270943631268</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Panda Financial Holding Corp., Ltd. (SHSE:600599)</t>
+          <t>Shenglong Splendecor International Limited (SEHK:8481)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,121 +1082,103 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.009990000000000001</v>
+        <v>0.0781</v>
       </c>
       <c r="E6">
-        <v>0.224</v>
+        <v>0.297</v>
       </c>
       <c r="G6">
-        <v>0.2863157894736842</v>
+        <v>0.1287591240875912</v>
       </c>
       <c r="H6">
-        <v>0.2863157894736842</v>
+        <v>0.09737226277372263</v>
       </c>
       <c r="I6">
-        <v>0.2610526315789474</v>
+        <v>0.06583941605839416</v>
       </c>
       <c r="J6">
-        <v>0.202226387887527</v>
+        <v>0.0596438530304273</v>
       </c>
       <c r="K6">
-        <v>11.3</v>
+        <v>3.23</v>
       </c>
       <c r="L6">
-        <v>0.2378947368421053</v>
+        <v>0.04715328467153285</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.002999702999703</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.08938053097345132</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>1.01</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.002999702999703</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.08938053097345132</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.06296406296406297</v>
-      </c>
-      <c r="W6">
-        <v>0.105904404873477</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>0.05037438774727347</v>
-      </c>
-      <c r="Y6">
-        <v>0.05553001712620358</v>
-      </c>
-      <c r="Z6">
-        <v>0.6152849740932642</v>
-      </c>
-      <c r="AA6">
-        <v>0.1244268578323515</v>
+        <v>0.06855134113098504</v>
       </c>
       <c r="AB6">
-        <v>0.05027795434745962</v>
-      </c>
-      <c r="AC6">
-        <v>0.07414890348489184</v>
+        <v>0.05335478001104496</v>
       </c>
       <c r="AD6">
-        <v>12.7</v>
+        <v>32.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12.7</v>
+        <v>32.8</v>
       </c>
       <c r="AG6">
-        <v>-8.5</v>
+        <v>32.8</v>
       </c>
       <c r="AH6">
-        <v>0.0363480251860332</v>
+        <v>0.6165413533834586</v>
       </c>
       <c r="AI6">
-        <v>0.1052195526097763</v>
+        <v>0.5038402457757296</v>
       </c>
       <c r="AJ6">
-        <v>-0.0258988421694089</v>
+        <v>0.6165413533834586</v>
       </c>
       <c r="AK6">
-        <v>-0.08542713567839195</v>
+        <v>0.5038402457757296</v>
       </c>
       <c r="AL6">
-        <v>0.806</v>
+        <v>1.33</v>
       </c>
       <c r="AM6">
-        <v>-0.3739999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AN6">
-        <v>1.016</v>
+        <v>3.706214689265537</v>
       </c>
       <c r="AO6">
-        <v>15.38461538461538</v>
+        <v>3.390977443609022</v>
       </c>
       <c r="AP6">
-        <v>-0.68</v>
+        <v>3.706214689265537</v>
       </c>
       <c r="AQ6">
-        <v>-33.15508021390375</v>
+        <v>3.390977443609022</v>
       </c>
     </row>
     <row r="7">
@@ -1243,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SY Holdings Group Limited (SEHK:6069)</t>
+          <t>Rendong Holdings Co., Ltd. (SZSE:002647)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,121 +1198,106 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.382</v>
-      </c>
-      <c r="E7">
-        <v>0.6629999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="G7">
-        <v>0.5577350859453993</v>
+        <v>0.1670907548770144</v>
       </c>
       <c r="H7">
-        <v>0.5237613751263902</v>
+        <v>0.1191687871077184</v>
       </c>
       <c r="I7">
-        <v>0.614762386248736</v>
+        <v>0.02124681933842239</v>
       </c>
       <c r="J7">
-        <v>0.5763620111076918</v>
+        <v>0.02124681933842239</v>
       </c>
       <c r="K7">
-        <v>62.5</v>
+        <v>-25</v>
       </c>
       <c r="L7">
-        <v>0.6319514661274014</v>
+        <v>-0.1060220525869381</v>
       </c>
       <c r="M7">
-        <v>10.0893</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.01245131432802666</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.1614288</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>9.0693</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.0111925212884117</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.1451088</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.02</v>
-      </c>
-      <c r="T7">
-        <v>0.1010972019862626</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>143.1</v>
+        <v>362.3</v>
       </c>
       <c r="V7">
-        <v>0.1766012587930396</v>
+        <v>0.6620979532163742</v>
       </c>
       <c r="W7">
-        <v>0.1323872061004024</v>
+        <v>-0.6793478260869565</v>
       </c>
       <c r="X7">
-        <v>0.05756862299469619</v>
+        <v>0.05452221366017351</v>
       </c>
       <c r="Y7">
-        <v>0.07481858310570624</v>
-      </c>
-      <c r="Z7">
-        <v>0.1314460393407762</v>
-      </c>
-      <c r="AA7">
-        <v>0.07576050358659055</v>
+        <v>-0.7338700397471301</v>
       </c>
       <c r="AB7">
-        <v>0.05293176601415059</v>
-      </c>
-      <c r="AC7">
-        <v>0.02282873757243996</v>
+        <v>0.05181178922903882</v>
       </c>
       <c r="AD7">
-        <v>721.1</v>
+        <v>120.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>721.1</v>
+        <v>120.9</v>
       </c>
       <c r="AG7">
-        <v>578</v>
+        <v>-241.4</v>
       </c>
       <c r="AH7">
-        <v>0.4708763223194463</v>
+        <v>0.1809609339919174</v>
       </c>
       <c r="AI7">
-        <v>0.5427517687791661</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="AJ7">
-        <v>0.4163365266873154</v>
+        <v>-0.7894048397645519</v>
       </c>
       <c r="AK7">
-        <v>0.4875579924082665</v>
+        <v>1.068614431164232</v>
       </c>
       <c r="AL7">
-        <v>29.5</v>
+        <v>24.6</v>
       </c>
       <c r="AM7">
-        <v>27.77</v>
+        <v>23.21</v>
       </c>
       <c r="AN7">
-        <v>11.70616883116883</v>
+        <v>4.257042253521127</v>
       </c>
       <c r="AO7">
-        <v>2.061016949152542</v>
+        <v>0.2036585365853658</v>
       </c>
       <c r="AP7">
-        <v>9.383116883116882</v>
+        <v>-8.5</v>
       </c>
       <c r="AQ7">
-        <v>2.189413035649982</v>
+        <v>0.2158552348125808</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>China Huirong Financial Holdings Limited (SEHK:1290)</t>
+          <t>Shenzhen Asia Link Technology Development Co.,Ltd. (SZSE:002316)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,121 +1317,109 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.19</v>
-      </c>
-      <c r="E8">
-        <v>0.09789999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="G8">
-        <v>0.2854209445585216</v>
+        <v>0.108645336963921</v>
       </c>
       <c r="H8">
-        <v>0.2854209445585216</v>
+        <v>0.0878148400272294</v>
       </c>
       <c r="I8">
-        <v>0.2720739219712526</v>
+        <v>0.01272974812797822</v>
       </c>
       <c r="J8">
-        <v>0.1896127509068377</v>
+        <v>0.01272974812797822</v>
       </c>
       <c r="K8">
-        <v>13.5</v>
+        <v>-9.84</v>
       </c>
       <c r="L8">
-        <v>0.1386036960985626</v>
+        <v>-0.06698434309053777</v>
       </c>
       <c r="M8">
-        <v>5.57</v>
+        <v>1.8</v>
       </c>
       <c r="N8">
-        <v>0.04194277108433735</v>
+        <v>0.006232686980609419</v>
       </c>
       <c r="O8">
-        <v>0.4125925925925926</v>
+        <v>-0.1829268292682927</v>
       </c>
       <c r="P8">
-        <v>5.57</v>
+        <v>0.03</v>
       </c>
       <c r="Q8">
-        <v>0.04194277108433735</v>
+        <v>0.0001038781163434903</v>
       </c>
       <c r="R8">
-        <v>0.4125925925925926</v>
+        <v>-0.003048780487804878</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="U8">
-        <v>55.9</v>
+        <v>18.2</v>
       </c>
       <c r="V8">
-        <v>0.420933734939759</v>
+        <v>0.06301939058171745</v>
       </c>
       <c r="W8">
-        <v>0.04856115107913669</v>
+        <v>0.826890756302521</v>
       </c>
       <c r="X8">
-        <v>0.05622216513542601</v>
+        <v>0.05233315846647502</v>
       </c>
       <c r="Y8">
-        <v>-0.007661014056289314</v>
-      </c>
-      <c r="Z8">
-        <v>0.3051378446115289</v>
-      </c>
-      <c r="AA8">
-        <v>0.05785802612257516</v>
+        <v>0.7745575978360459</v>
       </c>
       <c r="AB8">
-        <v>0.05019624702646572</v>
-      </c>
-      <c r="AC8">
-        <v>0.00766177909610944</v>
+        <v>0.05230413197958714</v>
       </c>
       <c r="AD8">
-        <v>97</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>97</v>
+        <v>1.31</v>
       </c>
       <c r="AG8">
-        <v>41.1</v>
+        <v>-16.89</v>
       </c>
       <c r="AH8">
-        <v>0.4221061792863359</v>
+        <v>0.004515528592602806</v>
       </c>
       <c r="AI8">
-        <v>0.2384464110127827</v>
+        <v>0.09218859957776214</v>
       </c>
       <c r="AJ8">
-        <v>0.2363427257044278</v>
+        <v>-0.06211614137030635</v>
       </c>
       <c r="AK8">
-        <v>0.1171273867198632</v>
+        <v>4.233082706766917</v>
       </c>
       <c r="AL8">
-        <v>4.1</v>
+        <v>1.17</v>
       </c>
       <c r="AM8">
-        <v>4.1</v>
+        <v>1.067</v>
       </c>
       <c r="AN8">
-        <v>3.646616541353383</v>
+        <v>0.6238095238095238</v>
       </c>
       <c r="AO8">
-        <v>6.463414634146342</v>
+        <v>1.598290598290598</v>
       </c>
       <c r="AP8">
-        <v>1.545112781954887</v>
+        <v>-8.042857142857143</v>
       </c>
       <c r="AQ8">
-        <v>6.463414634146342</v>
+        <v>1.752577319587629</v>
       </c>
     </row>
     <row r="9">
@@ -1511,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SPIC Industry-Finance Holdings Co., Ltd. (SZSE:000958)</t>
+          <t>Metropolis Capital Holdings Limited (SEHK:8621)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1520,121 +1439,106 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.168</v>
+        <v>0.0284</v>
       </c>
       <c r="E9">
-        <v>0.6840000000000001</v>
+        <v>-0.228</v>
       </c>
       <c r="G9">
-        <v>0.5444230986552153</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0.5427731947112668</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.2940445248050627</v>
+        <v>0.05903521486872901</v>
       </c>
       <c r="J9">
-        <v>0.2513060909104265</v>
+        <v>0.05903521486872901</v>
       </c>
       <c r="K9">
-        <v>193.6</v>
+        <v>0.282</v>
       </c>
       <c r="L9">
-        <v>0.2187817832523449</v>
+        <v>0.05529411764705882</v>
       </c>
       <c r="M9">
-        <v>611.1</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1755479589784838</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>3.15650826446281</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>181.1</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.05202378558501623</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.9354338842975206</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>430</v>
-      </c>
-      <c r="T9">
-        <v>0.7036491572574046</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>351.7</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>0.1010312832150757</v>
-      </c>
-      <c r="W9">
-        <v>0.07090276506134408</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>0.0546740595110899</v>
-      </c>
-      <c r="Y9">
-        <v>0.01622870555025417</v>
+        <v>0.07640786183101425</v>
       </c>
       <c r="Z9">
-        <v>0.2087274442740889</v>
+        <v>14.58801636111247</v>
       </c>
       <c r="AA9">
-        <v>0.05245447808624518</v>
+        <v>0.8612066803868088</v>
       </c>
       <c r="AB9">
-        <v>0.05221554532758464</v>
+        <v>0.05491744933387177</v>
       </c>
       <c r="AC9">
-        <v>0.0002389327586605414</v>
+        <v>0.806289231052937</v>
       </c>
       <c r="AD9">
-        <v>1904.3</v>
+        <v>10.5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>0.3496020208474101</v>
       </c>
       <c r="AF9">
-        <v>1904.3</v>
+        <v>10.84960202084741</v>
       </c>
       <c r="AG9">
-        <v>1552.6</v>
+        <v>10.84960202084741</v>
       </c>
       <c r="AH9">
-        <v>0.3536041891038735</v>
+        <v>0.7045378189747774</v>
       </c>
       <c r="AI9">
-        <v>0.3372651116660468</v>
+        <v>0.2743289809876813</v>
       </c>
       <c r="AJ9">
-        <v>0.3084411069392296</v>
+        <v>0.7045378189747774</v>
       </c>
       <c r="AK9">
-        <v>0.2932421712688399</v>
+        <v>0.2743289809876813</v>
       </c>
       <c r="AL9">
-        <v>95.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>-65.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>5.039163799947076</v>
-      </c>
-      <c r="AO9">
-        <v>2.736067297581493</v>
+        <v>28.30188679245283</v>
       </c>
       <c r="AP9">
-        <v>4.108494310664197</v>
-      </c>
-      <c r="AQ9">
-        <v>-3.966463414634147</v>
+        <v>29.24421029878008</v>
       </c>
     </row>
     <row r="10">
@@ -1645,7 +1549,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bairong Inc. (SEHK:6608)</t>
+          <t>Zero2IPO Holdings Inc. (SEHK:1945)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1654,31 +1558,31 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.2691292875989446</v>
+        <v>0.1792507204610951</v>
       </c>
       <c r="H10">
-        <v>0.10139464756879</v>
+        <v>0.09740634005763688</v>
       </c>
       <c r="I10">
-        <v>0.0336600075386355</v>
+        <v>0.1017291066282421</v>
       </c>
       <c r="J10">
-        <v>0.0336600075386355</v>
+        <v>0.08511695996075784</v>
       </c>
       <c r="K10">
-        <v>20.6</v>
+        <v>4.87</v>
       </c>
       <c r="L10">
-        <v>0.07764794572182435</v>
+        <v>0.1403458213256484</v>
       </c>
       <c r="M10">
-        <v>25.2</v>
+        <v>1.32</v>
       </c>
       <c r="N10">
-        <v>0.03819339193695059</v>
+        <v>0.03062645011600928</v>
       </c>
       <c r="O10">
-        <v>1.223300970873786</v>
+        <v>0.271047227926078</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1690,79 +1594,79 @@
         <v>-0</v>
       </c>
       <c r="S10">
-        <v>25.2</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
         <v>1</v>
       </c>
       <c r="U10">
-        <v>174.5</v>
+        <v>7.85</v>
       </c>
       <c r="V10">
-        <v>0.2644740830554714</v>
+        <v>0.1821345707656613</v>
       </c>
       <c r="W10">
-        <v>0.03199254542630844</v>
+        <v>0.065633423180593</v>
       </c>
       <c r="X10">
-        <v>0.05026963689118975</v>
+        <v>0.05391138034008325</v>
       </c>
       <c r="Y10">
-        <v>-0.01827709146488132</v>
+        <v>0.01172204284050975</v>
       </c>
       <c r="Z10">
-        <v>1.167539497425516</v>
+        <v>1.983990851915379</v>
       </c>
       <c r="AA10">
-        <v>0.03929938828499759</v>
+        <v>0.1688712699049912</v>
       </c>
       <c r="AB10">
-        <v>0.05020672969165312</v>
+        <v>0.05280374178059028</v>
       </c>
       <c r="AC10">
-        <v>-0.01090734140665552</v>
+        <v>0.1160675281244009</v>
       </c>
       <c r="AD10">
-        <v>16.7</v>
+        <v>6.92</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>16.7</v>
+        <v>6.92</v>
       </c>
       <c r="AG10">
-        <v>-157.8</v>
+        <v>-0.9299999999999997</v>
       </c>
       <c r="AH10">
-        <v>0.02468588322246859</v>
+        <v>0.1383446621351459</v>
       </c>
       <c r="AI10">
-        <v>0.02585539557206997</v>
+        <v>0.08345393150024119</v>
       </c>
       <c r="AJ10">
-        <v>-0.3143426294820718</v>
+        <v>-0.02205359260137538</v>
       </c>
       <c r="AK10">
-        <v>-0.3347475604582096</v>
+        <v>-0.01238843745837218</v>
       </c>
       <c r="AL10">
-        <v>1.54</v>
+        <v>0.218</v>
       </c>
       <c r="AM10">
-        <v>-7.329999999999999</v>
+        <v>-1.452</v>
       </c>
       <c r="AN10">
-        <v>1.325396825396825</v>
+        <v>1.76530612244898</v>
       </c>
       <c r="AO10">
-        <v>5.798701298701299</v>
+        <v>16.19266055045872</v>
       </c>
       <c r="AP10">
-        <v>-12.52380952380953</v>
+        <v>-0.2372448979591836</v>
       </c>
       <c r="AQ10">
-        <v>-1.218281036834925</v>
+        <v>-2.431129476584022</v>
       </c>
     </row>
     <row r="11">
@@ -1773,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shanghai Aj Group Co.,Ltd (SHSE:600643)</t>
+          <t>Momentum Financial Holdings Limited (SEHK:1152)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1782,121 +1686,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.103</v>
-      </c>
-      <c r="E11">
-        <v>-0.0223</v>
+        <v>0.459</v>
       </c>
       <c r="G11">
-        <v>0.6640295358649789</v>
+        <v>0.03013698630136986</v>
       </c>
       <c r="H11">
-        <v>0.6618143459915612</v>
+        <v>0.03013698630136986</v>
       </c>
       <c r="I11">
-        <v>0.3662447257383966</v>
+        <v>0.05902864259028643</v>
       </c>
       <c r="J11">
-        <v>0.262814502265979</v>
+        <v>0.0517184729449993</v>
       </c>
       <c r="K11">
-        <v>93.09999999999999</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>0.1964135021097046</v>
+        <v>0.04981320049813201</v>
       </c>
       <c r="M11">
-        <v>137.44</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.1065178640626211</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>1.476262083780881</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>128.2</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.099356738742928</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>1.377013963480129</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>9.240000000000009</v>
-      </c>
-      <c r="T11">
-        <v>0.06722933643771835</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>242</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
-        <v>0.1875532821824382</v>
+        <v>0.1557377049180328</v>
       </c>
       <c r="W11">
-        <v>0.04843408594319009</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="X11">
-        <v>0.06084151316364127</v>
+        <v>0.06837250793292994</v>
       </c>
       <c r="Y11">
-        <v>-0.01240742722045118</v>
+        <v>0.3356678961074741</v>
       </c>
       <c r="Z11">
-        <v>0.1260554484409281</v>
+        <v>2.986462362392145</v>
       </c>
       <c r="AA11">
-        <v>0.03312919993991732</v>
+        <v>0.1544552728906368</v>
       </c>
       <c r="AB11">
-        <v>0.05024238801339388</v>
+        <v>0.05457917077246247</v>
       </c>
       <c r="AC11">
-        <v>-0.01711318807347656</v>
+        <v>0.09987610211817438</v>
       </c>
       <c r="AD11">
-        <v>1648.5</v>
+        <v>19.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1648.5</v>
+        <v>19.4</v>
       </c>
       <c r="AG11">
-        <v>1406.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH11">
-        <v>0.5609432421396489</v>
+        <v>0.6139240506329113</v>
       </c>
       <c r="AI11">
-        <v>0.4768171694675035</v>
+        <v>0.5914634146341463</v>
       </c>
       <c r="AJ11">
-        <v>0.5215440522100266</v>
+        <v>0.5892255892255892</v>
       </c>
       <c r="AK11">
-        <v>0.4374397412372096</v>
+        <v>0.5663430420711975</v>
       </c>
       <c r="AL11">
-        <v>38</v>
+        <v>0.095</v>
       </c>
       <c r="AM11">
-        <v>32.83</v>
+        <v>0.093</v>
       </c>
       <c r="AN11">
-        <v>7.864980916030534</v>
+        <v>4.024896265560166</v>
       </c>
       <c r="AO11">
-        <v>4.568421052631579</v>
+        <v>49.89473684210527</v>
       </c>
       <c r="AP11">
-        <v>6.710400763358779</v>
+        <v>3.630705394190871</v>
       </c>
       <c r="AQ11">
-        <v>5.287846481876333</v>
+        <v>50.96774193548387</v>
       </c>
     </row>
     <row r="12">
@@ -1907,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minsheng Holdings Co.,Ltd (SZSE:000416)</t>
+          <t>Tungkong Inc. (SZSE:002117)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1916,43 +1814,46 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.19</v>
+        <v>-0.0493</v>
+      </c>
+      <c r="E12">
+        <v>-0.105</v>
       </c>
       <c r="G12">
-        <v>0.5584</v>
+        <v>0.2243488794669897</v>
       </c>
       <c r="H12">
-        <v>0.5584</v>
+        <v>0.1659600242277408</v>
       </c>
       <c r="I12">
-        <v>0.2224</v>
+        <v>0.1235614778921865</v>
       </c>
       <c r="J12">
-        <v>0.1112</v>
+        <v>0.1092681374410989</v>
       </c>
       <c r="K12">
-        <v>-0.326</v>
+        <v>20.6</v>
       </c>
       <c r="L12">
-        <v>-0.05216</v>
+        <v>0.1247728649303453</v>
       </c>
       <c r="M12">
-        <v>1.74</v>
+        <v>16.7</v>
       </c>
       <c r="N12">
-        <v>0.005876393110435663</v>
+        <v>0.02538379692962456</v>
       </c>
       <c r="O12">
-        <v>-5.337423312883435</v>
+        <v>0.8106796116504853</v>
       </c>
       <c r="P12">
-        <v>1.74</v>
+        <v>16.7</v>
       </c>
       <c r="Q12">
-        <v>0.005876393110435663</v>
+        <v>0.02538379692962456</v>
       </c>
       <c r="R12">
-        <v>-5.337423312883435</v>
+        <v>0.8106796116504853</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1961,70 +1862,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.13</v>
+        <v>15.5</v>
       </c>
       <c r="V12">
-        <v>0.02070246538331644</v>
+        <v>0.02355981152150783</v>
       </c>
       <c r="W12">
-        <v>-0.0023589001447178</v>
+        <v>0.09626168224299066</v>
       </c>
       <c r="X12">
-        <v>0.05011298572882499</v>
+        <v>0.05235461876705623</v>
       </c>
       <c r="Y12">
-        <v>-0.05247188587354279</v>
+        <v>0.04390706347593443</v>
       </c>
       <c r="Z12">
-        <v>0.04638563158675968</v>
+        <v>0.8313987743036846</v>
       </c>
       <c r="AA12">
-        <v>0.005158082232447676</v>
+        <v>0.09084539553897614</v>
       </c>
       <c r="AB12">
-        <v>0.05009693973450365</v>
+        <v>0.05226989724424256</v>
       </c>
       <c r="AC12">
-        <v>-0.04493885750205597</v>
+        <v>0.03857549829473358</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>4.38</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>4.38</v>
       </c>
       <c r="AG12">
-        <v>-4.13</v>
+        <v>-11.12</v>
       </c>
       <c r="AH12">
-        <v>0.006709158000670915</v>
+        <v>0.006613516941474905</v>
       </c>
       <c r="AI12">
-        <v>0.015527950310559</v>
+        <v>0.02033615006035844</v>
       </c>
       <c r="AJ12">
-        <v>-0.01414528889954447</v>
+        <v>-0.01719286310646588</v>
       </c>
       <c r="AK12">
-        <v>-0.03366756338142985</v>
+        <v>-0.05563338002801681</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="AM12">
-        <v>-1.87</v>
+        <v>-1.821</v>
       </c>
       <c r="AN12">
-        <v>1.092896174863388</v>
+        <v>0.1564285714285714</v>
+      </c>
+      <c r="AO12">
+        <v>120.7100591715976</v>
       </c>
       <c r="AP12">
-        <v>-2.256830601092896</v>
+        <v>-0.3971428571428572</v>
       </c>
       <c r="AQ12">
-        <v>-0.7433155080213902</v>
+        <v>-11.20263591433278</v>
       </c>
     </row>
     <row r="13">
@@ -2035,7 +1939,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolis Capital Holdings Limited (SEHK:8621)</t>
+          <t>Panda Financial Holding Corp., Ltd. (SHSE:600599)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2043,107 +1947,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D13">
+        <v>-0.0366</v>
+      </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.344927536231884</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.344927536231884</v>
       </c>
       <c r="I13">
-        <v>0.09212346417184436</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="J13">
-        <v>0.09212346417184436</v>
+        <v>0.2447241291634884</v>
       </c>
       <c r="K13">
-        <v>-0.333</v>
+        <v>8.75</v>
       </c>
       <c r="L13">
-        <v>-0.1534562211981567</v>
+        <v>0.2536231884057971</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.002361151497528352</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>0.09280000000000001</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.002361151497528352</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>0.09280000000000001</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.1474265774934574</v>
       </c>
       <c r="W13">
-        <v>-0.01030959752321981</v>
+        <v>0.08101851851851852</v>
       </c>
       <c r="X13">
-        <v>0.05068763368966726</v>
+        <v>0.05262259362895932</v>
       </c>
       <c r="Y13">
-        <v>-0.06099723121288708</v>
+        <v>0.0283959248895592</v>
       </c>
       <c r="Z13">
-        <v>0.05274612821969066</v>
+        <v>0.3467336683417085</v>
       </c>
       <c r="AA13">
-        <v>0.004859156053250182</v>
+        <v>0.08485409503658645</v>
       </c>
       <c r="AB13">
-        <v>0.05067953713219175</v>
+        <v>0.05234282892289988</v>
       </c>
       <c r="AC13">
-        <v>-0.04582038107894157</v>
+        <v>0.03251126611368657</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AE13">
-        <v>0.2304604137354888</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.2304604137354888</v>
+        <v>11.4</v>
       </c>
       <c r="AG13">
-        <v>0.2304604137354888</v>
+        <v>-39.3</v>
       </c>
       <c r="AH13">
-        <v>0.06961581923145235</v>
+        <v>0.03208556149732621</v>
       </c>
       <c r="AI13">
-        <v>1</v>
+        <v>0.09069212410501193</v>
       </c>
       <c r="AJ13">
-        <v>0.06961581923145235</v>
+        <v>-0.129021667760998</v>
       </c>
       <c r="AK13">
-        <v>1</v>
+        <v>-0.524</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.036363636363636</v>
+      </c>
+      <c r="AO13">
+        <v>15.06849315068493</v>
       </c>
       <c r="AP13">
-        <v>0.9368309501442633</v>
+        <v>-3.572727272727273</v>
+      </c>
+      <c r="AQ13">
+        <v>21.61100196463654</v>
       </c>
     </row>
     <row r="14">
@@ -2154,7 +2070,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baiying Holdings Group Limited (SEHK:8525)</t>
+          <t>Bairong Inc. (SEHK:6608)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2162,32 +2078,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="F14">
+        <v>0.144</v>
+      </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.2334258402713536</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.05827937095282146</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.09867406722170829</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.09772663068528183</v>
       </c>
       <c r="K14">
-        <v>-2.9</v>
+        <v>47.7</v>
       </c>
       <c r="L14">
-        <v>-0.8605341246290801</v>
+        <v>0.1470860314523589</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>29.7</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.0363080684596577</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2196,61 +2115,82 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>29.7</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>0.07493887530562347</v>
       </c>
       <c r="W14">
-        <v>-0.0651685393258427</v>
+        <v>0.07617374640689875</v>
       </c>
       <c r="X14">
-        <v>0.05005596463140148</v>
+        <v>0.0525469623913708</v>
       </c>
       <c r="Y14">
-        <v>-0.1152245039572442</v>
+        <v>0.02362678401552795</v>
       </c>
       <c r="Z14">
-        <v>0.07269197584124246</v>
+        <v>0.7345413363533407</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.07178424990087631</v>
       </c>
       <c r="AB14">
-        <v>0.05005596463140148</v>
+        <v>0.05233061227918183</v>
       </c>
       <c r="AC14">
-        <v>-0.05005596463140148</v>
+        <v>0.01945363762169448</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>-40.3</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.02502979737783075</v>
+      </c>
+      <c r="AI14">
+        <v>0.03347680535628886</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>-0.05181946766105181</v>
+      </c>
+      <c r="AK14">
+        <v>-0.07120141342756184</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>-9.33</v>
+      </c>
+      <c r="AN14">
+        <v>0.5898876404494382</v>
+      </c>
+      <c r="AO14">
+        <v>16.24365482233502</v>
+      </c>
+      <c r="AP14">
+        <v>-1.132022471910112</v>
+      </c>
+      <c r="AQ14">
+        <v>-3.429796355841372</v>
       </c>
     </row>
     <row r="15">
@@ -2261,7 +2201,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yangzhou Guangling District Taihe Rural Micro-finance Company Limited (SEHK:1915)</t>
+          <t>Shaanxi Jinye Science Technology and Education Group Co.,Ltd (SZSE:000812)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2269,86 +2209,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D15">
+        <v>0.0626</v>
+      </c>
+      <c r="E15">
+        <v>0.0203</v>
+      </c>
+      <c r="G15">
+        <v>0.2070724637681159</v>
+      </c>
+      <c r="H15">
+        <v>0.1750724637681159</v>
+      </c>
+      <c r="I15">
+        <v>0.1171014492753623</v>
+      </c>
+      <c r="J15">
+        <v>0.1085351609909331</v>
+      </c>
       <c r="K15">
-        <v>-1.96</v>
+        <v>6.81</v>
+      </c>
+      <c r="L15">
+        <v>0.03947826086956521</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>8.66</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.01578851412944394</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.271659324522761</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>8.66</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.01578851412944394</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.271659324522761</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>0.079</v>
+        <v>35.5</v>
       </c>
       <c r="V15">
-        <v>0.0004796599878567092</v>
+        <v>0.06472196900638104</v>
       </c>
       <c r="W15">
-        <v>-0.01409058231488138</v>
+        <v>0.02814049586776859</v>
       </c>
       <c r="X15">
-        <v>0.05006647224865757</v>
+        <v>0.0559221996680189</v>
       </c>
       <c r="Y15">
-        <v>-0.06415705456353894</v>
+        <v>-0.02778170380025031</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>0.5833615150490361</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.06331523595176176</v>
       </c>
       <c r="AB15">
-        <v>0.05006709985785952</v>
+        <v>0.05274498272678162</v>
       </c>
       <c r="AC15">
-        <v>-0.05006709985785952</v>
+        <v>0.01057025322498014</v>
       </c>
       <c r="AD15">
-        <v>0.205</v>
+        <v>197.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.205</v>
+        <v>197.1</v>
       </c>
       <c r="AG15">
-        <v>0.126</v>
+        <v>161.6</v>
       </c>
       <c r="AH15">
-        <v>0.001243139989691034</v>
+        <v>0.2643508583690987</v>
       </c>
       <c r="AI15">
-        <v>0.001549450134159707</v>
+        <v>0.4391711229946524</v>
       </c>
       <c r="AJ15">
-        <v>0.0007644425030031671</v>
+        <v>0.2275735811857485</v>
       </c>
       <c r="AK15">
-        <v>0.0009529139503577209</v>
+        <v>0.3909992741350109</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>8.99</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>8.196</v>
+      </c>
+      <c r="AN15">
+        <v>6.083333333333333</v>
+      </c>
+      <c r="AO15">
+        <v>2.246941045606229</v>
+      </c>
+      <c r="AP15">
+        <v>4.987654320987654</v>
+      </c>
+      <c r="AQ15">
+        <v>2.464616886285993</v>
       </c>
     </row>
     <row r="16">
@@ -2359,7 +2335,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jiangsu Financial Leasing Co., Ltd. (SHSE:600901)</t>
+          <t>SY Holdings Group Limited (SEHK:6069)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2367,104 +2343,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.222</v>
+      </c>
+      <c r="E16">
+        <v>0.0885</v>
+      </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.6403830806065443</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.6089385474860335</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.6831604150039904</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.5256245321649328</v>
       </c>
       <c r="K16">
-        <v>326.3</v>
+        <v>31.2</v>
       </c>
       <c r="L16">
-        <v>0.6462665874430581</v>
+        <v>0.2490023942537909</v>
       </c>
       <c r="M16">
-        <v>188.6</v>
+        <v>27.4</v>
       </c>
       <c r="N16">
-        <v>0.07947075678408899</v>
+        <v>0.04450942170240416</v>
       </c>
       <c r="O16">
-        <v>0.577995709469813</v>
+        <v>0.8782051282051282</v>
       </c>
       <c r="P16">
-        <v>188.6</v>
+        <v>8.9</v>
       </c>
       <c r="Q16">
-        <v>0.07947075678408899</v>
+        <v>0.01445743989603639</v>
       </c>
       <c r="R16">
-        <v>0.577995709469813</v>
+        <v>0.2852564102564103</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.6751824817518248</v>
       </c>
       <c r="U16">
-        <v>312.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V16">
-        <v>0.1317630203944042</v>
+        <v>0.1379142300194932</v>
       </c>
       <c r="W16">
-        <v>0.1533725029377203</v>
+        <v>0.05391394504924831</v>
       </c>
       <c r="X16">
-        <v>0.09171126278268701</v>
+        <v>0.06723369888830283</v>
       </c>
       <c r="Y16">
-        <v>0.06166124015503333</v>
+        <v>-0.01331975383905452</v>
       </c>
       <c r="Z16">
-        <v>0.03935123844559101</v>
+        <v>0.1129337539432176</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.0593607515820334</v>
       </c>
       <c r="AB16">
-        <v>0.05033230073859365</v>
+        <v>0.05072024927584592</v>
       </c>
       <c r="AC16">
-        <v>-0.05033230073859365</v>
+        <v>0.008640502306187479</v>
       </c>
       <c r="AD16">
-        <v>11710.1</v>
+        <v>909.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>11710.1</v>
+        <v>909.6</v>
       </c>
       <c r="AG16">
-        <v>11397.4</v>
+        <v>824.7</v>
       </c>
       <c r="AH16">
-        <v>0.8314883585523281</v>
+        <v>0.5963808025177026</v>
       </c>
       <c r="AI16">
-        <v>0.8441232654532348</v>
+        <v>0.6198296422487223</v>
       </c>
       <c r="AJ16">
-        <v>0.8276618302760955</v>
+        <v>0.5725890439491772</v>
       </c>
       <c r="AK16">
-        <v>0.8405286213660969</v>
+        <v>0.5964848835527268</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>43.89</v>
+      </c>
+      <c r="AN16">
+        <v>10.52777777777778</v>
+      </c>
+      <c r="AO16">
+        <v>1.73630831643002</v>
+      </c>
+      <c r="AP16">
+        <v>9.545138888888889</v>
+      </c>
+      <c r="AQ16">
+        <v>1.950330371383003</v>
       </c>
     </row>
     <row r="17">
@@ -2475,7 +2469,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AVIC Industry-Finance Holdings Co., Ltd. (SHSE:600705)</t>
+          <t>China Huirong Financial Holdings Limited (SEHK:1290)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2484,46 +2478,46 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.08359999999999999</v>
+        <v>0.203</v>
       </c>
       <c r="E17">
-        <v>0.0538</v>
+        <v>-0.0214</v>
       </c>
       <c r="G17">
-        <v>0.007565550834283345</v>
+        <v>0.1906392694063927</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.1906392694063927</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.1395985982797069</v>
       </c>
       <c r="K17">
-        <v>477.7</v>
+        <v>6.97</v>
       </c>
       <c r="L17">
-        <v>0.2475386050367914</v>
+        <v>0.0795662100456621</v>
       </c>
       <c r="M17">
-        <v>1729.8</v>
+        <v>4.3612</v>
       </c>
       <c r="N17">
-        <v>0.4119061793070604</v>
+        <v>0.03359938366718027</v>
       </c>
       <c r="O17">
-        <v>3.621101109482939</v>
+        <v>0.6257101865136299</v>
       </c>
       <c r="P17">
-        <v>1729.8</v>
+        <v>4.3612</v>
       </c>
       <c r="Q17">
-        <v>0.4119061793070604</v>
+        <v>0.03359938366718027</v>
       </c>
       <c r="R17">
-        <v>3.621101109482939</v>
+        <v>0.6257101865136299</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2532,64 +2526,73 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>7497.4</v>
+        <v>39.6</v>
       </c>
       <c r="V17">
-        <v>1.785307774735087</v>
+        <v>0.3050847457627118</v>
       </c>
       <c r="W17">
-        <v>0.07380911914216405</v>
+        <v>0.02524447663889895</v>
       </c>
       <c r="X17">
-        <v>0.09427425578709009</v>
+        <v>0.05975307343894674</v>
       </c>
       <c r="Y17">
-        <v>-0.02046513664492604</v>
+        <v>-0.03450859680004779</v>
       </c>
       <c r="Z17">
-        <v>0.07379862131417991</v>
+        <v>0.2761664564943253</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.03855245021848148</v>
       </c>
       <c r="AB17">
-        <v>0.05033502642416218</v>
+        <v>0.05117149409648716</v>
       </c>
       <c r="AC17">
-        <v>-0.05033502642416218</v>
+        <v>-0.01261904387800568</v>
       </c>
       <c r="AD17">
-        <v>21996.6</v>
+        <v>95.8</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>21996.6</v>
+        <v>95.8</v>
       </c>
       <c r="AG17">
-        <v>14499.2</v>
+        <v>56.2</v>
       </c>
       <c r="AH17">
-        <v>0.8396898775008493</v>
+        <v>0.4246453900709219</v>
       </c>
       <c r="AI17">
-        <v>0.6878881696219157</v>
+        <v>0.2450127877237852</v>
       </c>
       <c r="AJ17">
-        <v>0.7754121944306289</v>
+        <v>0.3021505376344086</v>
       </c>
       <c r="AK17">
-        <v>0.5922972597591464</v>
+        <v>0.1599317017643711</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AM17">
-        <v>-456.7</v>
+        <v>4.75</v>
+      </c>
+      <c r="AN17">
+        <v>5.668639053254438</v>
+      </c>
+      <c r="AO17">
+        <v>3.536842105263158</v>
+      </c>
+      <c r="AP17">
+        <v>3.325443786982249</v>
       </c>
       <c r="AQ17">
-        <v>-0</v>
+        <v>3.536842105263158</v>
       </c>
     </row>
     <row r="18">
@@ -2600,7 +2603,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Genertec Universal Medical Group Company Limited (SEHK:2666)</t>
+          <t>Yeahka Limited (SEHK:9923)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2608,110 +2611,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.271</v>
-      </c>
-      <c r="E18">
-        <v>0.134</v>
-      </c>
       <c r="G18">
-        <v>0.002398907814328436</v>
+        <v>0.09616474589079919</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.02871717362554317</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>0.02134895144530512</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.01849816331817756</v>
       </c>
       <c r="K18">
-        <v>296.7</v>
+        <v>15.4</v>
       </c>
       <c r="L18">
-        <v>0.1928877909244572</v>
+        <v>0.02909503117324769</v>
       </c>
       <c r="M18">
-        <v>86.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="N18">
-        <v>0.07513696843203757</v>
+        <v>0.07542758705549403</v>
       </c>
       <c r="O18">
-        <v>0.2912032355915066</v>
+        <v>3.98051948051948</v>
       </c>
       <c r="P18">
-        <v>86.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.07513696843203757</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.2912032355915066</v>
+        <v>-0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>549.3</v>
+        <v>182.5</v>
       </c>
       <c r="V18">
-        <v>0.4776937124967388</v>
+        <v>0.2245601082810385</v>
       </c>
       <c r="W18">
-        <v>0.1316793893129771</v>
+        <v>0.03455238949966345</v>
       </c>
       <c r="X18">
-        <v>0.1045165678329815</v>
+        <v>0.05440321843510886</v>
       </c>
       <c r="Y18">
-        <v>0.02716282147999562</v>
+        <v>-0.01985082893544541</v>
       </c>
       <c r="Z18">
-        <v>0.1739297587010109</v>
+        <v>2.001891074130106</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>0.03703130803446059</v>
       </c>
       <c r="AB18">
-        <v>0.05034370147393842</v>
+        <v>0.05258680153814094</v>
       </c>
       <c r="AC18">
-        <v>-0.05034370147393842</v>
+        <v>-0.01555549350368035</v>
       </c>
       <c r="AD18">
-        <v>7418.2</v>
+        <v>170</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>7418.2</v>
+        <v>170</v>
       </c>
       <c r="AG18">
-        <v>6868.9</v>
+        <v>-12.5</v>
       </c>
       <c r="AH18">
-        <v>0.8657928829028606</v>
+        <v>0.172992775007632</v>
       </c>
       <c r="AI18">
-        <v>0.7311596916950857</v>
+        <v>0.3126149319602796</v>
       </c>
       <c r="AJ18">
-        <v>0.8565994911956901</v>
+        <v>-0.01562109472631842</v>
       </c>
       <c r="AK18">
-        <v>0.7157713749804616</v>
+        <v>-0.0345972875726543</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>6.040000000000001</v>
+      </c>
+      <c r="AN18">
+        <v>8.457711442786069</v>
+      </c>
+      <c r="AO18">
+        <v>1</v>
+      </c>
+      <c r="AP18">
+        <v>-0.6218905472636815</v>
+      </c>
+      <c r="AQ18">
+        <v>1.870860927152318</v>
       </c>
     </row>
     <row r="19">
@@ -2722,7 +2731,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Anhui Xinli Finance Co., Ltd. (SHSE:600318)</t>
+          <t>SPIC Industry-Finance Holdings Co., Ltd. (SZSE:000958)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2731,43 +2740,46 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.121</v>
+        <v>0.173</v>
+      </c>
+      <c r="E19">
+        <v>0.376</v>
       </c>
       <c r="G19">
-        <v>0.02926208651399491</v>
+        <v>0.4483996592430327</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.4450529390288426</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>0.2279420713155653</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>0.1660613217789058</v>
       </c>
       <c r="K19">
-        <v>-43.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="L19">
-        <v>-1.114503816793893</v>
+        <v>0.114518680783741</v>
       </c>
       <c r="M19">
-        <v>1.59</v>
+        <v>156.6</v>
       </c>
       <c r="N19">
-        <v>0.003164179104477612</v>
+        <v>0.05235182027880854</v>
       </c>
       <c r="O19">
-        <v>-0.0363013698630137</v>
+        <v>1.664187035069076</v>
       </c>
       <c r="P19">
-        <v>1.59</v>
+        <v>156.6</v>
       </c>
       <c r="Q19">
-        <v>0.003164179104477612</v>
+        <v>0.05235182027880854</v>
       </c>
       <c r="R19">
-        <v>-0.0363013698630137</v>
+        <v>1.664187035069076</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2776,67 +2788,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>46.2</v>
+        <v>331.6</v>
       </c>
       <c r="V19">
-        <v>0.09194029850746269</v>
+        <v>0.1108548122889714</v>
       </c>
       <c r="W19">
-        <v>-0.2030598052851182</v>
+        <v>0.036121454070861</v>
       </c>
       <c r="X19">
-        <v>0.05254571680807864</v>
+        <v>0.05762889008855361</v>
       </c>
       <c r="Y19">
-        <v>-0.2556055220931969</v>
+        <v>-0.02150743601769261</v>
       </c>
       <c r="Z19">
-        <v>0.1350979718116191</v>
+        <v>0.2013526427993825</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>0.03343688600694134</v>
       </c>
       <c r="AB19">
-        <v>0.05144693997671509</v>
+        <v>0.05137924970490338</v>
       </c>
       <c r="AC19">
-        <v>-0.05144693997671509</v>
+        <v>-0.01794236369796205</v>
       </c>
       <c r="AD19">
-        <v>148.2</v>
+        <v>1579.6</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>148.2</v>
+        <v>1579.6</v>
       </c>
       <c r="AG19">
-        <v>102</v>
+        <v>1248</v>
       </c>
       <c r="AH19">
-        <v>0.2277547256800369</v>
+        <v>0.3455774573935111</v>
       </c>
       <c r="AI19">
-        <v>0.3041247691360558</v>
+        <v>0.2876445415642356</v>
       </c>
       <c r="AJ19">
-        <v>0.1687344913151365</v>
+        <v>0.2943882244710211</v>
       </c>
       <c r="AK19">
-        <v>0.2312400816141464</v>
+        <v>0.2418651524254346</v>
       </c>
       <c r="AL19">
-        <v>0.5679999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="AM19">
-        <v>0.5679999999999999</v>
+        <v>-28.40000000000001</v>
+      </c>
+      <c r="AN19">
+        <v>4.967295597484276</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>2.722383720930233</v>
+      </c>
+      <c r="AP19">
+        <v>3.924528301886792</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>-6.59507042253521</v>
       </c>
     </row>
     <row r="20">
@@ -2847,7 +2865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>East Money Information Co.,Ltd. (SZSE:300059)</t>
+          <t>Shanghai NAR Industrial Co., Ltd (SZSE:002825)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2856,115 +2874,121 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.403</v>
+        <v>0.122</v>
       </c>
       <c r="E20">
-        <v>0.718</v>
-      </c>
-      <c r="F20">
-        <v>0.113</v>
+        <v>-0.181</v>
       </c>
       <c r="G20">
-        <v>0.07534857780256553</v>
+        <v>0.1478494623655914</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.09301075268817205</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.02338709677419355</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.02187463782113193</v>
       </c>
       <c r="K20">
-        <v>1252.8</v>
+        <v>3.08</v>
       </c>
       <c r="L20">
-        <v>0.6987172336865588</v>
+        <v>0.01655913978494624</v>
       </c>
       <c r="M20">
-        <v>262.6</v>
+        <v>11.49</v>
       </c>
       <c r="N20">
-        <v>0.007065236400227078</v>
+        <v>0.0279086713626427</v>
       </c>
       <c r="O20">
-        <v>0.2096104725415071</v>
+        <v>3.73051948051948</v>
       </c>
       <c r="P20">
-        <v>262.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q20">
-        <v>0.007065236400227078</v>
+        <v>0.02526111246052951</v>
       </c>
       <c r="R20">
-        <v>0.2096104725415071</v>
+        <v>3.376623376623377</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.09486510008703218</v>
       </c>
       <c r="U20">
-        <v>7963</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="V20">
-        <v>0.2142440116336947</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="W20">
-        <v>0.1968016588645575</v>
+        <v>0.01549295774647887</v>
       </c>
       <c r="X20">
-        <v>0.05208319754046637</v>
+        <v>0.05321110545736187</v>
       </c>
       <c r="Y20">
-        <v>0.1447184613240911</v>
+        <v>-0.03771814771088299</v>
       </c>
       <c r="Z20">
-        <v>0.269510582010582</v>
+        <v>1.249160510409671</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>0.02732493374567185</v>
       </c>
       <c r="AB20">
-        <v>0.05209542241720233</v>
+        <v>0.05243217160851077</v>
       </c>
       <c r="AC20">
-        <v>-0.05209542241720233</v>
+        <v>-0.02510723786283892</v>
       </c>
       <c r="AD20">
-        <v>8925.4</v>
+        <v>37.6</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>8925.4</v>
+        <v>37.6</v>
       </c>
       <c r="AG20">
-        <v>962.3999999999996</v>
+        <v>-35.99999999999999</v>
       </c>
       <c r="AH20">
-        <v>0.1936376870391141</v>
+        <v>0.08368573336300912</v>
       </c>
       <c r="AI20">
-        <v>0.5002746482820469</v>
+        <v>0.1649846423870119</v>
       </c>
       <c r="AJ20">
-        <v>0.02523976994673526</v>
+        <v>-0.09582113388341761</v>
       </c>
       <c r="AK20">
-        <v>0.09742862927718157</v>
+        <v>-0.2333117303953337</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.827</v>
       </c>
       <c r="AM20">
-        <v>-198.6</v>
+        <v>0.827</v>
+      </c>
+      <c r="AN20">
+        <v>4.051724137931035</v>
+      </c>
+      <c r="AO20">
+        <v>5.259975816203144</v>
+      </c>
+      <c r="AP20">
+        <v>-3.879310344827586</v>
       </c>
       <c r="AQ20">
-        <v>-0</v>
+        <v>5.259975816203144</v>
       </c>
     </row>
     <row r="21">
@@ -2975,7 +2999,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Differ Group Auto Limited (SEHK:6878)</t>
+          <t>Shanghai Eliansy Industry Group Corporation Limited (SHSE:600836)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2984,46 +3008,43 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.391</v>
-      </c>
-      <c r="E21">
-        <v>0.246</v>
+        <v>-0.18</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.1387323943661972</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.1215492957746479</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>0.04366197183098592</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>0.04366197183098592</v>
       </c>
       <c r="K21">
-        <v>70.59999999999999</v>
+        <v>-5.82</v>
       </c>
       <c r="L21">
-        <v>0.3418886198547215</v>
+        <v>-0.0819718309859155</v>
       </c>
       <c r="M21">
-        <v>4.57</v>
+        <v>4.03</v>
       </c>
       <c r="N21">
-        <v>0.003340154948107002</v>
+        <v>0.01115416551342375</v>
       </c>
       <c r="O21">
-        <v>0.06473087818696885</v>
+        <v>-0.6924398625429553</v>
       </c>
       <c r="P21">
-        <v>4.57</v>
+        <v>4.03</v>
       </c>
       <c r="Q21">
-        <v>0.003340154948107002</v>
+        <v>0.01115416551342375</v>
       </c>
       <c r="R21">
-        <v>0.06473087818696885</v>
+        <v>-0.6924398625429553</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3032,61 +3053,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>8.890000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="V21">
-        <v>0.00649758807191931</v>
+        <v>0.2192084140603377</v>
       </c>
       <c r="W21">
-        <v>0.1944903581267217</v>
+        <v>-0.0327887323943662</v>
       </c>
       <c r="X21">
-        <v>0.05133750087643624</v>
+        <v>0.05448786927761158</v>
       </c>
       <c r="Y21">
-        <v>0.1431528572502855</v>
+        <v>-0.08727660167197779</v>
       </c>
       <c r="Z21">
-        <v>0.4010487473295786</v>
+        <v>0.5767668562144598</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>0.02518277822908205</v>
       </c>
       <c r="AB21">
-        <v>0.05235350688324462</v>
+        <v>0.05181779047238792</v>
       </c>
       <c r="AC21">
-        <v>-0.05235350688324462</v>
+        <v>-0.02663501224330587</v>
       </c>
       <c r="AD21">
-        <v>207.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>207.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AG21">
-        <v>198.81</v>
+        <v>-0.6000000000000085</v>
       </c>
       <c r="AH21">
-        <v>0.1317977028999302</v>
+        <v>0.1786769720390998</v>
       </c>
       <c r="AI21">
-        <v>0.3338691528693136</v>
+        <v>0.3305298570227082</v>
       </c>
       <c r="AJ21">
-        <v>0.1268721960931966</v>
+        <v>-0.001663432215137257</v>
       </c>
       <c r="AK21">
-        <v>0.3242119339214951</v>
+        <v>-0.003783102143757936</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="AN21">
+        <v>7.939393939393939</v>
+      </c>
+      <c r="AO21">
+        <v>0.8051948051948052</v>
+      </c>
+      <c r="AP21">
+        <v>-0.06060606060606147</v>
+      </c>
+      <c r="AQ21">
+        <v>1.2109375</v>
       </c>
     </row>
     <row r="22">
@@ -3097,7 +3130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yixin Group Limited (SEHK:2858)</t>
+          <t>Shanghai Aj Group Co.,Ltd (SHSE:600643)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3106,106 +3139,121 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0911</v>
+        <v>-0.0362</v>
+      </c>
+      <c r="E22">
+        <v>-0.229</v>
       </c>
       <c r="G22">
-        <v>0.04478120211135706</v>
+        <v>0.6461994076999014</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.6406712734452122</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.1997367555116815</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>0.1271923659098388</v>
       </c>
       <c r="K22">
-        <v>42.9</v>
+        <v>39.8</v>
       </c>
       <c r="L22">
-        <v>0.07304614336795505</v>
+        <v>0.1309641329384666</v>
       </c>
       <c r="M22">
-        <v>2.31</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N22">
-        <v>0.002846229669788073</v>
+        <v>0.0714963346269944</v>
       </c>
       <c r="O22">
-        <v>0.05384615384615385</v>
+        <v>2.082914572864322</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.0714963346269944</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>2.082914572864322</v>
       </c>
       <c r="S22">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>622.2</v>
+        <v>185.2</v>
       </c>
       <c r="V22">
-        <v>0.7666338097585017</v>
+        <v>0.1597240189736955</v>
       </c>
       <c r="W22">
-        <v>0.01922732162065257</v>
+        <v>0.02229067488098572</v>
       </c>
       <c r="X22">
-        <v>0.06699295995789639</v>
+        <v>0.06441709784647548</v>
       </c>
       <c r="Y22">
-        <v>-0.04776563833724383</v>
+        <v>-0.04212642296548976</v>
       </c>
       <c r="Z22">
-        <v>0.1933752592934049</v>
+        <v>0.09541121953057304</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>0.0121355787464366</v>
       </c>
       <c r="AB22">
-        <v>0.054131779330704</v>
+        <v>0.05085452937776092</v>
       </c>
       <c r="AC22">
-        <v>-0.054131779330704</v>
+        <v>-0.03871895063132431</v>
       </c>
       <c r="AD22">
-        <v>1628.3</v>
+        <v>1390.4</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>1628.3</v>
+        <v>1390.4</v>
       </c>
       <c r="AG22">
-        <v>1006.1</v>
+        <v>1205.2</v>
       </c>
       <c r="AH22">
-        <v>0.6673634165334644</v>
+        <v>0.5452762853445233</v>
       </c>
       <c r="AI22">
-        <v>0.4220033691849164</v>
+        <v>0.4423658171868537</v>
       </c>
       <c r="AJ22">
-        <v>0.5535016779446553</v>
+        <v>0.5096629593605955</v>
       </c>
       <c r="AK22">
-        <v>0.3108797083088712</v>
+        <v>0.407451232293181</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>23.24</v>
+      </c>
+      <c r="AN22">
+        <v>14.71322751322751</v>
+      </c>
+      <c r="AO22">
+        <v>2.003300330033003</v>
+      </c>
+      <c r="AP22">
+        <v>12.75343915343915</v>
+      </c>
+      <c r="AQ22">
+        <v>2.611876075731497</v>
       </c>
     </row>
     <row r="23">
@@ -3216,7 +3264,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zuoli Kechuang Micro-finance Company Limited (SEHK:6866)</t>
+          <t>China Art Financial Holdings Limited (SEHK:1572)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3225,109 +3273,118 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.0572</v>
+        <v>-0.457</v>
       </c>
       <c r="E23">
-        <v>-0.06309999999999999</v>
+        <v>-0.529</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1.534391534391534</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1.534391534391534</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.3857142857142857</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>0.2013061224489796</v>
       </c>
       <c r="K23">
-        <v>15</v>
+        <v>0.549</v>
       </c>
       <c r="L23">
-        <v>0.5859375</v>
+        <v>0.2904761904761905</v>
       </c>
       <c r="M23">
-        <v>8.26</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.1819383259911894</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.5506666666666666</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>8.26</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.1819383259911894</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.5506666666666666</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>4.36</v>
+        <v>119.3</v>
       </c>
       <c r="V23">
-        <v>0.0960352422907489</v>
+        <v>5.848039215686275</v>
       </c>
       <c r="W23">
-        <v>0.05272407732864675</v>
+        <v>0.003363970588235295</v>
       </c>
       <c r="X23">
-        <v>0.07210922573191164</v>
+        <v>0.05278313033156298</v>
       </c>
       <c r="Y23">
-        <v>-0.01938514840326489</v>
+        <v>-0.04941915974332768</v>
       </c>
       <c r="Z23">
-        <v>0.06475275072720374</v>
+        <v>0.05238359201773834</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>0.01054513778904022</v>
       </c>
       <c r="AB23">
-        <v>0.05447261352970116</v>
+        <v>0.05246172285299025</v>
       </c>
       <c r="AC23">
-        <v>-0.05447261352970116</v>
+        <v>-0.04191658506395003</v>
       </c>
       <c r="AD23">
-        <v>118.6</v>
+        <v>1</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>118.6</v>
+        <v>1</v>
       </c>
       <c r="AG23">
-        <v>114.24</v>
+        <v>-118.3</v>
       </c>
       <c r="AH23">
-        <v>0.723170731707317</v>
+        <v>0.04672897196261683</v>
       </c>
       <c r="AI23">
-        <v>0.3026282214850727</v>
+        <v>0.00657030223390276</v>
       </c>
       <c r="AJ23">
-        <v>0.7156101227762466</v>
+        <v>1.208375893769152</v>
       </c>
       <c r="AK23">
-        <v>0.294782474067193</v>
+        <v>-3.595744680851065</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>-0.389</v>
+      </c>
+      <c r="AN23">
+        <v>1.331557922769641</v>
+      </c>
+      <c r="AO23">
+        <v>104.1428571428571</v>
+      </c>
+      <c r="AP23">
+        <v>-157.5233022636485</v>
+      </c>
+      <c r="AQ23">
+        <v>-1.874035989717224</v>
       </c>
     </row>
     <row r="24">
@@ -3338,7 +3395,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
+          <t>Genertec Universal Medical Group Company Limited (SEHK:2666)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3347,13 +3404,13 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.186</v>
+        <v>0.265</v>
       </c>
       <c r="E24">
-        <v>0.183</v>
+        <v>0.0861</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.003879110699397869</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3365,28 +3422,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>606</v>
+        <v>271.9</v>
       </c>
       <c r="L24">
-        <v>0.2994367032315446</v>
+        <v>0.157422417786012</v>
       </c>
       <c r="M24">
-        <v>137.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N24">
-        <v>0.07982777680805259</v>
+        <v>0.07505518763796909</v>
       </c>
       <c r="O24">
-        <v>0.2264026402640264</v>
+        <v>0.3001103346818683</v>
       </c>
       <c r="P24">
-        <v>137.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>0.07982777680805259</v>
+        <v>0.07505518763796909</v>
       </c>
       <c r="R24">
-        <v>0.2264026402640264</v>
+        <v>0.3001103346818683</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3395,55 +3452,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>4554</v>
+        <v>346.1</v>
       </c>
       <c r="V24">
-        <v>2.649677081515099</v>
+        <v>0.3183406916850626</v>
       </c>
       <c r="W24">
-        <v>0.1409630146545708</v>
+        <v>0.1217208344525024</v>
       </c>
       <c r="X24">
-        <v>0.2655475664434029</v>
+        <v>0.1210132010398707</v>
       </c>
       <c r="Y24">
-        <v>-0.1245845517888321</v>
+        <v>0.0007076334126317335</v>
       </c>
       <c r="Z24">
-        <v>0.04875698361034887</v>
+        <v>0.1900653652309791</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.05448961369554494</v>
+        <v>0.04999683556721295</v>
       </c>
       <c r="AC24">
-        <v>-0.05448961369554494</v>
+        <v>-0.04999683556721295</v>
       </c>
       <c r="AD24">
-        <v>43871.9</v>
+        <v>7386.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>43871.9</v>
+        <v>7386.6</v>
       </c>
       <c r="AG24">
-        <v>39317.9</v>
+        <v>7040.5</v>
       </c>
       <c r="AH24">
-        <v>0.9623014393317921</v>
+        <v>0.8716986475961197</v>
       </c>
       <c r="AI24">
-        <v>0.900943619020238</v>
+        <v>0.7312741312741313</v>
       </c>
       <c r="AJ24">
-        <v>0.9581178752625705</v>
+        <v>0.8662352202960247</v>
       </c>
       <c r="AK24">
-        <v>0.8907241484770567</v>
+        <v>0.7217398435657977</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3460,7 +3517,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Roan Holdings Group Co., Ltd. (OTCPK:RAHG.F)</t>
+          <t>Zhongguancun Science-Tech Leasing Co., Ltd. (SEHK:1601)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3468,12 +3525,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D25">
-        <v>-0.288</v>
-      </c>
-      <c r="E25">
-        <v>-0.4</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3481,100 +3532,97 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.01208723058309487</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.008720423036062777</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>1.22</v>
+        <v>35.7</v>
       </c>
       <c r="L25">
-        <v>0.2791762013729977</v>
+        <v>0.534431137724551</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>15.7</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.1585858585858586</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.4397759103641456</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>15.7</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.1585858585858586</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.4397759103641456</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>1.04</v>
+        <v>69.8</v>
       </c>
       <c r="V25">
-        <v>0.3170731707317073</v>
+        <v>0.705050505050505</v>
       </c>
       <c r="W25">
-        <v>-0.1345093715545755</v>
+        <v>0.1135496183206107</v>
       </c>
       <c r="X25">
-        <v>0.06480598146890318</v>
+        <v>0.1115495420301905</v>
       </c>
       <c r="Y25">
-        <v>-0.1993153530234787</v>
+        <v>0.002000076290420191</v>
       </c>
       <c r="Z25">
-        <v>0.1185892148999252</v>
+        <v>0.066408191669152</v>
       </c>
       <c r="AA25">
-        <v>0.001034148121441907</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.0557527979358543</v>
+        <v>0.05004282125073742</v>
       </c>
       <c r="AC25">
-        <v>-0.0547186498144124</v>
+        <v>-0.05004282125073742</v>
       </c>
       <c r="AD25">
-        <v>5.67</v>
+        <v>580</v>
       </c>
       <c r="AE25">
-        <v>0.06089401175937712</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>5.730894011759377</v>
+        <v>580</v>
       </c>
       <c r="AG25">
-        <v>4.690894011759377</v>
+        <v>510.2</v>
       </c>
       <c r="AH25">
-        <v>0.635996162454076</v>
+        <v>0.8541973490427098</v>
       </c>
       <c r="AI25">
-        <v>0.09791229244863388</v>
+        <v>0.6431581281880684</v>
       </c>
       <c r="AJ25">
-        <v>0.5885028711759245</v>
+        <v>0.8374917925147733</v>
       </c>
       <c r="AK25">
-        <v>0.08159368700719606</v>
+        <v>0.6132211538461538</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-0.081</v>
-      </c>
-      <c r="AN25">
-        <v>87.23076923076923</v>
-      </c>
-      <c r="AP25">
-        <v>72.16760018091348</v>
+        <v>-1.21</v>
       </c>
       <c r="AQ25">
         <v>-0</v>
@@ -3588,7 +3636,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zhongguancun Science-Tech Leasing Co., Ltd. (SEHK:1601)</t>
+          <t>Jiangsu Financial Leasing Co., Ltd. (SHSE:600901)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3596,6 +3644,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.172</v>
+      </c>
+      <c r="E26">
+        <v>0.19</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3609,28 +3663,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>31.5</v>
+        <v>360</v>
       </c>
       <c r="L26">
-        <v>0.5311973018549747</v>
+        <v>0.6456241032998565</v>
       </c>
       <c r="M26">
-        <v>8.66</v>
+        <v>191.2</v>
       </c>
       <c r="N26">
-        <v>0.07787769784172661</v>
+        <v>0.06599019810864913</v>
       </c>
       <c r="O26">
-        <v>0.2749206349206349</v>
+        <v>0.5311111111111111</v>
       </c>
       <c r="P26">
-        <v>8.66</v>
+        <v>191.2</v>
       </c>
       <c r="Q26">
-        <v>0.07787769784172661</v>
+        <v>0.06599019810864913</v>
       </c>
       <c r="R26">
-        <v>0.2749206349206349</v>
+        <v>0.5311111111111111</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3639,55 +3693,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>70.2</v>
+        <v>533.7</v>
       </c>
       <c r="V26">
-        <v>0.6312949640287769</v>
+        <v>0.184199627252019</v>
       </c>
       <c r="W26">
-        <v>0.1040634291377602</v>
+        <v>0.1664816870144284</v>
       </c>
       <c r="X26">
-        <v>0.1078819645846738</v>
+        <v>0.09616839781496329</v>
       </c>
       <c r="Y26">
-        <v>-0.003818535446913629</v>
+        <v>0.0703132891994651</v>
       </c>
       <c r="Z26">
-        <v>0.06426790939633684</v>
+        <v>0.0411215504653461</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.05538528093992202</v>
+        <v>0.05015195025444996</v>
       </c>
       <c r="AC26">
-        <v>-0.05538528093992202</v>
+        <v>-0.05015195025444996</v>
       </c>
       <c r="AD26">
-        <v>761.7</v>
+        <v>12569</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>761.7</v>
+        <v>12569</v>
       </c>
       <c r="AG26">
-        <v>691.5</v>
+        <v>12035.3</v>
       </c>
       <c r="AH26">
-        <v>0.8726085462252262</v>
+        <v>0.8126648735323023</v>
       </c>
       <c r="AI26">
-        <v>0.7078338444382494</v>
+        <v>0.8419635321070189</v>
       </c>
       <c r="AJ26">
-        <v>0.8614675470287778</v>
+        <v>0.8059694495971927</v>
       </c>
       <c r="AK26">
-        <v>0.6874440799284223</v>
+        <v>0.836104067525791</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3704,7 +3758,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Haitong Unitrust International Financial Leasing Co., Ltd. (SEHK:1905)</t>
+          <t>Yangzhou Guangling District Taihe Rural Micro-finance Company Limited (SEHK:1915)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3713,10 +3767,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0329</v>
-      </c>
-      <c r="E27">
-        <v>0.0653</v>
+        <v>-0.169</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3731,94 +3782,88 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>213.7</v>
+        <v>-2.64</v>
       </c>
       <c r="L27">
-        <v>0.4041225416036309</v>
+        <v>-0.4791288566243195</v>
       </c>
       <c r="M27">
-        <v>313.3</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.348964134551125</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>1.466073935423491</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>104.4</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.1162842503898418</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.4885353299017314</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>208.9</v>
-      </c>
-      <c r="T27">
-        <v>0.6667730609639323</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1034.1</v>
+        <v>0.275</v>
       </c>
       <c r="V27">
-        <v>1.151815549120071</v>
+        <v>0.006626506024096386</v>
       </c>
       <c r="W27">
-        <v>0.07860952731285635</v>
+        <v>-0.01889763779527559</v>
       </c>
       <c r="X27">
-        <v>0.1641815164727743</v>
+        <v>0.05231067425507102</v>
       </c>
       <c r="Y27">
-        <v>-0.08557198915991794</v>
+        <v>-0.07120831205034661</v>
       </c>
       <c r="Z27">
-        <v>0.06791241250882937</v>
+        <v>0.03967025450880163</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.05574265403189646</v>
+        <v>0.05229589053210158</v>
       </c>
       <c r="AC27">
-        <v>-0.05574265403189646</v>
+        <v>-0.05229589053210158</v>
       </c>
       <c r="AD27">
-        <v>12137.2</v>
+        <v>0.096</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>12137.2</v>
+        <v>0.096</v>
       </c>
       <c r="AG27">
-        <v>11103.1</v>
+        <v>-0.179</v>
       </c>
       <c r="AH27">
-        <v>0.9311238971998467</v>
+        <v>0.002307914222521397</v>
       </c>
       <c r="AI27">
-        <v>0.8274667812024897</v>
+        <v>0.0008020318139286192</v>
       </c>
       <c r="AJ27">
-        <v>0.9251889441625212</v>
+        <v>-0.00433193775562063</v>
       </c>
       <c r="AK27">
-        <v>0.8143804368554622</v>
+        <v>-0.001498898853635458</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-3.07</v>
-      </c>
-      <c r="AQ27">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3829,7 +3874,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>51 Credit Card Inc. (SEHK:2051)</t>
+          <t>Quanzhou Huixin Micro-credit Co., Ltd. (SEHK:1577)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3837,116 +3882,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D28">
+        <v>-0.0121</v>
+      </c>
+      <c r="E28">
+        <v>-0.047</v>
+      </c>
       <c r="G28">
-        <v>0.06361111111111112</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>-0.03458333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>-0.1066666666666667</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>-0.1066666666666667</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>-9.369999999999999</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-0.1301388888888889</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M28">
-        <v>0.025</v>
+        <v>4.69</v>
       </c>
       <c r="N28">
-        <v>0.0007936507936507937</v>
+        <v>0.107816091954023</v>
       </c>
       <c r="O28">
-        <v>-0.002668089647812167</v>
+        <v>0.469</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>4.69</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>0.107816091954023</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="S28">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>52.5</v>
+        <v>11.2</v>
       </c>
       <c r="V28">
-        <v>1.666666666666667</v>
+        <v>0.2574712643678161</v>
       </c>
       <c r="W28">
-        <v>-0.07349019607843137</v>
+        <v>0.06146281499692687</v>
       </c>
       <c r="X28">
-        <v>0.05914113608388982</v>
+        <v>0.05261515494347631</v>
       </c>
       <c r="Y28">
-        <v>-0.1326313321623212</v>
+        <v>0.008847660053450557</v>
       </c>
       <c r="Z28">
-        <v>0.6328557616243298</v>
+        <v>0.1071647274954072</v>
       </c>
       <c r="AA28">
-        <v>-0.06750461457326183</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06737261288949242</v>
+        <v>0.05240448239924893</v>
       </c>
       <c r="AC28">
-        <v>-0.1348772274627543</v>
+        <v>-0.05240448239924893</v>
       </c>
       <c r="AD28">
-        <v>33.9</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>33.9</v>
+        <v>1.41</v>
       </c>
       <c r="AG28">
-        <v>-18.6</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="AH28">
-        <v>0.5183486238532109</v>
+        <v>0.03139612558450234</v>
       </c>
       <c r="AI28">
-        <v>0.2281292059219381</v>
+        <v>0.00817343922091473</v>
       </c>
       <c r="AJ28">
-        <v>-1.441860465116279</v>
+        <v>-0.2904182735093443</v>
       </c>
       <c r="AK28">
-        <v>-0.1935483870967742</v>
+        <v>-0.06069059574731882</v>
       </c>
       <c r="AL28">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1.353</v>
-      </c>
-      <c r="AN28">
-        <v>-5.905923344947735</v>
-      </c>
-      <c r="AO28">
-        <v>-3.522935779816514</v>
-      </c>
-      <c r="AP28">
-        <v>3.240418118466899</v>
-      </c>
-      <c r="AQ28">
-        <v>-5.676274944567626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3957,7 +3996,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oceanwide Holdings Co., Ltd. (SZSE:000046)</t>
+          <t>Anhui Xinli Finance Co., Ltd. (SHSE:600318)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3966,43 +4005,43 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.212</v>
+        <v>-0.0828</v>
       </c>
       <c r="G29">
-        <v>-1.902506557854853</v>
+        <v>0.03994778067885118</v>
       </c>
       <c r="H29">
-        <v>-1.902506557854853</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>-2.040221509763917</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>-2.040221509763917</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>-1645</v>
+        <v>-13.4</v>
       </c>
       <c r="L29">
-        <v>-2.397260273972603</v>
+        <v>-0.349869451697128</v>
       </c>
       <c r="M29">
-        <v>71.3</v>
+        <v>4.95</v>
       </c>
       <c r="N29">
-        <v>0.07571413401295529</v>
+        <v>0.00975177304964539</v>
       </c>
       <c r="O29">
-        <v>-0.0433434650455927</v>
+        <v>-0.3694029850746269</v>
       </c>
       <c r="P29">
-        <v>71.3</v>
+        <v>4.95</v>
       </c>
       <c r="Q29">
-        <v>0.07571413401295529</v>
+        <v>0.00975177304964539</v>
       </c>
       <c r="R29">
-        <v>-0.0433434650455927</v>
+        <v>-0.3694029850746269</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4011,73 +4050,64 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>380.5</v>
+        <v>28.1</v>
       </c>
       <c r="V29">
-        <v>0.4040564935754486</v>
+        <v>0.05535855003940111</v>
       </c>
       <c r="W29">
-        <v>-0.7100310773480663</v>
+        <v>-0.08343711083437111</v>
       </c>
       <c r="X29">
-        <v>0.1204371197135399</v>
+        <v>0.05531234599839564</v>
       </c>
       <c r="Y29">
-        <v>-0.8304681970616061</v>
+        <v>-0.1387494568327667</v>
       </c>
       <c r="Z29">
-        <v>0.0606435534188223</v>
+        <v>0.1598497495826377</v>
       </c>
       <c r="AA29">
-        <v>-0.1237262821135984</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.05550920645820581</v>
+        <v>0.05268586857874403</v>
       </c>
       <c r="AC29">
-        <v>-0.1792354885718042</v>
+        <v>-0.05268586857874403</v>
       </c>
       <c r="AD29">
-        <v>7851</v>
+        <v>151.8</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>7851</v>
+        <v>151.8</v>
       </c>
       <c r="AG29">
-        <v>7470.5</v>
+        <v>123.7</v>
       </c>
       <c r="AH29">
-        <v>0.8928997918728035</v>
+        <v>0.2302092811646952</v>
       </c>
       <c r="AI29">
-        <v>0.8259776330601466</v>
+        <v>0.3455497382198953</v>
       </c>
       <c r="AJ29">
-        <v>0.8880554432847531</v>
+        <v>0.1959448756534136</v>
       </c>
       <c r="AK29">
-        <v>0.8187208206387129</v>
+        <v>0.3008268482490272</v>
       </c>
       <c r="AL29">
-        <v>611.5</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>611.5</v>
-      </c>
-      <c r="AN29">
-        <v>-5.627553580388503</v>
-      </c>
-      <c r="AO29">
-        <v>-2.289452166802944</v>
-      </c>
-      <c r="AP29">
-        <v>-5.354813275034048</v>
+        <v>-3.16</v>
       </c>
       <c r="AQ29">
-        <v>-2.289452166802944</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -4088,7 +4118,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zero2IPO Holdings Inc. (SEHK:1945)</t>
+          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4096,116 +4126,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D30">
+        <v>0.199</v>
+      </c>
+      <c r="E30">
+        <v>0.114</v>
+      </c>
       <c r="G30">
-        <v>0.1805970149253731</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>0.08097014925373133</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>-0.1757462686567164</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>-0.1757462686567164</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>-3.81</v>
+        <v>463.5</v>
       </c>
       <c r="L30">
-        <v>-0.1421641791044776</v>
+        <v>0.2284939610549667</v>
       </c>
       <c r="M30">
-        <v>2.12</v>
+        <v>182.2</v>
       </c>
       <c r="N30">
-        <v>0.01843478260869565</v>
+        <v>0.08099577683929762</v>
       </c>
       <c r="O30">
-        <v>-0.5564304461942258</v>
+        <v>0.3930960086299892</v>
       </c>
       <c r="P30">
-        <v>-0</v>
+        <v>182.2</v>
       </c>
       <c r="Q30">
-        <v>-0</v>
+        <v>0.08099577683929762</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>0.3930960086299892</v>
       </c>
       <c r="S30">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>58.3</v>
+        <v>2929.8</v>
       </c>
       <c r="V30">
-        <v>0.5069565217391304</v>
+        <v>1.30242276061347</v>
       </c>
       <c r="W30">
-        <v>-0.04967405475880052</v>
+        <v>0.09609005721867483</v>
       </c>
       <c r="X30">
-        <v>0.05017268409073145</v>
+        <v>0.2357612758940585</v>
       </c>
       <c r="Y30">
-        <v>-0.09984673884953196</v>
+        <v>-0.1396712186753837</v>
       </c>
       <c r="Z30">
-        <v>1.445523193096009</v>
+        <v>0.04595448727388059</v>
       </c>
       <c r="AA30">
-        <v>-0.2540453074433657</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.05013925367159903</v>
+        <v>0.05297931222748981</v>
       </c>
       <c r="AC30">
-        <v>-0.3041845611149648</v>
+        <v>-0.05297931222748981</v>
       </c>
       <c r="AD30">
-        <v>1.59</v>
+        <v>40801.4</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.59</v>
+        <v>40801.4</v>
       </c>
       <c r="AG30">
-        <v>-56.70999999999999</v>
+        <v>37871.6</v>
       </c>
       <c r="AH30">
-        <v>0.0136375332361266</v>
+        <v>0.9477478984179193</v>
       </c>
       <c r="AI30">
-        <v>0.02097902097902098</v>
+        <v>0.8926006383625715</v>
       </c>
       <c r="AJ30">
-        <v>-0.9728941499399552</v>
+        <v>0.9439322451278753</v>
       </c>
       <c r="AK30">
-        <v>-3.24242424242424</v>
+        <v>0.8852455184439785</v>
       </c>
       <c r="AL30">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>-0.02100000000000002</v>
-      </c>
-      <c r="AN30">
-        <v>-0.3638443935926773</v>
-      </c>
-      <c r="AO30">
-        <v>-32.93706293706294</v>
-      </c>
-      <c r="AP30">
-        <v>12.97711670480549</v>
-      </c>
-      <c r="AQ30">
-        <v>224.2857142857141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4216,7 +4240,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Senmiao Technology Limited (NasdaqCM:AIHS)</t>
+          <t>Zuoli Kechuang Micro-finance Company Limited (SEHK:6866)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4225,118 +4249,109 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.99</v>
+        <v>-0.0733</v>
+      </c>
+      <c r="E31">
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G31">
-        <v>-1.2875</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>-1.2875</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>-0.9047816038905918</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>-0.9047816038905918</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>4.54</v>
+        <v>14</v>
       </c>
       <c r="L31">
-        <v>0.5675</v>
+        <v>0.5761316872427983</v>
       </c>
       <c r="M31">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N31">
-        <v>0.5129682997118156</v>
+        <v>0.1184738955823293</v>
       </c>
       <c r="O31">
-        <v>0.7841409691629956</v>
+        <v>0.4214285714285714</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>5.9</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.1184738955823293</v>
       </c>
       <c r="R31">
-        <v>-0</v>
+        <v>0.4214285714285714</v>
       </c>
       <c r="S31">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.97</v>
+        <v>4.61</v>
       </c>
       <c r="V31">
-        <v>0.2838616714697406</v>
+        <v>0.092570281124498</v>
       </c>
       <c r="W31">
-        <v>1.883817427385892</v>
+        <v>0.05295007564296521</v>
       </c>
       <c r="X31">
-        <v>0.05105496898537171</v>
+        <v>0.06981666925378477</v>
       </c>
       <c r="Y31">
-        <v>1.83276245840052</v>
+        <v>-0.01686659361081956</v>
       </c>
       <c r="Z31">
-        <v>0.8756314248067941</v>
+        <v>0.06465517241379311</v>
       </c>
       <c r="AA31">
-        <v>-0.7922552049536953</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.05100379238205713</v>
+        <v>0.05338516893368614</v>
       </c>
       <c r="AC31">
-        <v>-0.8432589973357524</v>
+        <v>-0.05338516893368614</v>
       </c>
       <c r="AD31">
-        <v>0.195</v>
+        <v>86.3</v>
       </c>
       <c r="AE31">
-        <v>0.6262641556236733</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.8212641556236733</v>
+        <v>86.3</v>
       </c>
       <c r="AG31">
-        <v>-1.148735844376327</v>
+        <v>81.69</v>
       </c>
       <c r="AH31">
-        <v>0.1058157716521734</v>
+        <v>0.6340925789860397</v>
       </c>
       <c r="AI31">
-        <v>0.07006617585950778</v>
+        <v>0.2400556328233658</v>
       </c>
       <c r="AJ31">
-        <v>-0.1983566650574613</v>
+        <v>0.6212639744467259</v>
       </c>
       <c r="AK31">
-        <v>-0.1178037868776057</v>
+        <v>0.2301840006762659</v>
       </c>
       <c r="AL31">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>0.033</v>
-      </c>
-      <c r="AN31">
-        <v>-0.0336613153806318</v>
-      </c>
-      <c r="AO31">
-        <v>-227.2727272727273</v>
-      </c>
-      <c r="AP31">
-        <v>0.1982972284440405</v>
-      </c>
-      <c r="AQ31">
-        <v>-227.2727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4347,127 +4362,2118 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Hanhua Financial Holding Co., Ltd. (SEHK:3903)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>-0.189</v>
+      </c>
+      <c r="E32">
+        <v>-0.547</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0.736</v>
+      </c>
+      <c r="L32">
+        <v>0.01130568356374808</v>
+      </c>
+      <c r="M32">
+        <v>-0</v>
+      </c>
+      <c r="N32">
+        <v>-0</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>-0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>86.2</v>
+      </c>
+      <c r="V32">
+        <v>0.4182435710819991</v>
+      </c>
+      <c r="W32">
+        <v>0.0006727605118829981</v>
+      </c>
+      <c r="X32">
+        <v>0.07076111080606083</v>
+      </c>
+      <c r="Y32">
+        <v>-0.07008835029417783</v>
+      </c>
+      <c r="Z32">
+        <v>0.04456919864443912</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.05340609804347686</v>
+      </c>
+      <c r="AC32">
+        <v>-0.05340609804347686</v>
+      </c>
+      <c r="AD32">
+        <v>376.4</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>376.4</v>
+      </c>
+      <c r="AG32">
+        <v>290.2</v>
+      </c>
+      <c r="AH32">
+        <v>0.6461802575107296</v>
+      </c>
+      <c r="AI32">
+        <v>0.2565430752453653</v>
+      </c>
+      <c r="AJ32">
+        <v>0.5847269796494057</v>
+      </c>
+      <c r="AK32">
+        <v>0.2101375814627082</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>East Money Information Co.,Ltd. (SZSE:300059)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.308</v>
+      </c>
+      <c r="E33">
+        <v>0.526</v>
+      </c>
+      <c r="F33">
+        <v>0.0229</v>
+      </c>
+      <c r="G33">
+        <v>0.08926386294841243</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1113.4</v>
+      </c>
+      <c r="L33">
+        <v>0.7170734848972757</v>
+      </c>
+      <c r="M33">
+        <v>234.8</v>
+      </c>
+      <c r="N33">
+        <v>0.007482520602425765</v>
+      </c>
+      <c r="O33">
+        <v>0.2108855757140291</v>
+      </c>
+      <c r="P33">
+        <v>234.8</v>
+      </c>
+      <c r="Q33">
+        <v>0.007482520602425765</v>
+      </c>
+      <c r="R33">
+        <v>0.2108855757140291</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>8079.8</v>
+      </c>
+      <c r="V33">
+        <v>0.2574841139841554</v>
+      </c>
+      <c r="W33">
+        <v>0.124882228902149</v>
+      </c>
+      <c r="X33">
+        <v>0.05598430718275597</v>
+      </c>
+      <c r="Y33">
+        <v>0.06889792171939307</v>
+      </c>
+      <c r="Z33">
+        <v>0.164065554369763</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.05355709874648462</v>
+      </c>
+      <c r="AC33">
+        <v>-0.05355709874648462</v>
+      </c>
+      <c r="AD33">
+        <v>11468.8</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>11468.8</v>
+      </c>
+      <c r="AG33">
+        <v>3388.999999999999</v>
+      </c>
+      <c r="AH33">
+        <v>0.2676586866315352</v>
+      </c>
+      <c r="AI33">
+        <v>0.5429249056764549</v>
+      </c>
+      <c r="AJ33">
+        <v>0.09747244656128481</v>
+      </c>
+      <c r="AK33">
+        <v>0.2598069654945071</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-281.2</v>
+      </c>
+      <c r="AQ33">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yixin Group Limited (SEHK:2858)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.004050000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.04068785505911255</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>70.8</v>
+      </c>
+      <c r="L34">
+        <v>0.1087056655918931</v>
+      </c>
+      <c r="M34">
+        <v>28.08</v>
+      </c>
+      <c r="N34">
+        <v>0.05512367491166078</v>
+      </c>
+      <c r="O34">
+        <v>0.3966101694915254</v>
+      </c>
+      <c r="P34">
+        <v>26.5</v>
+      </c>
+      <c r="Q34">
+        <v>0.05202198665096192</v>
+      </c>
+      <c r="R34">
+        <v>0.3742937853107345</v>
+      </c>
+      <c r="S34">
+        <v>1.579999999999998</v>
+      </c>
+      <c r="T34">
+        <v>0.05626780626780621</v>
+      </c>
+      <c r="U34">
+        <v>521.2</v>
+      </c>
+      <c r="V34">
+        <v>1.023164507263447</v>
+      </c>
+      <c r="W34">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="X34">
+        <v>0.1028149105954951</v>
+      </c>
+      <c r="Y34">
+        <v>-0.07106887884946338</v>
+      </c>
+      <c r="Z34">
+        <v>0.2012483391527361</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.05372990643620339</v>
+      </c>
+      <c r="AC34">
+        <v>-0.05372990643620339</v>
+      </c>
+      <c r="AD34">
+        <v>2544.5</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>2544.5</v>
+      </c>
+      <c r="AG34">
+        <v>2023.3</v>
+      </c>
+      <c r="AH34">
+        <v>0.8331968957726186</v>
+      </c>
+      <c r="AI34">
+        <v>0.5432090858631143</v>
+      </c>
+      <c r="AJ34">
+        <v>0.79887077032416</v>
+      </c>
+      <c r="AK34">
+        <v>0.4860196973336536</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Guangdong Join-Share Financing Guarantee Investment Co., Ltd. (SEHK:1543)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.0219</v>
+      </c>
+      <c r="E35">
+        <v>-0.191</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>5.02</v>
+      </c>
+      <c r="L35">
+        <v>0.1224390243902439</v>
+      </c>
+      <c r="M35">
+        <v>12.5</v>
+      </c>
+      <c r="N35">
+        <v>0.07921419518377693</v>
+      </c>
+      <c r="O35">
+        <v>2.49003984063745</v>
+      </c>
+      <c r="P35">
+        <v>12.5</v>
+      </c>
+      <c r="Q35">
+        <v>0.07921419518377693</v>
+      </c>
+      <c r="R35">
+        <v>2.49003984063745</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>0.6337135614702154</v>
+      </c>
+      <c r="W35">
+        <v>0.01641595814257684</v>
+      </c>
+      <c r="X35">
+        <v>0.05901168106415627</v>
+      </c>
+      <c r="Y35">
+        <v>-0.04259572292157943</v>
+      </c>
+      <c r="Z35">
+        <v>0.1370609453193687</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.05377799334357078</v>
+      </c>
+      <c r="AC35">
+        <v>-0.05377799334357078</v>
+      </c>
+      <c r="AD35">
+        <v>104.9</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>104.9</v>
+      </c>
+      <c r="AG35">
+        <v>4.900000000000006</v>
+      </c>
+      <c r="AH35">
+        <v>0.3993148077655119</v>
+      </c>
+      <c r="AI35">
+        <v>0.2424312456667437</v>
+      </c>
+      <c r="AJ35">
+        <v>0.03011677934849419</v>
+      </c>
+      <c r="AK35">
+        <v>0.01472798316801925</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AVIC Industry-Finance Holdings Co., Ltd. (SHSE:600705)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.0352</v>
+      </c>
+      <c r="E36">
+        <v>-0.303</v>
+      </c>
+      <c r="G36">
+        <v>0.007271925958572058</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>68.3</v>
+      </c>
+      <c r="L36">
+        <v>0.0376267078007933</v>
+      </c>
+      <c r="M36">
+        <v>1514</v>
+      </c>
+      <c r="N36">
+        <v>0.3911639323084873</v>
+      </c>
+      <c r="O36">
+        <v>22.16691068814056</v>
+      </c>
+      <c r="P36">
+        <v>754</v>
+      </c>
+      <c r="Q36">
+        <v>0.1948068724970934</v>
+      </c>
+      <c r="R36">
+        <v>11.03953147877013</v>
+      </c>
+      <c r="S36">
+        <v>760</v>
+      </c>
+      <c r="T36">
+        <v>0.5019815059445178</v>
+      </c>
+      <c r="U36">
+        <v>7064.7</v>
+      </c>
+      <c r="V36">
+        <v>1.825268053223098</v>
+      </c>
+      <c r="W36">
+        <v>0.01207673945716559</v>
+      </c>
+      <c r="X36">
+        <v>0.1222209977165985</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1101442582594329</v>
+      </c>
+      <c r="Z36">
+        <v>0.09006966108263217</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.05379992175618943</v>
+      </c>
+      <c r="AC36">
+        <v>-0.05379992175618943</v>
+      </c>
+      <c r="AD36">
+        <v>26758.9</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>26758.9</v>
+      </c>
+      <c r="AG36">
+        <v>19694.2</v>
+      </c>
+      <c r="AH36">
+        <v>0.8736344819030082</v>
+      </c>
+      <c r="AI36">
+        <v>0.7426879971579081</v>
+      </c>
+      <c r="AJ36">
+        <v>0.8357500838118033</v>
+      </c>
+      <c r="AK36">
+        <v>0.6799286037334586</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-456.8</v>
+      </c>
+      <c r="AQ36">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Haitong Unitrust International Financial Leasing Co., Ltd. (SEHK:1905)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.0973</v>
+      </c>
+      <c r="E37">
+        <v>0.0526</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>217</v>
+      </c>
+      <c r="L37">
+        <v>0.3590337524818001</v>
+      </c>
+      <c r="M37">
+        <v>174.2</v>
+      </c>
+      <c r="N37">
+        <v>0.2015037593984962</v>
+      </c>
+      <c r="O37">
+        <v>0.8027649769585253</v>
+      </c>
+      <c r="P37">
+        <v>91.5</v>
+      </c>
+      <c r="Q37">
+        <v>0.1058415268941585</v>
+      </c>
+      <c r="R37">
+        <v>0.4216589861751152</v>
+      </c>
+      <c r="S37">
+        <v>82.69999999999999</v>
+      </c>
+      <c r="T37">
+        <v>0.4747416762342135</v>
+      </c>
+      <c r="U37">
+        <v>1227.5</v>
+      </c>
+      <c r="V37">
+        <v>1.419895893580104</v>
+      </c>
+      <c r="W37">
+        <v>0.08153297012962615</v>
+      </c>
+      <c r="X37">
+        <v>0.2071479437145499</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1256149735849238</v>
+      </c>
+      <c r="Z37">
+        <v>0.04341642123410674</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0.05391255350970683</v>
+      </c>
+      <c r="AC37">
+        <v>-0.05391255350970683</v>
+      </c>
+      <c r="AD37">
+        <v>13234.9</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>13234.9</v>
+      </c>
+      <c r="AG37">
+        <v>12007.4</v>
+      </c>
+      <c r="AH37">
+        <v>0.9386853341276934</v>
+      </c>
+      <c r="AI37">
+        <v>0.8314110537358813</v>
+      </c>
+      <c r="AJ37">
+        <v>0.9328381979350368</v>
+      </c>
+      <c r="AK37">
+        <v>0.817324774863693</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Differ Group Auto Limited (SEHK:6878)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>0.256</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-54.9</v>
+      </c>
+      <c r="L38">
+        <v>-0.244</v>
+      </c>
+      <c r="M38">
+        <v>-0</v>
+      </c>
+      <c r="N38">
+        <v>-0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>-0</v>
+      </c>
+      <c r="Q38">
+        <v>-0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>13.2</v>
+      </c>
+      <c r="V38">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="W38">
+        <v>-0.132480694980695</v>
+      </c>
+      <c r="X38">
+        <v>0.1064745995487091</v>
+      </c>
+      <c r="Y38">
+        <v>-0.2389552945294041</v>
+      </c>
+      <c r="Z38">
+        <v>0.3765627353517097</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.05543319874002073</v>
+      </c>
+      <c r="AC38">
+        <v>-0.05543319874002073</v>
+      </c>
+      <c r="AD38">
+        <v>295.7</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>295.7</v>
+      </c>
+      <c r="AG38">
+        <v>282.5</v>
+      </c>
+      <c r="AH38">
+        <v>0.8426902251353662</v>
+      </c>
+      <c r="AI38">
+        <v>0.4573859242072699</v>
+      </c>
+      <c r="AJ38">
+        <v>0.8365413088540125</v>
+      </c>
+      <c r="AK38">
+        <v>0.4460761092689089</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hongbo Co.,Ltd. (SZSE:002229)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.0259</v>
+      </c>
+      <c r="G39">
+        <v>0.04031141868512111</v>
+      </c>
+      <c r="H39">
+        <v>-0.003863898500576701</v>
+      </c>
+      <c r="I39">
+        <v>-0.01741637831603229</v>
+      </c>
+      <c r="J39">
+        <v>-0.01741637831603229</v>
+      </c>
+      <c r="K39">
+        <v>-8.35</v>
+      </c>
+      <c r="L39">
+        <v>-0.09630911188004612</v>
+      </c>
+      <c r="M39">
+        <v>3.47</v>
+      </c>
+      <c r="N39">
+        <v>0.001794580057923045</v>
+      </c>
+      <c r="O39">
+        <v>-0.4155688622754491</v>
+      </c>
+      <c r="P39">
+        <v>3.47</v>
+      </c>
+      <c r="Q39">
+        <v>0.001794580057923045</v>
+      </c>
+      <c r="R39">
+        <v>-0.4155688622754491</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>114.5</v>
+      </c>
+      <c r="V39">
+        <v>0.05921597021100538</v>
+      </c>
+      <c r="W39">
+        <v>-0.03617850953206239</v>
+      </c>
+      <c r="X39">
+        <v>0.05261789981062175</v>
+      </c>
+      <c r="Y39">
+        <v>-0.08879640934268415</v>
+      </c>
+      <c r="Z39">
+        <v>0.6268980477223428</v>
+      </c>
+      <c r="AA39">
+        <v>-0.01091829356471439</v>
+      </c>
+      <c r="AB39">
+        <v>0.05240543255416314</v>
+      </c>
+      <c r="AC39">
+        <v>-0.06332372611887753</v>
+      </c>
+      <c r="AD39">
+        <v>63.2</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>63.2</v>
+      </c>
+      <c r="AG39">
+        <v>-51.3</v>
+      </c>
+      <c r="AH39">
+        <v>0.03165064102564103</v>
+      </c>
+      <c r="AI39">
+        <v>0.2154790317081487</v>
+      </c>
+      <c r="AJ39">
+        <v>-0.02725389151569888</v>
+      </c>
+      <c r="AK39">
+        <v>-0.2869127516778523</v>
+      </c>
+      <c r="AL39">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AM39">
+        <v>-1.045</v>
+      </c>
+      <c r="AN39">
+        <v>16.76392572944297</v>
+      </c>
+      <c r="AO39">
+        <v>-1.614973262032086</v>
+      </c>
+      <c r="AP39">
+        <v>-13.60742705570292</v>
+      </c>
+      <c r="AQ39">
+        <v>1.444976076555024</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Beijing Cuiwei Tower Co., Ltd. (SHSE:603123)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>-0.0571</v>
+      </c>
+      <c r="G40">
+        <v>0.08029480217222652</v>
+      </c>
+      <c r="H40">
+        <v>0.05411171450737005</v>
+      </c>
+      <c r="I40">
+        <v>-0.01551590380139643</v>
+      </c>
+      <c r="J40">
+        <v>-0.01551590380139643</v>
+      </c>
+      <c r="K40">
+        <v>-114.6</v>
+      </c>
+      <c r="L40">
+        <v>-0.2222653219550039</v>
+      </c>
+      <c r="M40">
+        <v>6.48</v>
+      </c>
+      <c r="N40">
+        <v>0.005650505755144752</v>
+      </c>
+      <c r="O40">
+        <v>-0.05654450261780106</v>
+      </c>
+      <c r="P40">
+        <v>6.48</v>
+      </c>
+      <c r="Q40">
+        <v>0.005650505755144752</v>
+      </c>
+      <c r="R40">
+        <v>-0.05654450261780106</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>263.2</v>
+      </c>
+      <c r="V40">
+        <v>0.2295081967213115</v>
+      </c>
+      <c r="W40">
+        <v>-0.1985103065996882</v>
+      </c>
+      <c r="X40">
+        <v>0.05496167842570385</v>
+      </c>
+      <c r="Y40">
+        <v>-0.253471985025392</v>
+      </c>
+      <c r="Z40">
+        <v>0.9135364989369245</v>
+      </c>
+      <c r="AA40">
+        <v>-0.01417434443656981</v>
+      </c>
+      <c r="AB40">
+        <v>0.05306789788866035</v>
+      </c>
+      <c r="AC40">
+        <v>-0.06724224232523016</v>
+      </c>
+      <c r="AD40">
+        <v>303.2</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>303.2</v>
+      </c>
+      <c r="AG40">
+        <v>40</v>
+      </c>
+      <c r="AH40">
+        <v>0.2091034482758621</v>
+      </c>
+      <c r="AI40">
+        <v>0.4172859895403249</v>
+      </c>
+      <c r="AJ40">
+        <v>0.03370407819346141</v>
+      </c>
+      <c r="AK40">
+        <v>0.08631851532153648</v>
+      </c>
+      <c r="AL40">
+        <v>1.5</v>
+      </c>
+      <c r="AM40">
+        <v>-8.06</v>
+      </c>
+      <c r="AN40">
+        <v>25.05785123966942</v>
+      </c>
+      <c r="AO40">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AP40">
+        <v>3.305785123966942</v>
+      </c>
+      <c r="AQ40">
+        <v>0.9925558312655086</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Beijing Shengtong Printing Co., Ltd (SZSE:002599)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0.0506</v>
+      </c>
+      <c r="G41">
+        <v>0.05750311332503113</v>
+      </c>
+      <c r="H41">
+        <v>0.04140722291407224</v>
+      </c>
+      <c r="I41">
+        <v>-0.009122042341220424</v>
+      </c>
+      <c r="J41">
+        <v>-0.009122042341220424</v>
+      </c>
+      <c r="K41">
+        <v>-2.55</v>
+      </c>
+      <c r="L41">
+        <v>-0.007938978829389789</v>
+      </c>
+      <c r="M41">
+        <v>4.461</v>
+      </c>
+      <c r="N41">
+        <v>0.009098511115643484</v>
+      </c>
+      <c r="O41">
+        <v>-1.749411764705883</v>
+      </c>
+      <c r="P41">
+        <v>0.351</v>
+      </c>
+      <c r="Q41">
+        <v>0.0007158882316948806</v>
+      </c>
+      <c r="R41">
+        <v>-0.1376470588235294</v>
+      </c>
+      <c r="S41">
+        <v>4.11</v>
+      </c>
+      <c r="T41">
+        <v>0.9213180901143242</v>
+      </c>
+      <c r="U41">
+        <v>35.6</v>
+      </c>
+      <c r="V41">
+        <v>0.07260860697532123</v>
+      </c>
+      <c r="W41">
+        <v>-0.01257396449704142</v>
+      </c>
+      <c r="X41">
+        <v>0.05272878139307704</v>
+      </c>
+      <c r="Y41">
+        <v>-0.06530274589011846</v>
+      </c>
+      <c r="Z41">
+        <v>1.734341252699784</v>
+      </c>
+      <c r="AA41">
+        <v>-0.0158207343412527</v>
+      </c>
+      <c r="AB41">
+        <v>0.05235968592384982</v>
+      </c>
+      <c r="AC41">
+        <v>-0.06818042026510251</v>
+      </c>
+      <c r="AD41">
+        <v>21.4</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>21.4</v>
+      </c>
+      <c r="AG41">
+        <v>-14.2</v>
+      </c>
+      <c r="AH41">
+        <v>0.04182137971467657</v>
+      </c>
+      <c r="AI41">
+        <v>0.09812012838147638</v>
+      </c>
+      <c r="AJ41">
+        <v>-0.02982566687670658</v>
+      </c>
+      <c r="AK41">
+        <v>-0.07780821917808221</v>
+      </c>
+      <c r="AL41">
+        <v>1.24</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>2.401795735129068</v>
+      </c>
+      <c r="AO41">
+        <v>-2.362903225806452</v>
+      </c>
+      <c r="AP41">
+        <v>-1.593714927048261</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Minsheng Holdings Co.,Ltd (SZSE:000416)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>-0.139</v>
+      </c>
+      <c r="G42">
+        <v>-0.8339920948616601</v>
+      </c>
+      <c r="H42">
+        <v>-0.8339920948616601</v>
+      </c>
+      <c r="I42">
+        <v>-0.5079051383399209</v>
+      </c>
+      <c r="J42">
+        <v>-0.5079051383399209</v>
+      </c>
+      <c r="K42">
+        <v>-1.9</v>
+      </c>
+      <c r="L42">
+        <v>-0.3754940711462451</v>
+      </c>
+      <c r="M42">
+        <v>-0</v>
+      </c>
+      <c r="N42">
+        <v>-0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>-0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>7.67</v>
+      </c>
+      <c r="V42">
+        <v>0.05326388888888889</v>
+      </c>
+      <c r="W42">
+        <v>-0.01544715447154471</v>
+      </c>
+      <c r="X42">
+        <v>0.05233939734285575</v>
+      </c>
+      <c r="Y42">
+        <v>-0.06778655181440046</v>
+      </c>
+      <c r="Z42">
+        <v>0.04256751072600319</v>
+      </c>
+      <c r="AA42">
+        <v>-0.02162025742407672</v>
+      </c>
+      <c r="AB42">
+        <v>0.05229615064394915</v>
+      </c>
+      <c r="AC42">
+        <v>-0.07391640806802588</v>
+      </c>
+      <c r="AD42">
+        <v>0.742</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0.742</v>
+      </c>
+      <c r="AG42">
+        <v>-6.928</v>
+      </c>
+      <c r="AH42">
+        <v>0.005126362769617664</v>
+      </c>
+      <c r="AI42">
+        <v>0.006074896432021745</v>
+      </c>
+      <c r="AJ42">
+        <v>-0.05054278043655889</v>
+      </c>
+      <c r="AK42">
+        <v>-0.06052135019917534</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1.88</v>
+      </c>
+      <c r="AN42">
+        <v>-0.3483568075117371</v>
+      </c>
+      <c r="AP42">
+        <v>3.252582159624413</v>
+      </c>
+      <c r="AQ42">
+        <v>1.367021276595745</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sichuan Jinshi Technology Co.,Ltd (SZSE:002951)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.32</v>
+      </c>
+      <c r="G43">
+        <v>0.4008547008547008</v>
+      </c>
+      <c r="H43">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="I43">
+        <v>-0.5660884629565434</v>
+      </c>
+      <c r="J43">
+        <v>-0.5660884629565434</v>
+      </c>
+      <c r="K43">
+        <v>-8.57</v>
+      </c>
+      <c r="L43">
+        <v>-0.7324786324786325</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>37.8</v>
+      </c>
+      <c r="V43">
+        <v>0.07870081199250467</v>
+      </c>
+      <c r="W43">
+        <v>-0.026873628096582</v>
+      </c>
+      <c r="X43">
+        <v>0.05228793121523138</v>
+      </c>
+      <c r="Y43">
+        <v>-0.07916155931181339</v>
+      </c>
+      <c r="Z43">
+        <v>0.0408760506140151</v>
+      </c>
+      <c r="AA43">
+        <v>-0.02313946066382168</v>
+      </c>
+      <c r="AB43">
+        <v>0.05228738702233859</v>
+      </c>
+      <c r="AC43">
+        <v>-0.07542684768616027</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0.03117508295778494</v>
+      </c>
+      <c r="AF43">
+        <v>0.03117508295778494</v>
+      </c>
+      <c r="AG43">
+        <v>-37.76882491704221</v>
+      </c>
+      <c r="AH43">
+        <v>6.490330958093799e-05</v>
+      </c>
+      <c r="AI43">
+        <v>0.0001163114064926813</v>
+      </c>
+      <c r="AJ43">
+        <v>-0.08534726374918555</v>
+      </c>
+      <c r="AK43">
+        <v>-0.1640473967238937</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-0.877</v>
+      </c>
+      <c r="AN43">
+        <v>-0</v>
+      </c>
+      <c r="AP43">
+        <v>10.47098001581431</v>
+      </c>
+      <c r="AQ43">
+        <v>7.582668187001141</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Oceanwide Holdings Co., Ltd. (SZSE:000046)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>-0.184</v>
+      </c>
+      <c r="G44">
+        <v>-0.1677876971994619</v>
+      </c>
+      <c r="H44">
+        <v>-0.1677876971994619</v>
+      </c>
+      <c r="I44">
+        <v>-0.8992295462883697</v>
+      </c>
+      <c r="J44">
+        <v>-0.8992295462883697</v>
+      </c>
+      <c r="K44">
+        <v>-2217.9</v>
+      </c>
+      <c r="L44">
+        <v>-2.712363947658065</v>
+      </c>
+      <c r="M44">
+        <v>60.8</v>
+      </c>
+      <c r="N44">
+        <v>0.2199710564399421</v>
+      </c>
+      <c r="O44">
+        <v>-0.02741331890527075</v>
+      </c>
+      <c r="P44">
+        <v>60.8</v>
+      </c>
+      <c r="Q44">
+        <v>0.2199710564399421</v>
+      </c>
+      <c r="R44">
+        <v>-0.02741331890527075</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>223.4</v>
+      </c>
+      <c r="V44">
+        <v>0.8082489146164979</v>
+      </c>
+      <c r="W44">
+        <v>-3.935237757274663</v>
+      </c>
+      <c r="X44">
+        <v>0.3118087399974665</v>
+      </c>
+      <c r="Y44">
+        <v>-4.247046497272129</v>
+      </c>
+      <c r="Z44">
+        <v>0.1053452029734221</v>
+      </c>
+      <c r="AA44">
+        <v>-0.09472951907344661</v>
+      </c>
+      <c r="AB44">
+        <v>0.05395376106933408</v>
+      </c>
+      <c r="AC44">
+        <v>-0.1486832801427807</v>
+      </c>
+      <c r="AD44">
+        <v>7091.3</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>7091.3</v>
+      </c>
+      <c r="AG44">
+        <v>6867.900000000001</v>
+      </c>
+      <c r="AH44">
+        <v>0.9624849003081016</v>
+      </c>
+      <c r="AI44">
+        <v>1.169313216258554</v>
+      </c>
+      <c r="AJ44">
+        <v>0.9613118150133674</v>
+      </c>
+      <c r="AK44">
+        <v>1.17578880690281</v>
+      </c>
+      <c r="AL44">
+        <v>500.4</v>
+      </c>
+      <c r="AM44">
+        <v>500.4</v>
+      </c>
+      <c r="AN44">
+        <v>-9.64671473268943</v>
+      </c>
+      <c r="AO44">
+        <v>-1.469424460431655</v>
+      </c>
+      <c r="AP44">
+        <v>-9.34281050197252</v>
+      </c>
+      <c r="AQ44">
+        <v>-1.469424460431655</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>51 Credit Card Inc. (SEHK:2051)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>-0.367</v>
+      </c>
+      <c r="G45">
+        <v>-0.1940054495912806</v>
+      </c>
+      <c r="H45">
+        <v>-0.2572207084468665</v>
+      </c>
+      <c r="I45">
+        <v>-0.2942779291553134</v>
+      </c>
+      <c r="J45">
+        <v>-0.2942779291553134</v>
+      </c>
+      <c r="K45">
+        <v>-10.5</v>
+      </c>
+      <c r="L45">
+        <v>-0.2861035422343324</v>
+      </c>
+      <c r="M45">
+        <v>-0</v>
+      </c>
+      <c r="N45">
+        <v>-0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>48.6</v>
+      </c>
+      <c r="V45">
+        <v>3.375</v>
+      </c>
+      <c r="W45">
+        <v>-0.08951406649616368</v>
+      </c>
+      <c r="X45">
+        <v>0.07012981506321231</v>
+      </c>
+      <c r="Y45">
+        <v>-0.159643881559376</v>
+      </c>
+      <c r="Z45">
+        <v>0.3918428357890242</v>
+      </c>
+      <c r="AA45">
+        <v>-0.1153106982703396</v>
+      </c>
+      <c r="AB45">
+        <v>0.0533922650321348</v>
+      </c>
+      <c r="AC45">
+        <v>-0.1687029633024744</v>
+      </c>
+      <c r="AD45">
+        <v>25.4</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>25.4</v>
+      </c>
+      <c r="AG45">
+        <v>-23.2</v>
+      </c>
+      <c r="AH45">
+        <v>0.6381909547738693</v>
+      </c>
+      <c r="AI45">
+        <v>0.206336311941511</v>
+      </c>
+      <c r="AJ45">
+        <v>2.636363636363636</v>
+      </c>
+      <c r="AK45">
+        <v>-0.3114093959731544</v>
+      </c>
+      <c r="AL45">
+        <v>1.45</v>
+      </c>
+      <c r="AM45">
+        <v>-0.1100000000000001</v>
+      </c>
+      <c r="AN45">
+        <v>-2.626680455015512</v>
+      </c>
+      <c r="AO45">
+        <v>-7.448275862068966</v>
+      </c>
+      <c r="AP45">
+        <v>2.399172699069287</v>
+      </c>
+      <c r="AQ45">
+        <v>98.1818181818181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Senmiao Technology Limited (NasdaqCM:AIHS)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>0.7090000000000001</v>
+      </c>
+      <c r="G46">
+        <v>-0.6549865229110513</v>
+      </c>
+      <c r="H46">
+        <v>-0.6549865229110513</v>
+      </c>
+      <c r="I46">
+        <v>-0.6802254515483497</v>
+      </c>
+      <c r="J46">
+        <v>-0.6802254515483497</v>
+      </c>
+      <c r="K46">
+        <v>-3.72</v>
+      </c>
+      <c r="L46">
+        <v>-0.5013477088948788</v>
+      </c>
+      <c r="M46">
+        <v>-0</v>
+      </c>
+      <c r="N46">
+        <v>-0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>-0</v>
+      </c>
+      <c r="Q46">
+        <v>-0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>1.31</v>
+      </c>
+      <c r="V46">
+        <v>0.3341836734693878</v>
+      </c>
+      <c r="W46">
+        <v>-0.5933014354066987</v>
+      </c>
+      <c r="X46">
+        <v>0.05498480936119993</v>
+      </c>
+      <c r="Y46">
+        <v>-0.6482862447678985</v>
+      </c>
+      <c r="Z46">
+        <v>1.455654262189074</v>
+      </c>
+      <c r="AA46">
+        <v>-0.990173077795843</v>
+      </c>
+      <c r="AB46">
+        <v>0.05307322807819101</v>
+      </c>
+      <c r="AC46">
+        <v>-1.043246305874034</v>
+      </c>
+      <c r="AD46">
+        <v>0.729</v>
+      </c>
+      <c r="AE46">
+        <v>0.3163642524437711</v>
+      </c>
+      <c r="AF46">
+        <v>1.045364252443771</v>
+      </c>
+      <c r="AG46">
+        <v>-0.2646357475562291</v>
+      </c>
+      <c r="AH46">
+        <v>0.2105312318082769</v>
+      </c>
+      <c r="AI46">
+        <v>0.1407828918426096</v>
+      </c>
+      <c r="AJ46">
+        <v>-0.0723965463576738</v>
+      </c>
+      <c r="AK46">
+        <v>-0.04327391413364749</v>
+      </c>
+      <c r="AL46">
+        <v>0.036</v>
+      </c>
+      <c r="AM46">
+        <v>0.036</v>
+      </c>
+      <c r="AN46">
+        <v>-0.189154125583809</v>
+      </c>
+      <c r="AO46">
+        <v>-144.1666666666667</v>
+      </c>
+      <c r="AP46">
+        <v>0.06866521732128415</v>
+      </c>
+      <c r="AQ46">
+        <v>-144.1666666666667</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Beijing Compass Technology Development Co., Ltd. (SZSE:300803)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>0.08349999999999999</v>
+      </c>
+      <c r="G47">
+        <v>0.4978279756733275</v>
+      </c>
+      <c r="H47">
+        <v>0.3562119895742832</v>
+      </c>
+      <c r="I47">
+        <v>-0.2258905299739357</v>
+      </c>
+      <c r="J47">
+        <v>-0.2258905299739357</v>
+      </c>
+      <c r="K47">
+        <v>-2.21</v>
+      </c>
+      <c r="L47">
+        <v>-0.01920069504778454</v>
+      </c>
+      <c r="M47">
+        <v>0.983</v>
+      </c>
+      <c r="N47">
+        <v>0.0002829021210464213</v>
+      </c>
+      <c r="O47">
+        <v>-0.4447963800904977</v>
+      </c>
+      <c r="P47">
+        <v>0.983</v>
+      </c>
+      <c r="Q47">
+        <v>0.0002829021210464213</v>
+      </c>
+      <c r="R47">
+        <v>-0.4447963800904977</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>282.9</v>
+      </c>
+      <c r="V47">
+        <v>0.08141710075689987</v>
+      </c>
+      <c r="W47">
+        <v>-0.009396258503401362</v>
+      </c>
+      <c r="X47">
+        <v>0.05240051931113949</v>
+      </c>
+      <c r="Y47">
+        <v>-0.06179677781454085</v>
+      </c>
+      <c r="AB47">
+        <v>0.05230644389677298</v>
+      </c>
+      <c r="AD47">
+        <v>38.9</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>38.9</v>
+      </c>
+      <c r="AG47">
+        <v>-244</v>
+      </c>
+      <c r="AH47">
+        <v>0.01107126593806922</v>
+      </c>
+      <c r="AI47">
+        <v>0.140993113446901</v>
+      </c>
+      <c r="AJ47">
+        <v>-0.0755254279258365</v>
+      </c>
+      <c r="AK47">
+        <v>34.857142857143</v>
+      </c>
+      <c r="AL47">
+        <v>1.34</v>
+      </c>
+      <c r="AM47">
+        <v>-5.96</v>
+      </c>
+      <c r="AN47">
+        <v>-1.800925925925926</v>
+      </c>
+      <c r="AO47">
+        <v>-19.40298507462687</v>
+      </c>
+      <c r="AP47">
+        <v>11.29629629629629</v>
+      </c>
+      <c r="AQ47">
+        <v>4.36241610738255</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Shanghai DZH Limited (SHSE:601519)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D32">
-        <v>-0.0225</v>
-      </c>
-      <c r="G32">
-        <v>0.2304029304029304</v>
-      </c>
-      <c r="H32">
-        <v>0.008424908424908424</v>
-      </c>
-      <c r="I32">
-        <v>-0.1010989010989011</v>
-      </c>
-      <c r="J32">
-        <v>-0.1010989010989011</v>
-      </c>
-      <c r="K32">
-        <v>-10.9</v>
-      </c>
-      <c r="L32">
-        <v>-0.07985347985347986</v>
-      </c>
-      <c r="M32">
-        <v>0.041</v>
-      </c>
-      <c r="N32">
-        <v>2.415743577657318e-05</v>
-      </c>
-      <c r="O32">
-        <v>-0.003761467889908257</v>
-      </c>
-      <c r="P32">
-        <v>0.041</v>
-      </c>
-      <c r="Q32">
-        <v>2.415743577657318e-05</v>
-      </c>
-      <c r="R32">
-        <v>-0.003761467889908257</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>201.2</v>
-      </c>
-      <c r="V32">
-        <v>0.118548197030403</v>
-      </c>
-      <c r="W32">
-        <v>-0.04526578073089701</v>
-      </c>
-      <c r="X32">
-        <v>0.05011615074914245</v>
-      </c>
-      <c r="Y32">
-        <v>-0.09538193148003946</v>
-      </c>
-      <c r="Z32">
-        <v>8.863636363636344</v>
-      </c>
-      <c r="AA32">
-        <v>-0.8961038961038942</v>
-      </c>
-      <c r="AB32">
-        <v>0.05005831723382369</v>
-      </c>
-      <c r="AC32">
-        <v>-0.9461622133377179</v>
-      </c>
-      <c r="AD32">
-        <v>12.1</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>12.1</v>
-      </c>
-      <c r="AG32">
-        <v>-189.1</v>
-      </c>
-      <c r="AH32">
-        <v>0.00707892119581115</v>
-      </c>
-      <c r="AI32">
-        <v>0.04971240755957271</v>
-      </c>
-      <c r="AJ32">
-        <v>-0.1253895630263245</v>
-      </c>
-      <c r="AK32">
-        <v>-4.481042654028434</v>
-      </c>
-      <c r="AL32">
-        <v>0.512</v>
-      </c>
-      <c r="AM32">
-        <v>-3.108</v>
-      </c>
-      <c r="AN32">
-        <v>-1.070796460176991</v>
-      </c>
-      <c r="AO32">
-        <v>-26.953125</v>
-      </c>
-      <c r="AP32">
-        <v>16.73451327433628</v>
-      </c>
-      <c r="AQ32">
-        <v>4.440154440154441</v>
+      <c r="D48">
+        <v>0.09</v>
+      </c>
+      <c r="G48">
+        <v>0.1410373066424022</v>
+      </c>
+      <c r="H48">
+        <v>-0.1082802547770701</v>
+      </c>
+      <c r="I48">
+        <v>-0.1546860782529572</v>
+      </c>
+      <c r="J48">
+        <v>-0.1490434414361827</v>
+      </c>
+      <c r="K48">
+        <v>31.6</v>
+      </c>
+      <c r="L48">
+        <v>0.2875341219290264</v>
+      </c>
+      <c r="M48">
+        <v>0.062</v>
+      </c>
+      <c r="N48">
+        <v>2.949852507374631e-05</v>
+      </c>
+      <c r="O48">
+        <v>0.001962025316455696</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>-0</v>
+      </c>
+      <c r="S48">
+        <v>0.062</v>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
+      <c r="U48">
+        <v>206.3</v>
+      </c>
+      <c r="V48">
+        <v>0.09815396326957845</v>
+      </c>
+      <c r="W48">
+        <v>0.1370338248048569</v>
+      </c>
+      <c r="X48">
+        <v>0.0523628349557607</v>
+      </c>
+      <c r="Y48">
+        <v>0.0846709898490962</v>
+      </c>
+      <c r="AB48">
+        <v>0.05230011225339906</v>
+      </c>
+      <c r="AD48">
+        <v>15.7</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>15.7</v>
+      </c>
+      <c r="AG48">
+        <v>-190.6</v>
+      </c>
+      <c r="AH48">
+        <v>0.007414403778040141</v>
+      </c>
+      <c r="AI48">
+        <v>0.05769937522969497</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.09972791963164504</v>
+      </c>
+      <c r="AK48">
+        <v>-2.89665653495441</v>
+      </c>
+      <c r="AL48">
+        <v>0.518</v>
+      </c>
+      <c r="AM48">
+        <v>-3.062</v>
+      </c>
+      <c r="AN48">
+        <v>-1.105633802816901</v>
+      </c>
+      <c r="AO48">
+        <v>-32.81853281853282</v>
+      </c>
+      <c r="AP48">
+        <v>13.42253521126761</v>
+      </c>
+      <c r="AQ48">
+        <v>5.551926845199215</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1825</v>
+        <v>-6E-05</v>
       </c>
       <c r="E2">
-        <v>0.2353</v>
+        <v>-0.0584</v>
       </c>
       <c r="F2">
-        <v>0.0407</v>
+        <v>0.127</v>
       </c>
       <c r="G2">
-        <v>0.0432557767650116</v>
+        <v>0.07803020185055165</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.04362540095161421</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.01904501242223882</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01547376471100002</v>
       </c>
       <c r="K2">
-        <v>1704.4</v>
+        <v>2533.521</v>
       </c>
       <c r="L2">
-        <v>0.4542522853868501</v>
+        <v>0.1890336049495281</v>
       </c>
       <c r="M2">
-        <v>354.7</v>
+        <v>4249.528</v>
       </c>
       <c r="N2">
-        <v>0.00610302708078467</v>
+        <v>0.04930899403120852</v>
       </c>
       <c r="O2">
-        <v>0.2081084252522882</v>
+        <v>1.67732100898315</v>
       </c>
       <c r="P2">
-        <v>354.7</v>
+        <v>2886.654</v>
       </c>
       <c r="Q2">
-        <v>0.00610302708078467</v>
+        <v>0.03349501517725361</v>
       </c>
       <c r="R2">
-        <v>0.2081084252522882</v>
+        <v>1.139384279822429</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1362.874</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.3207118531752232</v>
       </c>
       <c r="U2">
-        <v>30723.2</v>
+        <v>44149.656</v>
       </c>
       <c r="V2">
-        <v>0.5286284793018426</v>
+        <v>0.5122863349021137</v>
       </c>
       <c r="W2">
-        <v>0.1163074085951621</v>
+        <v>0.02635658914728682</v>
       </c>
       <c r="X2">
-        <v>0.179860096712707</v>
+        <v>0.06201886584828469</v>
       </c>
       <c r="Y2">
-        <v>-0.06355268811754483</v>
+        <v>-0.03566227670099787</v>
       </c>
       <c r="Z2">
-        <v>0.0677011629060924</v>
+        <v>0.1011553874271458</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05711419509989529</v>
+        <v>0.05820881324345277</v>
       </c>
       <c r="AC2">
-        <v>-0.05711419509989529</v>
+        <v>-0.05648652976941106</v>
       </c>
       <c r="AD2">
-        <v>73389.10000000001</v>
+        <v>140241.272</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.7820573053422106</v>
       </c>
       <c r="AF2">
-        <v>73389.10000000001</v>
+        <v>140242.0540573053</v>
       </c>
       <c r="AG2">
-        <v>42665.90000000001</v>
+        <v>96092.39805730533</v>
       </c>
       <c r="AH2">
-        <v>0.5580589136157704</v>
+        <v>0.619378989537072</v>
       </c>
       <c r="AI2">
-        <v>0.8196016635694375</v>
+        <v>0.7375042790295129</v>
       </c>
       <c r="AJ2">
-        <v>0.4233374940219042</v>
+        <v>0.5271865382965634</v>
       </c>
       <c r="AK2">
-        <v>0.7253736875034003</v>
+        <v>0.6581312370630573</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>173.881</v>
       </c>
       <c r="AM2">
-        <v>-370</v>
+        <v>-789.2990000000001</v>
+      </c>
+      <c r="AN2">
+        <v>316.1834496690294</v>
+      </c>
+      <c r="AO2">
+        <v>1.464185276137128</v>
+      </c>
+      <c r="AP2">
+        <v>216.6468220904923</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>-0.3225571044686487</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
+          <t>JF SmartInvest Holdings Ltd (SEHK:9636)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,110 +724,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.151</v>
-      </c>
-      <c r="E3">
-        <v>0.08160000000000001</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2431059506531204</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.09506531204644411</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.05079825834542815</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.05079825834542815</v>
       </c>
       <c r="K3">
-        <v>560.2</v>
+        <v>7.47</v>
       </c>
       <c r="L3">
-        <v>0.2377657994142864</v>
+        <v>0.02710449927431059</v>
       </c>
       <c r="M3">
-        <v>129.6</v>
+        <v>54.6</v>
       </c>
       <c r="N3">
-        <v>0.05687702975511279</v>
+        <v>0.03523035230352304</v>
       </c>
       <c r="O3">
-        <v>0.2313459478757586</v>
+        <v>7.309236947791165</v>
       </c>
       <c r="P3">
-        <v>129.6</v>
+        <v>29.6</v>
       </c>
       <c r="Q3">
-        <v>0.05687702975511279</v>
+        <v>0.01909923861143373</v>
       </c>
       <c r="R3">
-        <v>0.2313459478757586</v>
+        <v>3.962516733601071</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4578754578754579</v>
       </c>
       <c r="U3">
-        <v>14755.6</v>
+        <v>99.3</v>
       </c>
       <c r="V3">
-        <v>6.475730711840605</v>
+        <v>0.06407278358497871</v>
       </c>
       <c r="W3">
-        <v>0.1141099545760088</v>
+        <v>0.04420118343195266</v>
       </c>
       <c r="X3">
-        <v>0.2986403071207657</v>
+        <v>0.05848127680551433</v>
       </c>
       <c r="Y3">
-        <v>-0.1845303525447569</v>
+        <v>-0.01428009337356167</v>
       </c>
       <c r="Z3">
-        <v>0.05507364267698903</v>
+        <v>3.537869062901156</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1797175866495507</v>
       </c>
       <c r="AB3">
-        <v>0.05555020572608484</v>
+        <v>0.05842346332679278</v>
       </c>
       <c r="AC3">
-        <v>-0.05555020572608484</v>
+        <v>0.121294123322758</v>
       </c>
       <c r="AD3">
-        <v>57776.6</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>57776.6</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AG3">
-        <v>43021</v>
+        <v>-90.19</v>
       </c>
       <c r="AH3">
-        <v>0.9620582397527608</v>
+        <v>0.00584382677640146</v>
       </c>
       <c r="AI3">
-        <v>0.9176584197494</v>
+        <v>0.05704088660697514</v>
       </c>
       <c r="AJ3">
-        <v>0.9496993350934666</v>
+        <v>-0.06179047827844424</v>
       </c>
       <c r="AK3">
-        <v>0.8924537343404148</v>
+        <v>-1.492964740936931</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-1.564</v>
+      </c>
+      <c r="AN3">
+        <v>0.5993421052631579</v>
+      </c>
+      <c r="AO3">
+        <v>52.63157894736842</v>
+      </c>
+      <c r="AP3">
+        <v>-5.933552631578947</v>
+      </c>
+      <c r="AQ3">
+        <v>-8.951406649616368</v>
       </c>
     </row>
     <row r="4">
@@ -829,124 +844,4273 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>51 Credit Card Inc. (SEHK:2051)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.422</v>
+      </c>
+      <c r="G4">
+        <v>0.4680769230769231</v>
+      </c>
+      <c r="H4">
+        <v>0.2734615384615385</v>
+      </c>
+      <c r="I4">
+        <v>0.3430769230769231</v>
+      </c>
+      <c r="J4">
+        <v>0.3430769230769231</v>
+      </c>
+      <c r="K4">
+        <v>-4.3</v>
+      </c>
+      <c r="L4">
+        <v>-0.1653846153846154</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>37.3</v>
+      </c>
+      <c r="V4">
+        <v>0.740079365079365</v>
+      </c>
+      <c r="W4">
+        <v>-0.04356636271529888</v>
+      </c>
+      <c r="X4">
+        <v>0.06122504463543001</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1047914073507289</v>
+      </c>
+      <c r="Z4">
+        <v>0.3669724770642202</v>
+      </c>
+      <c r="AA4">
+        <v>0.1258997882851094</v>
+      </c>
+      <c r="AB4">
+        <v>0.05834159721440663</v>
+      </c>
+      <c r="AC4">
+        <v>0.06755819107070277</v>
+      </c>
+      <c r="AD4">
+        <v>14.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>14.9</v>
+      </c>
+      <c r="AG4">
+        <v>-22.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.2281776416539051</v>
+      </c>
+      <c r="AI4">
+        <v>0.1243739565943239</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7999999999999999</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2715151515151515</v>
+      </c>
+      <c r="AL4">
+        <v>1.43</v>
+      </c>
+      <c r="AM4">
+        <v>-0.26</v>
+      </c>
+      <c r="AN4">
+        <v>1.221311475409836</v>
+      </c>
+      <c r="AO4">
+        <v>6.237762237762238</v>
+      </c>
+      <c r="AP4">
+        <v>-1.836065573770492</v>
+      </c>
+      <c r="AQ4">
+        <v>-34.30769230769231</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>China Art Financial Holdings Limited (SEHK:1572)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.17</v>
+      </c>
+      <c r="E5">
+        <v>-0.368</v>
+      </c>
+      <c r="G5">
+        <v>0.2395161290322581</v>
+      </c>
+      <c r="H5">
+        <v>0.2395161290322581</v>
+      </c>
+      <c r="I5">
+        <v>0.2564516129032258</v>
+      </c>
+      <c r="J5">
+        <v>0.1759652605459057</v>
+      </c>
+      <c r="K5">
+        <v>1.79</v>
+      </c>
+      <c r="L5">
+        <v>0.1443548387096774</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>94.2</v>
+      </c>
+      <c r="V5">
+        <v>4.55072463768116</v>
+      </c>
+      <c r="W5">
+        <v>0.01183862433862434</v>
+      </c>
+      <c r="X5">
+        <v>0.05894253339673284</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0471039090581085</v>
+      </c>
+      <c r="Z5">
+        <v>0.3768996960486323</v>
+      </c>
+      <c r="AA5">
+        <v>0.06632125321487026</v>
+      </c>
+      <c r="AB5">
+        <v>0.05840655507730926</v>
+      </c>
+      <c r="AC5">
+        <v>0.007914698137561002</v>
+      </c>
+      <c r="AD5">
+        <v>1.13</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.13</v>
+      </c>
+      <c r="AG5">
+        <v>-93.07000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.05176362803481448</v>
+      </c>
+      <c r="AI5">
+        <v>0.007336233201324417</v>
+      </c>
+      <c r="AJ5">
+        <v>1.286030122979135</v>
+      </c>
+      <c r="AK5">
+        <v>-1.555574126692295</v>
+      </c>
+      <c r="AL5">
+        <v>0.007</v>
+      </c>
+      <c r="AM5">
+        <v>-0.181</v>
+      </c>
+      <c r="AN5">
+        <v>0.353125</v>
+      </c>
+      <c r="AO5">
+        <v>454.2857142857143</v>
+      </c>
+      <c r="AP5">
+        <v>-29.084375</v>
+      </c>
+      <c r="AQ5">
+        <v>-17.56906077348066</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bairong Inc. (SEHK:6608)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0.2615222544113774</v>
+      </c>
+      <c r="H6">
+        <v>0.1156175928364498</v>
+      </c>
+      <c r="I6">
+        <v>0.09428496181195681</v>
+      </c>
+      <c r="J6">
+        <v>0.09047963044833798</v>
+      </c>
+      <c r="K6">
+        <v>37.9</v>
+      </c>
+      <c r="L6">
+        <v>0.09981564392941795</v>
+      </c>
+      <c r="M6">
+        <v>26.5</v>
+      </c>
+      <c r="N6">
+        <v>0.05051467784979032</v>
+      </c>
+      <c r="O6">
+        <v>0.6992084432717678</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>26.5</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>86.3</v>
+      </c>
+      <c r="V6">
+        <v>0.164506290507053</v>
+      </c>
+      <c r="W6">
+        <v>0.06274834437086092</v>
+      </c>
+      <c r="X6">
+        <v>0.05863319407232064</v>
+      </c>
+      <c r="Y6">
+        <v>0.004115150298540281</v>
+      </c>
+      <c r="Z6">
+        <v>0.7045834106513267</v>
+      </c>
+      <c r="AA6">
+        <v>0.06375044661576158</v>
+      </c>
+      <c r="AB6">
+        <v>0.0583774954464221</v>
+      </c>
+      <c r="AC6">
+        <v>0.005372951169339481</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>11.5</v>
+      </c>
+      <c r="AG6">
+        <v>-74.8</v>
+      </c>
+      <c r="AH6">
+        <v>0.02145122178698004</v>
+      </c>
+      <c r="AI6">
+        <v>0.01800250469630557</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1662961316140507</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1353846153846154</v>
+      </c>
+      <c r="AL6">
+        <v>1.69</v>
+      </c>
+      <c r="AM6">
+        <v>-10.11</v>
+      </c>
+      <c r="AN6">
+        <v>0.2896725440806045</v>
+      </c>
+      <c r="AO6">
+        <v>21.18343195266272</v>
+      </c>
+      <c r="AP6">
+        <v>-1.884130982367758</v>
+      </c>
+      <c r="AQ6">
+        <v>-3.54104846686449</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>China Huirong Financial Holdings Limited (SEHK:1290)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.117</v>
+      </c>
+      <c r="E7">
+        <v>-0.0584</v>
+      </c>
+      <c r="G7">
+        <v>0.2105820105820106</v>
+      </c>
+      <c r="H7">
+        <v>0.2105820105820106</v>
+      </c>
+      <c r="I7">
+        <v>0.2465608465608466</v>
+      </c>
+      <c r="J7">
+        <v>0.1766432350718065</v>
+      </c>
+      <c r="K7">
+        <v>6.8</v>
+      </c>
+      <c r="L7">
+        <v>0.07195767195767196</v>
+      </c>
+      <c r="M7">
+        <v>6.88</v>
+      </c>
+      <c r="N7">
+        <v>0.06126447016918967</v>
+      </c>
+      <c r="O7">
+        <v>1.011764705882353</v>
+      </c>
+      <c r="P7">
+        <v>6.88</v>
+      </c>
+      <c r="Q7">
+        <v>0.06126447016918967</v>
+      </c>
+      <c r="R7">
+        <v>1.011764705882353</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>17.1</v>
+      </c>
+      <c r="V7">
+        <v>0.1522707034728406</v>
+      </c>
+      <c r="W7">
+        <v>0.02635658914728682</v>
+      </c>
+      <c r="X7">
+        <v>0.07198437895099571</v>
+      </c>
+      <c r="Y7">
+        <v>-0.04562778980370889</v>
+      </c>
+      <c r="Z7">
+        <v>0.3007638446849141</v>
+      </c>
+      <c r="AA7">
+        <v>0.05312789851777758</v>
+      </c>
+      <c r="AB7">
+        <v>0.05820881324345277</v>
+      </c>
+      <c r="AC7">
+        <v>-0.005080914725675185</v>
+      </c>
+      <c r="AD7">
+        <v>160.8</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>160.8</v>
+      </c>
+      <c r="AG7">
+        <v>143.7</v>
+      </c>
+      <c r="AH7">
+        <v>0.5887953130721347</v>
+      </c>
+      <c r="AI7">
+        <v>0.3494892414692458</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5613281250000001</v>
+      </c>
+      <c r="AK7">
+        <v>0.3243792325056434</v>
+      </c>
+      <c r="AL7">
+        <v>7.31</v>
+      </c>
+      <c r="AM7">
+        <v>7.31</v>
+      </c>
+      <c r="AN7">
+        <v>6.784810126582279</v>
+      </c>
+      <c r="AO7">
+        <v>3.187414500683995</v>
+      </c>
+      <c r="AP7">
+        <v>6.063291139240508</v>
+      </c>
+      <c r="AQ7">
+        <v>3.187414500683995</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SPIC Industry-Finance Holdings Co., Ltd. (SZSE:000958)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.204</v>
+      </c>
+      <c r="E8">
+        <v>-0.0688</v>
+      </c>
+      <c r="G8">
+        <v>0.4221774685707311</v>
+      </c>
+      <c r="H8">
+        <v>0.4202367875015257</v>
+      </c>
+      <c r="I8">
+        <v>0.2685219089466618</v>
+      </c>
+      <c r="J8">
+        <v>0.2189092895793738</v>
+      </c>
+      <c r="K8">
+        <v>187.7</v>
+      </c>
+      <c r="L8">
+        <v>0.2290980104967655</v>
+      </c>
+      <c r="M8">
+        <v>105.9</v>
+      </c>
+      <c r="N8">
+        <v>0.02304729156238439</v>
+      </c>
+      <c r="O8">
+        <v>0.564198188598828</v>
+      </c>
+      <c r="P8">
+        <v>95.5</v>
+      </c>
+      <c r="Q8">
+        <v>0.02078391259875079</v>
+      </c>
+      <c r="R8">
+        <v>0.5087906233351093</v>
+      </c>
+      <c r="S8">
+        <v>10.40000000000001</v>
+      </c>
+      <c r="T8">
+        <v>0.09820585457979231</v>
+      </c>
+      <c r="U8">
+        <v>346.6</v>
+      </c>
+      <c r="V8">
+        <v>0.07543145661494266</v>
+      </c>
+      <c r="W8">
+        <v>0.07256630325523854</v>
+      </c>
+      <c r="X8">
+        <v>0.06146098068925679</v>
+      </c>
+      <c r="Y8">
+        <v>0.01110532256598175</v>
+      </c>
+      <c r="Z8">
+        <v>0.2179163231108865</v>
+      </c>
+      <c r="AA8">
+        <v>0.04770390747995344</v>
+      </c>
+      <c r="AB8">
+        <v>0.05833623503535364</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0106323275554002</v>
+      </c>
+      <c r="AD8">
+        <v>1472.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1472.9</v>
+      </c>
+      <c r="AG8">
+        <v>1126.3</v>
+      </c>
+      <c r="AH8">
+        <v>0.2427403671841525</v>
+      </c>
+      <c r="AI8">
+        <v>0.2602204869085898</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1968642942040132</v>
+      </c>
+      <c r="AK8">
+        <v>0.2119655224330021</v>
+      </c>
+      <c r="AL8">
+        <v>53.1</v>
+      </c>
+      <c r="AM8">
+        <v>-72.69999999999999</v>
+      </c>
+      <c r="AN8">
+        <v>4.31303074670571</v>
+      </c>
+      <c r="AO8">
+        <v>4.143126177024482</v>
+      </c>
+      <c r="AP8">
+        <v>3.298096632503661</v>
+      </c>
+      <c r="AQ8">
+        <v>-3.026134800550207</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SY Holdings Group Limited (SEHK:6069)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.115</v>
+      </c>
+      <c r="E9">
+        <v>-0.00326</v>
+      </c>
+      <c r="G9">
+        <v>0.8152610441767069</v>
+      </c>
+      <c r="H9">
+        <v>0.7718875502008031</v>
+      </c>
+      <c r="I9">
+        <v>0.6803212851405622</v>
+      </c>
+      <c r="J9">
+        <v>0.4857520813035179</v>
+      </c>
+      <c r="K9">
+        <v>34.2</v>
+      </c>
+      <c r="L9">
+        <v>0.2746987951807229</v>
+      </c>
+      <c r="M9">
+        <v>45.37</v>
+      </c>
+      <c r="N9">
+        <v>0.04989003738728833</v>
+      </c>
+      <c r="O9">
+        <v>1.326608187134503</v>
+      </c>
+      <c r="P9">
+        <v>42.2</v>
+      </c>
+      <c r="Q9">
+        <v>0.04640422256432813</v>
+      </c>
+      <c r="R9">
+        <v>1.233918128654971</v>
+      </c>
+      <c r="S9">
+        <v>3.170000000000002</v>
+      </c>
+      <c r="T9">
+        <v>0.06986995812210715</v>
+      </c>
+      <c r="U9">
+        <v>102</v>
+      </c>
+      <c r="V9">
+        <v>0.1121618649659116</v>
+      </c>
+      <c r="W9">
+        <v>0.06460143558745751</v>
+      </c>
+      <c r="X9">
+        <v>0.06686710357296317</v>
+      </c>
+      <c r="Y9">
+        <v>-0.002265667985505662</v>
+      </c>
+      <c r="Z9">
+        <v>0.0950019076688287</v>
+      </c>
+      <c r="AA9">
+        <v>0.04614737437793818</v>
+      </c>
+      <c r="AB9">
+        <v>0.0573683669978846</v>
+      </c>
+      <c r="AC9">
+        <v>-0.01122099261994642</v>
+      </c>
+      <c r="AD9">
+        <v>810.7</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>810.7</v>
+      </c>
+      <c r="AG9">
+        <v>708.7</v>
+      </c>
+      <c r="AH9">
+        <v>0.4713098075693274</v>
+      </c>
+      <c r="AI9">
+        <v>0.6023926289196017</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4379828193560349</v>
+      </c>
+      <c r="AK9">
+        <v>0.5697861392506833</v>
+      </c>
+      <c r="AL9">
+        <v>54.2</v>
+      </c>
+      <c r="AM9">
+        <v>49.6</v>
+      </c>
+      <c r="AN9">
+        <v>9.492974238875878</v>
+      </c>
+      <c r="AO9">
+        <v>1.562730627306273</v>
+      </c>
+      <c r="AP9">
+        <v>8.298594847775176</v>
+      </c>
+      <c r="AQ9">
+        <v>1.707661290322581</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sunny Loan Top Co.,Ltd. (SHSE:600830)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.0568</v>
+      </c>
+      <c r="E10">
+        <v>0.199</v>
+      </c>
+      <c r="G10">
+        <v>0.179923518164436</v>
+      </c>
+      <c r="H10">
+        <v>0.179923518164436</v>
+      </c>
+      <c r="I10">
+        <v>0.3059273422562142</v>
+      </c>
+      <c r="J10">
+        <v>0.1882982791586998</v>
+      </c>
+      <c r="K10">
+        <v>7.96</v>
+      </c>
+      <c r="L10">
+        <v>0.1521988527724666</v>
+      </c>
+      <c r="M10">
+        <v>6.9</v>
+      </c>
+      <c r="N10">
+        <v>0.009483232545354591</v>
+      </c>
+      <c r="O10">
+        <v>0.8668341708542714</v>
+      </c>
+      <c r="P10">
+        <v>6.9</v>
+      </c>
+      <c r="Q10">
+        <v>0.009483232545354591</v>
+      </c>
+      <c r="R10">
+        <v>0.8668341708542714</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>123.9</v>
+      </c>
+      <c r="V10">
+        <v>0.1702858713578889</v>
+      </c>
+      <c r="W10">
+        <v>0.02737276478679505</v>
+      </c>
+      <c r="X10">
+        <v>0.06201886584828469</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03464610106148965</v>
+      </c>
+      <c r="Z10">
+        <v>0.1859886201991465</v>
+      </c>
+      <c r="AA10">
+        <v>0.03502133712660029</v>
+      </c>
+      <c r="AB10">
+        <v>0.05780854724920664</v>
+      </c>
+      <c r="AC10">
+        <v>-0.02278721012260635</v>
+      </c>
+      <c r="AD10">
+        <v>276.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>276.1</v>
+      </c>
+      <c r="AG10">
+        <v>152.2</v>
+      </c>
+      <c r="AH10">
+        <v>0.2750821958752616</v>
+      </c>
+      <c r="AI10">
+        <v>0.4055522914218567</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1729938622414185</v>
+      </c>
+      <c r="AK10">
+        <v>0.2732986173460227</v>
+      </c>
+      <c r="AL10">
+        <v>0.187</v>
+      </c>
+      <c r="AM10">
+        <v>-2.173</v>
+      </c>
+      <c r="AN10">
+        <v>15.0054347826087</v>
+      </c>
+      <c r="AO10">
+        <v>85.56149732620321</v>
+      </c>
+      <c r="AP10">
+        <v>8.271739130434785</v>
+      </c>
+      <c r="AQ10">
+        <v>-7.363092498849516</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Shanghai Aj Group Co.,Ltd (SHSE:600643)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.0687</v>
+      </c>
+      <c r="G11">
+        <v>0.3333978970669618</v>
+      </c>
+      <c r="H11">
+        <v>0.329551743220808</v>
+      </c>
+      <c r="I11">
+        <v>0.158273381294964</v>
+      </c>
+      <c r="J11">
+        <v>0.158273381294964</v>
+      </c>
+      <c r="K11">
+        <v>-18.2</v>
+      </c>
+      <c r="L11">
+        <v>-0.05035971223021583</v>
+      </c>
+      <c r="M11">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.06061143110323439</v>
+      </c>
+      <c r="O11">
+        <v>-3.758241758241759</v>
+      </c>
+      <c r="P11">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.06061143110323439</v>
+      </c>
+      <c r="R11">
+        <v>-3.758241758241759</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>172.2</v>
+      </c>
+      <c r="V11">
+        <v>0.1525919361984936</v>
+      </c>
+      <c r="W11">
+        <v>-0.01038338658146965</v>
+      </c>
+      <c r="X11">
+        <v>0.06930450963036039</v>
+      </c>
+      <c r="Y11">
+        <v>-0.07968789621183003</v>
+      </c>
+      <c r="Z11">
+        <v>0.1224470435171507</v>
+      </c>
+      <c r="AA11">
+        <v>0.01938010760703105</v>
+      </c>
+      <c r="AB11">
+        <v>0.05722630576223846</v>
+      </c>
+      <c r="AC11">
+        <v>-0.03784619815520741</v>
+      </c>
+      <c r="AD11">
+        <v>1296.5</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>1296.5</v>
+      </c>
+      <c r="AG11">
+        <v>1124.3</v>
+      </c>
+      <c r="AH11">
+        <v>0.534639175257732</v>
+      </c>
+      <c r="AI11">
+        <v>0.4200822991932087</v>
+      </c>
+      <c r="AJ11">
+        <v>0.4990678267045454</v>
+      </c>
+      <c r="AK11">
+        <v>0.3858138018599224</v>
+      </c>
+      <c r="AL11">
+        <v>23.9</v>
+      </c>
+      <c r="AM11">
+        <v>13.5</v>
+      </c>
+      <c r="AN11">
+        <v>15.73422330097087</v>
+      </c>
+      <c r="AO11">
+        <v>2.393305439330544</v>
+      </c>
+      <c r="AP11">
+        <v>13.64441747572815</v>
+      </c>
+      <c r="AQ11">
+        <v>4.237037037037037</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Metropolis Capital Holdings Limited (SEHK:8621)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.09949999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0.06429667468424065</v>
+      </c>
+      <c r="J12">
+        <v>0.06429667468424065</v>
+      </c>
+      <c r="K12">
+        <v>-1.07</v>
+      </c>
+      <c r="L12">
+        <v>-0.193840579710145</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>8.24</v>
+      </c>
+      <c r="V12">
+        <v>1.551789077212806</v>
+      </c>
+      <c r="W12">
+        <v>-0.03715277777777778</v>
+      </c>
+      <c r="X12">
+        <v>0.06334819936701956</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1005009771447973</v>
+      </c>
+      <c r="Z12">
+        <v>0.1562393338230369</v>
+      </c>
+      <c r="AA12">
+        <v>0.01004566961970228</v>
+      </c>
+      <c r="AB12">
+        <v>0.05829967128811232</v>
+      </c>
+      <c r="AC12">
+        <v>-0.04825400166841005</v>
+      </c>
+      <c r="AD12">
+        <v>2.35</v>
+      </c>
+      <c r="AE12">
+        <v>0.4104117787149584</v>
+      </c>
+      <c r="AF12">
+        <v>2.760411778714959</v>
+      </c>
+      <c r="AG12">
+        <v>-5.479588221285042</v>
+      </c>
+      <c r="AH12">
+        <v>0.3420410078696747</v>
+      </c>
+      <c r="AI12">
+        <v>0.090622930470161</v>
+      </c>
+      <c r="AJ12">
+        <v>32.31113682167238</v>
+      </c>
+      <c r="AK12">
+        <v>-0.2466015605765671</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>5.377574370709382</v>
+      </c>
+      <c r="AP12">
+        <v>-12.53910348120147</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Genertec Universal Medical Group Company Limited (SEHK:2666)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.196</v>
+      </c>
+      <c r="E13">
+        <v>0.0771</v>
+      </c>
+      <c r="G13">
+        <v>0.003439925147228796</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>295</v>
+      </c>
+      <c r="L13">
+        <v>0.1623644669491992</v>
+      </c>
+      <c r="M13">
+        <v>83.226</v>
+      </c>
+      <c r="N13">
+        <v>0.0689013991224439</v>
+      </c>
+      <c r="O13">
+        <v>0.2821220338983051</v>
+      </c>
+      <c r="P13">
+        <v>83.226</v>
+      </c>
+      <c r="Q13">
+        <v>0.0689013991224439</v>
+      </c>
+      <c r="R13">
+        <v>0.2821220338983051</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>295.1</v>
+      </c>
+      <c r="V13">
+        <v>0.2443083036675222</v>
+      </c>
+      <c r="W13">
+        <v>0.1274132941735412</v>
+      </c>
+      <c r="X13">
+        <v>0.1131007268217327</v>
+      </c>
+      <c r="Y13">
+        <v>0.01431256735180847</v>
+      </c>
+      <c r="Z13">
+        <v>0.194493507605682</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05427606521928016</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05427606521928016</v>
+      </c>
+      <c r="AD13">
+        <v>6974.4</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>6974.4</v>
+      </c>
+      <c r="AG13">
+        <v>6679.299999999999</v>
+      </c>
+      <c r="AH13">
+        <v>0.8523764711633649</v>
+      </c>
+      <c r="AI13">
+        <v>0.6945299196367222</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8468531291206005</v>
+      </c>
+      <c r="AK13">
+        <v>0.6852813231009152</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Zero2IPO Holdings Inc. (SEHK:1945)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0.08928802588996763</v>
+      </c>
+      <c r="H14">
+        <v>0.01517799352750809</v>
+      </c>
+      <c r="I14">
+        <v>0.01275080906148867</v>
+      </c>
+      <c r="J14">
+        <v>0.009323332106767812</v>
+      </c>
+      <c r="K14">
+        <v>2.5</v>
+      </c>
+      <c r="L14">
+        <v>0.08090614886731393</v>
+      </c>
+      <c r="M14">
+        <v>0.195</v>
+      </c>
+      <c r="N14">
+        <v>0.00352622061482821</v>
+      </c>
+      <c r="O14">
+        <v>0.078</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0.195</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>16.3</v>
+      </c>
+      <c r="V14">
+        <v>0.2947558770343581</v>
+      </c>
+      <c r="W14">
+        <v>0.0328515111695138</v>
+      </c>
+      <c r="X14">
+        <v>0.05924753579095814</v>
+      </c>
+      <c r="Y14">
+        <v>-0.02639602462144434</v>
+      </c>
+      <c r="Z14">
+        <v>0.4110682453106292</v>
+      </c>
+      <c r="AA14">
+        <v>0.003832525769577296</v>
+      </c>
+      <c r="AB14">
+        <v>0.0583962071026546</v>
+      </c>
+      <c r="AC14">
+        <v>-0.0545636813330773</v>
+      </c>
+      <c r="AD14">
+        <v>4.8</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>4.8</v>
+      </c>
+      <c r="AG14">
+        <v>-11.5</v>
+      </c>
+      <c r="AH14">
+        <v>0.07986688851913477</v>
+      </c>
+      <c r="AI14">
+        <v>0.05853658536585366</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.2625570776255708</v>
+      </c>
+      <c r="AK14">
+        <v>-0.1750380517503805</v>
+      </c>
+      <c r="AL14">
+        <v>0.24</v>
+      </c>
+      <c r="AM14">
+        <v>-2.15</v>
+      </c>
+      <c r="AN14">
+        <v>5.918618988902589</v>
+      </c>
+      <c r="AO14">
+        <v>1.641666666666667</v>
+      </c>
+      <c r="AP14">
+        <v>-14.18002466091245</v>
+      </c>
+      <c r="AQ14">
+        <v>-0.1832558139534884</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zhongguancun Science-Tech Leasing Co., Ltd. (SEHK:1601)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.139</v>
+      </c>
+      <c r="E15">
+        <v>0.14</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>38</v>
+      </c>
+      <c r="L15">
+        <v>0.5359661495063469</v>
+      </c>
+      <c r="M15">
+        <v>17.9</v>
+      </c>
+      <c r="N15">
+        <v>0.1256140350877193</v>
+      </c>
+      <c r="O15">
+        <v>0.4710526315789473</v>
+      </c>
+      <c r="P15">
+        <v>17.9</v>
+      </c>
+      <c r="Q15">
+        <v>0.1256140350877193</v>
+      </c>
+      <c r="R15">
+        <v>0.4710526315789473</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>115.6</v>
+      </c>
+      <c r="V15">
+        <v>0.8112280701754385</v>
+      </c>
+      <c r="W15">
+        <v>0.1180857675574891</v>
+      </c>
+      <c r="X15">
+        <v>0.09385043303667531</v>
+      </c>
+      <c r="Y15">
+        <v>0.02423533452081381</v>
+      </c>
+      <c r="Z15">
+        <v>0.08521634615384616</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05458422353753525</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05458422353753525</v>
+      </c>
+      <c r="AD15">
+        <v>533.1</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>533.1</v>
+      </c>
+      <c r="AG15">
+        <v>417.5</v>
+      </c>
+      <c r="AH15">
+        <v>0.7890763765541741</v>
+      </c>
+      <c r="AI15">
+        <v>0.5970433419195879</v>
+      </c>
+      <c r="AJ15">
+        <v>0.7455357142857143</v>
+      </c>
+      <c r="AK15">
+        <v>0.5371156567605815</v>
+      </c>
+      <c r="AL15">
+        <v>0.778</v>
+      </c>
+      <c r="AM15">
+        <v>0.778</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jiangsu Financial Leasing Co., Ltd. (SHSE:600901)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.171</v>
+      </c>
+      <c r="E16">
+        <v>0.136</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>405.7</v>
+      </c>
+      <c r="L16">
+        <v>0.6396027116506385</v>
+      </c>
+      <c r="M16">
+        <v>243.9</v>
+      </c>
+      <c r="N16">
+        <v>0.05887038377986966</v>
+      </c>
+      <c r="O16">
+        <v>0.6011831402514173</v>
+      </c>
+      <c r="P16">
+        <v>243.9</v>
+      </c>
+      <c r="Q16">
+        <v>0.05887038377986966</v>
+      </c>
+      <c r="R16">
+        <v>0.6011831402514173</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>738.4</v>
+      </c>
+      <c r="V16">
+        <v>0.1782283369538981</v>
+      </c>
+      <c r="W16">
+        <v>0.1719650729060699</v>
+      </c>
+      <c r="X16">
+        <v>0.09172578919662977</v>
+      </c>
+      <c r="Y16">
+        <v>0.08023928370944008</v>
+      </c>
+      <c r="Z16">
+        <v>0.0440654416617458</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05463523266425919</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05463523266425919</v>
+      </c>
+      <c r="AD16">
+        <v>14569.6</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>14569.6</v>
+      </c>
+      <c r="AG16">
+        <v>13831.2</v>
+      </c>
+      <c r="AH16">
+        <v>0.7785983775637806</v>
+      </c>
+      <c r="AI16">
+        <v>0.8111571973387524</v>
+      </c>
+      <c r="AJ16">
+        <v>0.7695029542344026</v>
+      </c>
+      <c r="AK16">
+        <v>0.8030610052777954</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>China Development Bank Financial Leasing Co., Ltd. (SEHK:1606)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.151</v>
+      </c>
+      <c r="E17">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>560.2</v>
+      </c>
+      <c r="L17">
+        <v>0.2377657994142864</v>
+      </c>
+      <c r="M17">
+        <v>129.6</v>
+      </c>
+      <c r="N17">
+        <v>0.05687702975511279</v>
+      </c>
+      <c r="O17">
+        <v>0.2313459478757586</v>
+      </c>
+      <c r="P17">
+        <v>129.6</v>
+      </c>
+      <c r="Q17">
+        <v>0.05687702975511279</v>
+      </c>
+      <c r="R17">
+        <v>0.2313459478757586</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>14755.6</v>
+      </c>
+      <c r="V17">
+        <v>6.475730711840605</v>
+      </c>
+      <c r="W17">
+        <v>0.1141099545760088</v>
+      </c>
+      <c r="X17">
+        <v>0.2985286761567131</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1844187215807043</v>
+      </c>
+      <c r="Z17">
+        <v>0.05507364267698903</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05554597025081059</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05554597025081059</v>
+      </c>
+      <c r="AD17">
+        <v>57776.6</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>57776.6</v>
+      </c>
+      <c r="AG17">
+        <v>43021</v>
+      </c>
+      <c r="AH17">
+        <v>0.9620582397527608</v>
+      </c>
+      <c r="AI17">
+        <v>0.9176584197494</v>
+      </c>
+      <c r="AJ17">
+        <v>0.9496993350934666</v>
+      </c>
+      <c r="AK17">
+        <v>0.8924537343404148</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AVIC Industry-Finance Holdings Co., Ltd. (SHSE:600705)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.0216</v>
+      </c>
+      <c r="E18">
+        <v>-0.422</v>
+      </c>
+      <c r="G18">
+        <v>0.006908791278443303</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>28.3</v>
+      </c>
+      <c r="L18">
+        <v>0.01793750396146289</v>
+      </c>
+      <c r="M18">
+        <v>2726.7</v>
+      </c>
+      <c r="N18">
+        <v>0.6212860007291287</v>
+      </c>
+      <c r="O18">
+        <v>96.34982332155477</v>
+      </c>
+      <c r="P18">
+        <v>1742.1</v>
+      </c>
+      <c r="Q18">
+        <v>0.3969422165512212</v>
+      </c>
+      <c r="R18">
+        <v>61.55830388692579</v>
+      </c>
+      <c r="S18">
+        <v>984.5999999999999</v>
+      </c>
+      <c r="T18">
+        <v>0.3610958301243261</v>
+      </c>
+      <c r="U18">
+        <v>8290.299999999999</v>
+      </c>
+      <c r="V18">
+        <v>1.888967371491068</v>
+      </c>
+      <c r="W18">
+        <v>0.005173958352377645</v>
+      </c>
+      <c r="X18">
+        <v>0.1205994624294538</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1154255040770761</v>
+      </c>
+      <c r="Z18">
+        <v>0.06269695873851032</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05647889254764188</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05647889254764188</v>
+      </c>
+      <c r="AD18">
+        <v>28816.4</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>28816.4</v>
+      </c>
+      <c r="AG18">
+        <v>20526.1</v>
+      </c>
+      <c r="AH18">
+        <v>0.8678279305650921</v>
+      </c>
+      <c r="AI18">
+        <v>0.7544073680407567</v>
+      </c>
+      <c r="AJ18">
+        <v>0.823848379885129</v>
+      </c>
+      <c r="AK18">
+        <v>0.6863286644308543</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-389.3</v>
+      </c>
+      <c r="AQ18">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VCREDIT Holdings Limited (SEHK:2003)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.127</v>
+      </c>
+      <c r="G19">
+        <v>0.05341614906832298</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>37.4</v>
+      </c>
+      <c r="L19">
+        <v>0.1161490683229814</v>
+      </c>
+      <c r="M19">
+        <v>15.3</v>
+      </c>
+      <c r="N19">
+        <v>0.1240875912408759</v>
+      </c>
+      <c r="O19">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="P19">
+        <v>15.3</v>
+      </c>
+      <c r="Q19">
+        <v>0.1240875912408759</v>
+      </c>
+      <c r="R19">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>191.3</v>
+      </c>
+      <c r="V19">
+        <v>1.551500405515004</v>
+      </c>
+      <c r="W19">
+        <v>0.06646525679758307</v>
+      </c>
+      <c r="X19">
+        <v>0.1203479597025407</v>
+      </c>
+      <c r="Y19">
+        <v>-0.0538827029049576</v>
+      </c>
+      <c r="Z19">
+        <v>0.3508007408214402</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05647993704170764</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05647993704170764</v>
+      </c>
+      <c r="AD19">
+        <v>806.3</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>806.3</v>
+      </c>
+      <c r="AG19">
+        <v>615</v>
+      </c>
+      <c r="AH19">
+        <v>0.8673623063683304</v>
+      </c>
+      <c r="AI19">
+        <v>0.5799884908646238</v>
+      </c>
+      <c r="AJ19">
+        <v>0.8329947175944739</v>
+      </c>
+      <c r="AK19">
+        <v>0.5129702227041454</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Haitong Unitrust International Financial Leasing Co., Ltd. (SEHK:1905)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-6E-05</v>
+      </c>
+      <c r="E20">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>234.8</v>
+      </c>
+      <c r="L20">
+        <v>0.4479206409767264</v>
+      </c>
+      <c r="M20">
+        <v>407.6</v>
+      </c>
+      <c r="N20">
+        <v>0.4319626960576516</v>
+      </c>
+      <c r="O20">
+        <v>1.735945485519591</v>
+      </c>
+      <c r="P20">
+        <v>126.8</v>
+      </c>
+      <c r="Q20">
+        <v>0.1343789741415854</v>
+      </c>
+      <c r="R20">
+        <v>0.5400340715502555</v>
+      </c>
+      <c r="S20">
+        <v>280.8</v>
+      </c>
+      <c r="T20">
+        <v>0.6889106967615309</v>
+      </c>
+      <c r="U20">
+        <v>1239.7</v>
+      </c>
+      <c r="V20">
+        <v>1.31379821958457</v>
+      </c>
+      <c r="W20">
+        <v>0.08444220671797455</v>
+      </c>
+      <c r="X20">
+        <v>0.1188003671990905</v>
+      </c>
+      <c r="Y20">
+        <v>-0.03435816048111599</v>
+      </c>
+      <c r="Z20">
+        <v>0.06074159907300116</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.05648652976941106</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05648652976941106</v>
+      </c>
+      <c r="AD20">
+        <v>6016.3</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>6016.3</v>
+      </c>
+      <c r="AG20">
+        <v>4776.6</v>
+      </c>
+      <c r="AH20">
+        <v>0.8644233394157962</v>
+      </c>
+      <c r="AI20">
+        <v>0.6723099444612066</v>
+      </c>
+      <c r="AJ20">
+        <v>0.835040732841509</v>
+      </c>
+      <c r="AK20">
+        <v>0.6196134388377222</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-5.68</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Yixin Group Limited (SEHK:2858)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.042</v>
+      </c>
+      <c r="E21">
+        <v>0.4320000000000001</v>
+      </c>
+      <c r="F21">
+        <v>0.127</v>
+      </c>
+      <c r="G21">
+        <v>0.02903258552431225</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="L21">
+        <v>0.09755354786316109</v>
+      </c>
+      <c r="M21">
+        <v>25.336</v>
+      </c>
+      <c r="N21">
+        <v>0.0338943143812709</v>
+      </c>
+      <c r="O21">
+        <v>0.2636420395421436</v>
+      </c>
+      <c r="P21">
+        <v>24.5</v>
+      </c>
+      <c r="Q21">
+        <v>0.03277591973244147</v>
+      </c>
+      <c r="R21">
+        <v>0.2549427679500521</v>
+      </c>
+      <c r="S21">
+        <v>0.8359999999999985</v>
+      </c>
+      <c r="T21">
+        <v>0.0329965266814019</v>
+      </c>
+      <c r="U21">
+        <v>612.5</v>
+      </c>
+      <c r="V21">
+        <v>0.8193979933110368</v>
+      </c>
+      <c r="W21">
+        <v>0.04491283824835257</v>
+      </c>
+      <c r="X21">
+        <v>0.1006766659682242</v>
+      </c>
+      <c r="Y21">
+        <v>-0.05576382771987159</v>
+      </c>
+      <c r="Z21">
+        <v>0.2366322363680038</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05659310138384641</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05659310138384641</v>
+      </c>
+      <c r="AD21">
+        <v>3335.3</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>3335.3</v>
+      </c>
+      <c r="AG21">
+        <v>2722.8</v>
+      </c>
+      <c r="AH21">
+        <v>0.8169148623493681</v>
+      </c>
+      <c r="AI21">
+        <v>0.6019201963509051</v>
+      </c>
+      <c r="AJ21">
+        <v>0.7846007549779558</v>
+      </c>
+      <c r="AK21">
+        <v>0.5524489713103112</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Anhui Xinli Finance Co., Ltd. (SHSE:600318)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.0935</v>
+      </c>
+      <c r="E22">
+        <v>-0.15</v>
+      </c>
+      <c r="G22">
+        <v>0.03463541666666667</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>3.4</v>
+      </c>
+      <c r="L22">
+        <v>0.08854166666666667</v>
+      </c>
+      <c r="M22">
+        <v>4.5</v>
+      </c>
+      <c r="N22">
+        <v>0.007563025210084034</v>
+      </c>
+      <c r="O22">
+        <v>1.323529411764706</v>
+      </c>
+      <c r="P22">
+        <v>4.5</v>
+      </c>
+      <c r="Q22">
+        <v>0.007563025210084034</v>
+      </c>
+      <c r="R22">
+        <v>1.323529411764706</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>35.4</v>
+      </c>
+      <c r="V22">
+        <v>0.05949579831932773</v>
+      </c>
+      <c r="W22">
+        <v>0.02361111111111111</v>
+      </c>
+      <c r="X22">
+        <v>0.06173904332849053</v>
+      </c>
+      <c r="Y22">
+        <v>-0.03812793221737942</v>
+      </c>
+      <c r="Z22">
+        <v>0.1476695892939548</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05784414489869755</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05784414489869755</v>
+      </c>
+      <c r="AD22">
+        <v>208.2</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>208.2</v>
+      </c>
+      <c r="AG22">
+        <v>172.8</v>
+      </c>
+      <c r="AH22">
+        <v>0.2592131474103586</v>
+      </c>
+      <c r="AI22">
+        <v>0.4079153605015674</v>
+      </c>
+      <c r="AJ22">
+        <v>0.2250586090127637</v>
+      </c>
+      <c r="AK22">
+        <v>0.3637894736842105</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-3.37</v>
+      </c>
+      <c r="AQ22">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Differ Group Auto Limited (SEHK:6878)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.175</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-346.4</v>
+      </c>
+      <c r="L23">
+        <v>-1.911699779249448</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>4.22</v>
+      </c>
+      <c r="V23">
+        <v>0.4912689173457508</v>
+      </c>
+      <c r="W23">
+        <v>-0.9874572405929304</v>
+      </c>
+      <c r="X23">
+        <v>0.4044541871949952</v>
+      </c>
+      <c r="Y23">
+        <v>-1.391911427787926</v>
+      </c>
+      <c r="Z23">
+        <v>0.291599613775346</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.0580672103852973</v>
+      </c>
+      <c r="AC23">
+        <v>-0.0580672103852973</v>
+      </c>
+      <c r="AD23">
+        <v>313.9</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>313.9</v>
+      </c>
+      <c r="AG23">
+        <v>309.6799999999999</v>
+      </c>
+      <c r="AH23">
+        <v>0.9733635151477565</v>
+      </c>
+      <c r="AI23">
+        <v>0.9740279889533621</v>
+      </c>
+      <c r="AJ23">
+        <v>0.973010337135137</v>
+      </c>
+      <c r="AK23">
+        <v>0.9736833831158622</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hanhua Financial Holding Co., Ltd. (SEHK:3903)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>-0.213</v>
+      </c>
+      <c r="E24">
+        <v>-0.302</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>5.85</v>
+      </c>
+      <c r="L24">
+        <v>0.1101694915254237</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>15.3</v>
+      </c>
+      <c r="V24">
+        <v>0.1624203821656051</v>
+      </c>
+      <c r="W24">
+        <v>0.005780061258768896</v>
+      </c>
+      <c r="X24">
+        <v>0.09802139365546866</v>
+      </c>
+      <c r="Y24">
+        <v>-0.09224133239669977</v>
+      </c>
+      <c r="Z24">
+        <v>0.04081601279055467</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.0581284650385589</v>
+      </c>
+      <c r="AC24">
+        <v>-0.0581284650385589</v>
+      </c>
+      <c r="AD24">
+        <v>393.9</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>393.9</v>
+      </c>
+      <c r="AG24">
+        <v>378.6</v>
+      </c>
+      <c r="AH24">
+        <v>0.8070067609096496</v>
+      </c>
+      <c r="AI24">
+        <v>0.2644866715906801</v>
+      </c>
+      <c r="AJ24">
+        <v>0.800761421319797</v>
+      </c>
+      <c r="AK24">
+        <v>0.2568521031207598</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Zuoli Kechuang Micro-finance Company Limited (SEHK:6866)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>-0.07480000000000001</v>
+      </c>
+      <c r="E25">
+        <v>-0.132</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>9.43</v>
+      </c>
+      <c r="L25">
+        <v>0.3864754098360656</v>
+      </c>
+      <c r="M25">
+        <v>3.54</v>
+      </c>
+      <c r="N25">
+        <v>0.08027210884353742</v>
+      </c>
+      <c r="O25">
+        <v>0.3753976670201485</v>
+      </c>
+      <c r="P25">
+        <v>3.54</v>
+      </c>
+      <c r="Q25">
+        <v>0.08027210884353742</v>
+      </c>
+      <c r="R25">
+        <v>0.3753976670201485</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>5.09</v>
+      </c>
+      <c r="V25">
+        <v>0.1154195011337868</v>
+      </c>
+      <c r="W25">
+        <v>0.03554466641537882</v>
+      </c>
+      <c r="X25">
+        <v>0.07489474227389269</v>
+      </c>
+      <c r="Y25">
+        <v>-0.03935007585851387</v>
+      </c>
+      <c r="Z25">
+        <v>0.07084373729748562</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.05819182448041626</v>
+      </c>
+      <c r="AC25">
+        <v>-0.05819182448041626</v>
+      </c>
+      <c r="AD25">
+        <v>76.7</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>76.7</v>
+      </c>
+      <c r="AG25">
+        <v>71.61</v>
+      </c>
+      <c r="AH25">
+        <v>0.634933774834437</v>
+      </c>
+      <c r="AI25">
+        <v>0.208991825613079</v>
+      </c>
+      <c r="AJ25">
+        <v>0.6188747731397458</v>
+      </c>
+      <c r="AK25">
+        <v>0.19786687297947</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Guangdong Join-Share Financing Guarantee Investment Co., Ltd. (SEHK:1543)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.0208</v>
+      </c>
+      <c r="E26">
+        <v>-0.212</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>5.53</v>
+      </c>
+      <c r="L26">
+        <v>0.1307328605200946</v>
+      </c>
+      <c r="M26">
+        <v>7.99</v>
+      </c>
+      <c r="N26">
+        <v>0.07950248756218906</v>
+      </c>
+      <c r="O26">
+        <v>1.444846292947559</v>
+      </c>
+      <c r="P26">
+        <v>7.99</v>
+      </c>
+      <c r="Q26">
+        <v>0.07950248756218906</v>
+      </c>
+      <c r="R26">
+        <v>1.444846292947559</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>75</v>
+      </c>
+      <c r="V26">
+        <v>0.746268656716418</v>
+      </c>
+      <c r="W26">
+        <v>0.01973590292648109</v>
+      </c>
+      <c r="X26">
+        <v>0.06967560347533287</v>
+      </c>
+      <c r="Y26">
+        <v>-0.04993970054885179</v>
+      </c>
+      <c r="Z26">
+        <v>0.1483991832782537</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.05822568519920947</v>
+      </c>
+      <c r="AC26">
+        <v>-0.05822568519920947</v>
+      </c>
+      <c r="AD26">
+        <v>119.4</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>119.4</v>
+      </c>
+      <c r="AG26">
+        <v>44.40000000000001</v>
+      </c>
+      <c r="AH26">
+        <v>0.5429740791268759</v>
+      </c>
+      <c r="AI26">
+        <v>0.2705642420122366</v>
+      </c>
+      <c r="AJ26">
+        <v>0.3064182194616977</v>
+      </c>
+      <c r="AK26">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Baiying Holdings Group Limited (SEHK:8525)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>-0.0579</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-2.54</v>
+      </c>
+      <c r="L27">
+        <v>-0.5291666666666667</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1.37</v>
+      </c>
+      <c r="V27">
+        <v>0.08404907975460123</v>
+      </c>
+      <c r="W27">
+        <v>-0.07514792899408285</v>
+      </c>
+      <c r="X27">
+        <v>0.05995346943976755</v>
+      </c>
+      <c r="Y27">
+        <v>-0.1351013984338504</v>
+      </c>
+      <c r="Z27">
+        <v>0.1314096421824951</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.05837445824895609</v>
+      </c>
+      <c r="AC27">
+        <v>-0.05837445824895609</v>
+      </c>
+      <c r="AD27">
+        <v>2.63</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>2.63</v>
+      </c>
+      <c r="AG27">
+        <v>1.26</v>
+      </c>
+      <c r="AH27">
+        <v>0.138932910723719</v>
+      </c>
+      <c r="AI27">
+        <v>0.07705830647524171</v>
+      </c>
+      <c r="AJ27">
+        <v>0.07175398633257402</v>
+      </c>
+      <c r="AK27">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quanzhou Huixin Micro-credit Co., Ltd. (SEHK:1577)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>-0.0545</v>
+      </c>
+      <c r="E28">
+        <v>-0.0593</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0.635036496350365</v>
+      </c>
+      <c r="M28">
+        <v>4.68</v>
+      </c>
+      <c r="N28">
+        <v>0.07428571428571427</v>
+      </c>
+      <c r="O28">
+        <v>0.5379310344827586</v>
+      </c>
+      <c r="P28">
+        <v>4.68</v>
+      </c>
+      <c r="Q28">
+        <v>0.07428571428571427</v>
+      </c>
+      <c r="R28">
+        <v>0.5379310344827586</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>20.4</v>
+      </c>
+      <c r="V28">
+        <v>0.3238095238095238</v>
+      </c>
+      <c r="W28">
+        <v>0.0558766859344894</v>
+      </c>
+      <c r="X28">
+        <v>0.05863604201574395</v>
+      </c>
+      <c r="Y28">
+        <v>-0.002759356081254542</v>
+      </c>
+      <c r="Z28">
+        <v>0.09521823742007228</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.05841761047568047</v>
+      </c>
+      <c r="AC28">
+        <v>-0.05841761047568047</v>
+      </c>
+      <c r="AD28">
+        <v>1.4</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>1.4</v>
+      </c>
+      <c r="AG28">
+        <v>-19</v>
+      </c>
+      <c r="AH28">
+        <v>0.0217391304347826</v>
+      </c>
+      <c r="AI28">
+        <v>0.008111239860950173</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.4318181818181818</v>
+      </c>
+      <c r="AK28">
+        <v>-0.1248357424441524</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Yangzhou Guangling District Taihe Rural Micro-finance Company Limited (SEHK:1915)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.137</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-0.6889999999999999</v>
+      </c>
+      <c r="L29">
+        <v>-0.09569444444444443</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.004</v>
+      </c>
+      <c r="V29">
+        <v>0.0001204819277108434</v>
+      </c>
+      <c r="W29">
+        <v>-0.005770519262981574</v>
+      </c>
+      <c r="X29">
+        <v>0.0584589855108507</v>
+      </c>
+      <c r="Y29">
+        <v>-0.06422950477383227</v>
+      </c>
+      <c r="Z29">
+        <v>0.06039204502562468</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.05842432203762234</v>
+      </c>
+      <c r="AC29">
+        <v>-0.05842432203762234</v>
+      </c>
+      <c r="AD29">
+        <v>0.117</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0.117</v>
+      </c>
+      <c r="AG29">
+        <v>0.113</v>
+      </c>
+      <c r="AH29">
+        <v>0.003511720743164151</v>
+      </c>
+      <c r="AI29">
+        <v>0.0009855370334492955</v>
+      </c>
+      <c r="AJ29">
+        <v>0.003392069162188935</v>
+      </c>
+      <c r="AK29">
+        <v>0.0009518755317446279</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>East Money Information Co.,Ltd. (SZSE:300059)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D30">
         <v>0.214</v>
       </c>
-      <c r="E4">
+      <c r="E30">
         <v>0.389</v>
       </c>
-      <c r="F4">
+      <c r="F30">
         <v>0.0407</v>
       </c>
-      <c r="G4">
+      <c r="G30">
         <v>0.1162607449856734</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>1144.2</v>
       </c>
-      <c r="L4">
+      <c r="L30">
         <v>0.8196275071633238</v>
       </c>
-      <c r="M4">
+      <c r="M30">
         <v>225.1</v>
       </c>
-      <c r="N4">
+      <c r="N30">
         <v>0.004031153239338755</v>
       </c>
-      <c r="O4">
+      <c r="O30">
         <v>0.1967313406747072</v>
       </c>
-      <c r="P4">
+      <c r="P30">
         <v>225.1</v>
       </c>
-      <c r="Q4">
+      <c r="Q30">
         <v>0.004031153239338755</v>
       </c>
-      <c r="R4">
+      <c r="R30">
         <v>0.1967313406747072</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
         <v>15967.6</v>
       </c>
-      <c r="V4">
+      <c r="V30">
         <v>0.2859522099709707</v>
       </c>
-      <c r="W4">
+      <c r="W30">
         <v>0.1185048626143155</v>
       </c>
-      <c r="X4">
-        <v>0.06107988630464824</v>
-      </c>
-      <c r="Y4">
-        <v>0.05742497630966722</v>
-      </c>
-      <c r="Z4">
+      <c r="X30">
+        <v>0.06107314011588497</v>
+      </c>
+      <c r="Y30">
+        <v>0.0574317224984305</v>
+      </c>
+      <c r="Z30">
         <v>0.110437795674256</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05867818447370574</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05867818447370574</v>
-      </c>
-      <c r="AD4">
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.05867291233728018</v>
+      </c>
+      <c r="AC30">
+        <v>-0.05867291233728018</v>
+      </c>
+      <c r="AD30">
         <v>15612.5</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
         <v>15612.5</v>
       </c>
-      <c r="AG4">
+      <c r="AG30">
         <v>-355.1000000000004</v>
       </c>
-      <c r="AH4">
+      <c r="AH30">
         <v>0.218501496096713</v>
       </c>
-      <c r="AI4">
+      <c r="AI30">
         <v>0.5873445817579895</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ30">
         <v>-0.00639992790844373</v>
       </c>
-      <c r="AK4">
+      <c r="AK30">
         <v>-0.03345612828460796</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
         <v>-370</v>
       </c>
-      <c r="AQ4">
-        <v>-0</v>
+      <c r="AQ30">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fengyinhe Holdings Limited (SEHK:8030)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.007650000000000001</v>
+      </c>
+      <c r="E31">
+        <v>-0.178</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>4.2</v>
+      </c>
+      <c r="L31">
+        <v>0.2234042553191489</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>-0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>2.64</v>
+      </c>
+      <c r="V31">
+        <v>0.06111111111111111</v>
+      </c>
+      <c r="W31">
+        <v>0.5777166437414031</v>
+      </c>
+      <c r="X31">
+        <v>0.05859724455268406</v>
+      </c>
+      <c r="Y31">
+        <v>0.519119399188719</v>
+      </c>
+      <c r="Z31">
+        <v>3.618864292589028</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.05923084642621634</v>
+      </c>
+      <c r="AC31">
+        <v>-0.05923084642621634</v>
+      </c>
+      <c r="AD31">
+        <v>0.783</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0.783</v>
+      </c>
+      <c r="AG31">
+        <v>-1.857</v>
+      </c>
+      <c r="AH31">
+        <v>0.01780233271945979</v>
+      </c>
+      <c r="AI31">
+        <v>0.06173618229125601</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.04491691459255497</v>
+      </c>
+      <c r="AK31">
+        <v>-0.1849049088917654</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yeahka Limited (SEHK:9923)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.166</v>
+      </c>
+      <c r="F32">
+        <v>0.408</v>
+      </c>
+      <c r="G32">
+        <v>0.0889517819706499</v>
+      </c>
+      <c r="H32">
+        <v>0.01075471698113208</v>
+      </c>
+      <c r="I32">
+        <v>-0.02368972746331237</v>
+      </c>
+      <c r="J32">
+        <v>-0.01184486373165619</v>
+      </c>
+      <c r="K32">
+        <v>1.39</v>
+      </c>
+      <c r="L32">
+        <v>0.002914046121593291</v>
+      </c>
+      <c r="M32">
+        <v>21.9</v>
+      </c>
+      <c r="N32">
+        <v>0.03229135948097906</v>
+      </c>
+      <c r="O32">
+        <v>15.75539568345324</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>-0</v>
+      </c>
+      <c r="S32">
+        <v>21.9</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.1387496313771749</v>
+      </c>
+      <c r="W32">
+        <v>0.003596377749029754</v>
+      </c>
+      <c r="X32">
+        <v>0.0605408989598065</v>
+      </c>
+      <c r="Y32">
+        <v>-0.05694452121077675</v>
+      </c>
+      <c r="Z32">
+        <v>1.521531100478469</v>
+      </c>
+      <c r="AA32">
+        <v>-0.01802232854864434</v>
+      </c>
+      <c r="AB32">
+        <v>0.0580160131821425</v>
+      </c>
+      <c r="AC32">
+        <v>-0.07603834173078684</v>
+      </c>
+      <c r="AD32">
+        <v>151.5</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>151.5</v>
+      </c>
+      <c r="AG32">
+        <v>57.40000000000001</v>
+      </c>
+      <c r="AH32">
+        <v>0.1825961190791852</v>
+      </c>
+      <c r="AI32">
+        <v>0.2989934872705743</v>
+      </c>
+      <c r="AJ32">
+        <v>0.078031538879826</v>
+      </c>
+      <c r="AK32">
+        <v>0.1391177896267572</v>
+      </c>
+      <c r="AL32">
+        <v>12</v>
+      </c>
+      <c r="AM32">
+        <v>7.3</v>
+      </c>
+      <c r="AN32">
+        <v>-23.34360554699538</v>
+      </c>
+      <c r="AO32">
+        <v>-0.9416666666666668</v>
+      </c>
+      <c r="AP32">
+        <v>-8.844375963020031</v>
+      </c>
+      <c r="AQ32">
+        <v>-1.547945205479452</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Beijing Cuiwei Tower Co., Ltd. (SHSE:603123)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>-0.127</v>
+      </c>
+      <c r="G33">
+        <v>0.05179063360881543</v>
+      </c>
+      <c r="H33">
+        <v>0.01735537190082645</v>
+      </c>
+      <c r="I33">
+        <v>-0.1597796143250689</v>
+      </c>
+      <c r="J33">
+        <v>-0.1597796143250689</v>
+      </c>
+      <c r="K33">
+        <v>-88.7</v>
+      </c>
+      <c r="L33">
+        <v>-0.2443526170798898</v>
+      </c>
+      <c r="M33">
+        <v>7.203</v>
+      </c>
+      <c r="N33">
+        <v>0.008655371304974766</v>
+      </c>
+      <c r="O33">
+        <v>-0.08120631341600902</v>
+      </c>
+      <c r="P33">
+        <v>7.19</v>
+      </c>
+      <c r="Q33">
+        <v>0.00863975006008171</v>
+      </c>
+      <c r="R33">
+        <v>-0.0810597519729425</v>
+      </c>
+      <c r="S33">
+        <v>0.0129999999999999</v>
+      </c>
+      <c r="T33">
+        <v>0.001804803554074677</v>
+      </c>
+      <c r="U33">
+        <v>262.4</v>
+      </c>
+      <c r="V33">
+        <v>0.3153088199951934</v>
+      </c>
+      <c r="W33">
+        <v>-0.2107388928486577</v>
+      </c>
+      <c r="X33">
+        <v>0.06256398587155515</v>
+      </c>
+      <c r="Y33">
+        <v>-0.2733028787202128</v>
+      </c>
+      <c r="Z33">
+        <v>0.7875894988066827</v>
+      </c>
+      <c r="AA33">
+        <v>-0.1258407463658061</v>
+      </c>
+      <c r="AB33">
+        <v>0.05774340385639632</v>
+      </c>
+      <c r="AC33">
+        <v>-0.1835841502222024</v>
+      </c>
+      <c r="AD33">
+        <v>363.7</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>363.7</v>
+      </c>
+      <c r="AG33">
+        <v>101.3</v>
+      </c>
+      <c r="AH33">
+        <v>0.3041224182623965</v>
+      </c>
+      <c r="AI33">
+        <v>0.5089560593338931</v>
+      </c>
+      <c r="AJ33">
+        <v>0.1085163363685056</v>
+      </c>
+      <c r="AK33">
+        <v>0.224015922158337</v>
+      </c>
+      <c r="AL33">
+        <v>15</v>
+      </c>
+      <c r="AM33">
+        <v>11.32</v>
+      </c>
+      <c r="AN33">
+        <v>-9.115288220551378</v>
+      </c>
+      <c r="AO33">
+        <v>-3.866666666666667</v>
+      </c>
+      <c r="AP33">
+        <v>-2.538847117794487</v>
+      </c>
+      <c r="AQ33">
+        <v>-5.123674911660777</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lianlian DigiTech Co., Ltd. (SEHK:2598)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>-0.03920386007237636</v>
+      </c>
+      <c r="H34">
+        <v>-0.2852834740651387</v>
+      </c>
+      <c r="I34">
+        <v>-0.4025974925430973</v>
+      </c>
+      <c r="J34">
+        <v>-0.4025974925430973</v>
+      </c>
+      <c r="K34">
+        <v>-85.90000000000001</v>
+      </c>
+      <c r="L34">
+        <v>-0.5180940892641737</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>79.2</v>
+      </c>
+      <c r="V34">
+        <v>0.06007281553398058</v>
+      </c>
+      <c r="W34">
+        <v>-0.5574302401038287</v>
+      </c>
+      <c r="X34">
+        <v>0.05892829577456973</v>
+      </c>
+      <c r="Y34">
+        <v>-0.6163585358783984</v>
+      </c>
+      <c r="Z34">
+        <v>0.8507436406580251</v>
+      </c>
+      <c r="AA34">
+        <v>-0.3425072565259067</v>
+      </c>
+      <c r="AB34">
+        <v>0.05840705358877841</v>
+      </c>
+      <c r="AC34">
+        <v>-0.4009143101146851</v>
+      </c>
+      <c r="AD34">
+        <v>69.7</v>
+      </c>
+      <c r="AE34">
+        <v>0.288321318227671</v>
+      </c>
+      <c r="AF34">
+        <v>69.98832131822768</v>
+      </c>
+      <c r="AG34">
+        <v>-9.211678681772327</v>
+      </c>
+      <c r="AH34">
+        <v>0.0504097594625228</v>
+      </c>
+      <c r="AI34">
+        <v>0.3522518125568709</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.007036175416304542</v>
+      </c>
+      <c r="AK34">
+        <v>-0.07709271148968018</v>
+      </c>
+      <c r="AL34">
+        <v>2.49</v>
+      </c>
+      <c r="AM34">
+        <v>-19.41</v>
+      </c>
+      <c r="AN34">
+        <v>-1.084099357628358</v>
+      </c>
+      <c r="AO34">
+        <v>-26.90763052208835</v>
+      </c>
+      <c r="AP34">
+        <v>0.1432765414862011</v>
+      </c>
+      <c r="AQ34">
+        <v>3.451828954147347</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Panda Financial Holding Corp., Ltd. (SHSE:600599)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="G35">
+        <v>-0.6580459770114943</v>
+      </c>
+      <c r="H35">
+        <v>-0.6580459770114943</v>
+      </c>
+      <c r="I35">
+        <v>-0.8706896551724139</v>
+      </c>
+      <c r="J35">
+        <v>-0.8706896551724139</v>
+      </c>
+      <c r="K35">
+        <v>-32.5</v>
+      </c>
+      <c r="L35">
+        <v>-0.9339080459770116</v>
+      </c>
+      <c r="M35">
+        <v>0.745</v>
+      </c>
+      <c r="N35">
+        <v>0.002404777275661717</v>
+      </c>
+      <c r="O35">
+        <v>-0.02292307692307692</v>
+      </c>
+      <c r="P35">
+        <v>0.745</v>
+      </c>
+      <c r="Q35">
+        <v>0.002404777275661717</v>
+      </c>
+      <c r="R35">
+        <v>-0.02292307692307692</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>56.3</v>
+      </c>
+      <c r="V35">
+        <v>0.1817301484828922</v>
+      </c>
+      <c r="W35">
+        <v>-0.284339457567804</v>
+      </c>
+      <c r="X35">
+        <v>0.05881379774368689</v>
+      </c>
+      <c r="Y35">
+        <v>-0.3431532553114909</v>
+      </c>
+      <c r="Z35">
+        <v>0.464</v>
+      </c>
+      <c r="AA35">
+        <v>-0.404</v>
+      </c>
+      <c r="AB35">
+        <v>0.05841111494229168</v>
+      </c>
+      <c r="AC35">
+        <v>-0.4624111149422917</v>
+      </c>
+      <c r="AD35">
+        <v>12.7</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>12.7</v>
+      </c>
+      <c r="AG35">
+        <v>-43.59999999999999</v>
+      </c>
+      <c r="AH35">
+        <v>0.03937984496124031</v>
+      </c>
+      <c r="AI35">
+        <v>0.125</v>
+      </c>
+      <c r="AJ35">
+        <v>-0.1637866265965439</v>
+      </c>
+      <c r="AK35">
+        <v>-0.962472406181015</v>
+      </c>
+      <c r="AL35">
+        <v>0.777</v>
+      </c>
+      <c r="AM35">
+        <v>0.415</v>
+      </c>
+      <c r="AN35">
+        <v>-0.4205298013245033</v>
+      </c>
+      <c r="AO35">
+        <v>-38.996138996139</v>
+      </c>
+      <c r="AP35">
+        <v>1.443708609271523</v>
+      </c>
+      <c r="AQ35">
+        <v>-73.01204819277108</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Shanghai DZH Limited (SHSE:601519)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.0374</v>
+      </c>
+      <c r="G36">
+        <v>0.09005628517823641</v>
+      </c>
+      <c r="H36">
+        <v>-0.2101313320825516</v>
+      </c>
+      <c r="I36">
+        <v>-0.3545966228893058</v>
+      </c>
+      <c r="J36">
+        <v>-0.3545966228893058</v>
+      </c>
+      <c r="K36">
+        <v>-47</v>
+      </c>
+      <c r="L36">
+        <v>-0.4409005628517824</v>
+      </c>
+      <c r="M36">
+        <v>9.563000000000001</v>
+      </c>
+      <c r="N36">
+        <v>0.003765701909824769</v>
+      </c>
+      <c r="O36">
+        <v>-0.203468085106383</v>
+      </c>
+      <c r="P36">
+        <v>0.103</v>
+      </c>
+      <c r="Q36">
+        <v>4.055916518999803E-05</v>
+      </c>
+      <c r="R36">
+        <v>-0.002191489361702127</v>
+      </c>
+      <c r="S36">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="T36">
+        <v>0.9892293213426749</v>
+      </c>
+      <c r="U36">
+        <v>187.9</v>
+      </c>
+      <c r="V36">
+        <v>0.07399094309903524</v>
+      </c>
+      <c r="W36">
+        <v>-0.1836654943337241</v>
+      </c>
+      <c r="X36">
+        <v>0.05851846146955188</v>
+      </c>
+      <c r="Y36">
+        <v>-0.242183955803276</v>
+      </c>
+      <c r="Z36">
+        <v>5.857142857142853</v>
+      </c>
+      <c r="AA36">
+        <v>-1</v>
+      </c>
+      <c r="AB36">
+        <v>0.05840383378651159</v>
+      </c>
+      <c r="AC36">
+        <v>-1.058403833786512</v>
+      </c>
+      <c r="AD36">
+        <v>24.9</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>24.9</v>
+      </c>
+      <c r="AG36">
+        <v>-163</v>
+      </c>
+      <c r="AH36">
+        <v>0.009709873654656059</v>
+      </c>
+      <c r="AI36">
+        <v>0.108355091383812</v>
+      </c>
+      <c r="AJ36">
+        <v>-0.06858826004628656</v>
+      </c>
+      <c r="AK36">
+        <v>-3.890214797136037</v>
+      </c>
+      <c r="AL36">
+        <v>0.467</v>
+      </c>
+      <c r="AM36">
+        <v>-2.663</v>
+      </c>
+      <c r="AN36">
+        <v>-0.7073863636363635</v>
+      </c>
+      <c r="AO36">
+        <v>-80.94218415417558</v>
+      </c>
+      <c r="AP36">
+        <v>4.630681818181817</v>
+      </c>
+      <c r="AQ36">
+        <v>14.19451746150957</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Senmiao Technology Limited (NasdaqCM:AIHS)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.145</v>
+      </c>
+      <c r="G37">
+        <v>-0.5930807248764415</v>
+      </c>
+      <c r="H37">
+        <v>-0.5930807248764415</v>
+      </c>
+      <c r="I37">
+        <v>-0.7327289689752745</v>
+      </c>
+      <c r="J37">
+        <v>-0.7327289689752745</v>
+      </c>
+      <c r="K37">
+        <v>-3.7</v>
+      </c>
+      <c r="L37">
+        <v>-0.6095551894563427</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0.792</v>
+      </c>
+      <c r="V37">
+        <v>0.07008849557522123</v>
+      </c>
+      <c r="W37">
+        <v>-1.456692913385827</v>
+      </c>
+      <c r="X37">
+        <v>0.05887420784574522</v>
+      </c>
+      <c r="Y37">
+        <v>-1.515567121231572</v>
+      </c>
+      <c r="Z37">
+        <v>2.666579733063439</v>
+      </c>
+      <c r="AA37">
+        <v>-1</v>
+      </c>
+      <c r="AB37">
+        <v>0.05840896045276646</v>
+      </c>
+      <c r="AC37">
+        <v>-1.058408960452766</v>
+      </c>
+      <c r="AD37">
+        <v>0.452</v>
+      </c>
+      <c r="AE37">
+        <v>0.08332420839958127</v>
+      </c>
+      <c r="AF37">
+        <v>0.5353242083995813</v>
+      </c>
+      <c r="AG37">
+        <v>-0.2566757916004188</v>
+      </c>
+      <c r="AH37">
+        <v>0.04523105569171137</v>
+      </c>
+      <c r="AI37">
+        <v>0.1436986899536348</v>
+      </c>
+      <c r="AJ37">
+        <v>-0.02324262031582759</v>
+      </c>
+      <c r="AK37">
+        <v>-0.08750338297601984</v>
+      </c>
+      <c r="AL37">
+        <v>0.039</v>
+      </c>
+      <c r="AM37">
+        <v>0.039</v>
+      </c>
+      <c r="AN37">
+        <v>-0.1361035832580548</v>
+      </c>
+      <c r="AO37">
+        <v>-115.3846153846154</v>
+      </c>
+      <c r="AP37">
+        <v>0.077288705691183</v>
+      </c>
+      <c r="AQ37">
+        <v>-115.3846153846154</v>
       </c>
     </row>
   </sheetData>
